--- a/SAV/output/website/SAV_BBpct_LMEresults_All.xlsx
+++ b/SAV/output/website/SAV_BBpct_LMEresults_All.xlsx
@@ -191,7 +191,7 @@
     <t xml:space="preserve">965, 4018, 4049</t>
   </si>
   <si>
-    <t xml:space="preserve">Miami-Dade County DERM Benthic Habitat Monitoring Program, North Biscayne Bay Seagrass Loss Monitoring Program, South Florida Seagrass Fish and Invertebrate Assessment Network, The South Florida Fisheries Habitat Assessment Program (FHAP)</t>
+    <t xml:space="preserve">Miami-Dade County DERM Benthic Habitat Monitoring Program, North Biscayne Bay Seagrass Monitoring Program, South Florida Seagrass Fish and Invertebrate Assessment Network, The South Florida Fisheries Habitat Assessment Program (FHAP)</t>
   </si>
   <si>
     <t xml:space="preserve">965, 4018, 4049, 5027</t>
@@ -827,13 +827,13 @@
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>79.4029214173515</v>
+        <v>79.4024458379973</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.35626636964849</v>
+        <v>-2.3562408050717</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0273449574529121</v>
+        <v>0.0273462910086319</v>
       </c>
       <c r="P2" t="s">
         <v>21</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>29.7876434404689</v>
+        <v>29.7876385227131</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.499367096337099</v>
+        <v>-0.499366822442305</v>
       </c>
       <c r="O3" t="n">
-        <v>0.47169123539315</v>
+        <v>0.471691483034255</v>
       </c>
       <c r="P3" t="s">
         <v>23</v>
@@ -1059,13 +1059,13 @@
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>47.8583554328725</v>
+        <v>47.8583559827204</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.22814508288897</v>
+        <v>-1.22814510144716</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0253567863646845</v>
+        <v>0.0253567825587495</v>
       </c>
       <c r="P7" t="s">
         <v>21</v>
@@ -1109,13 +1109,13 @@
         <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>30.9690324948559</v>
+        <v>30.9690281919503</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.453089171674389</v>
+        <v>-0.453089114504738</v>
       </c>
       <c r="O8" t="n">
-        <v>0.377857977930008</v>
+        <v>0.37785757960882</v>
       </c>
       <c r="P8" t="s">
         <v>23</v>
@@ -1159,13 +1159,13 @@
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>84.8219702012535</v>
+        <v>84.8219501837185</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.63096007154072</v>
+        <v>-2.63095713712759</v>
       </c>
       <c r="O9" t="n">
-        <v>0.00143449561043848</v>
+        <v>0.00143440332984336</v>
       </c>
       <c r="P9" t="s">
         <v>21</v>
@@ -1209,13 +1209,13 @@
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>31.689931606138</v>
+        <v>31.6899376314409</v>
       </c>
       <c r="N10" t="n">
-        <v>0.916393272319195</v>
+        <v>0.916393045143222</v>
       </c>
       <c r="O10" t="n">
-        <v>0.487611162523752</v>
+        <v>0.487611201074338</v>
       </c>
       <c r="P10" t="s">
         <v>23</v>
@@ -1347,13 +1347,13 @@
         <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>60.3078035654648</v>
+        <v>60.3086992409572</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.83626458333325</v>
+        <v>-1.83629600396035</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0314669515239364</v>
+        <v>0.0314622501331645</v>
       </c>
       <c r="P13" t="s">
         <v>21</v>
@@ -1397,13 +1397,13 @@
         <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>42.9808649251357</v>
+        <v>42.9808695316888</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.244491943134917</v>
+        <v>-0.244492117921787</v>
       </c>
       <c r="O14" t="n">
-        <v>0.726844670485489</v>
+        <v>0.726844468394392</v>
       </c>
       <c r="P14" t="s">
         <v>23</v>
@@ -1648,28 +1648,28 @@
         <v>43</v>
       </c>
       <c r="H20" t="n">
-        <v>5015</v>
+        <v>5129</v>
       </c>
       <c r="I20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J20" t="n">
         <v>1997</v>
       </c>
       <c r="K20" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L20" t="b">
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>33.9007874331586</v>
+        <v>32.7066091430685</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.35742555341704</v>
+        <v>-1.27421024612962</v>
       </c>
       <c r="O20" t="n">
-        <v>0.000000000000000000000000203377469239067</v>
+        <v>0.00000000000000000000000000234034760816071</v>
       </c>
       <c r="P20" t="s">
         <v>21</v>
@@ -1698,31 +1698,31 @@
         <v>43</v>
       </c>
       <c r="H21" t="n">
-        <v>15099</v>
+        <v>15441</v>
       </c>
       <c r="I21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J21" t="n">
         <v>1997</v>
       </c>
       <c r="K21" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L21" t="b">
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>0.586438098835243</v>
+        <v>0.499717286812712</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0187455406333436</v>
+        <v>-0.0130908444524584</v>
       </c>
       <c r="O21" t="n">
-        <v>0.00260339690177092</v>
+        <v>0.1417157133767</v>
       </c>
       <c r="P21" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22">
@@ -1748,28 +1748,28 @@
         <v>43</v>
       </c>
       <c r="H22" t="n">
-        <v>5017</v>
+        <v>5131</v>
       </c>
       <c r="I22" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J22" t="n">
         <v>1997</v>
       </c>
       <c r="K22" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L22" t="b">
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>8.1349572946358</v>
+        <v>7.79828345677389</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.368128240338782</v>
+        <v>-0.344328370167375</v>
       </c>
       <c r="O22" t="n">
-        <v>0.000220172022349172</v>
+        <v>0.000230385165200919</v>
       </c>
       <c r="P22" t="s">
         <v>21</v>
@@ -1798,28 +1798,28 @@
         <v>43</v>
       </c>
       <c r="H23" t="n">
-        <v>5033</v>
+        <v>5147</v>
       </c>
       <c r="I23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J23" t="n">
         <v>1997</v>
       </c>
       <c r="K23" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L23" t="b">
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0920067229315442</v>
+        <v>0.0924090068810235</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.00281889011236782</v>
+        <v>-0.00286056085647991</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0740554281068865</v>
+        <v>0.0682854623978636</v>
       </c>
       <c r="P23" t="s">
         <v>23</v>
@@ -1848,16 +1848,16 @@
         <v>43</v>
       </c>
       <c r="H24" t="n">
-        <v>5033</v>
+        <v>5147</v>
       </c>
       <c r="I24" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J24" t="n">
         <v>1997</v>
       </c>
       <c r="K24" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L24" t="b">
         <v>1</v>
@@ -1892,28 +1892,28 @@
         <v>43</v>
       </c>
       <c r="H25" t="n">
-        <v>5268</v>
+        <v>5382</v>
       </c>
       <c r="I25" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J25" t="n">
         <v>1994</v>
       </c>
       <c r="K25" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L25" t="b">
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>40.2866137603621</v>
+        <v>39.0719765042805</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.61058688172235</v>
+        <v>-1.51988946018712</v>
       </c>
       <c r="O25" t="n">
-        <v>0.000000000000000000722113633213353</v>
+        <v>0.00000000000000000016644362385066</v>
       </c>
       <c r="P25" t="s">
         <v>21</v>
@@ -1997,13 +1997,13 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>5.45391072011971</v>
+        <v>5.4539122005051</v>
       </c>
       <c r="N27" t="n">
-        <v>0.812732977917008</v>
+        <v>0.812732920657474</v>
       </c>
       <c r="O27" t="n">
-        <v>0.000000874242615872593</v>
+        <v>0.000000874243938426819</v>
       </c>
       <c r="P27" t="s">
         <v>50</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>24.8297466095871</v>
+        <v>24.8297465486173</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.431455086397473</v>
+        <v>-0.431455084497684</v>
       </c>
       <c r="O28" t="n">
-        <v>0.000128012089267812</v>
+        <v>0.000128012104588442</v>
       </c>
       <c r="P28" t="s">
         <v>21</v>
@@ -2097,13 +2097,13 @@
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>18.5527893672857</v>
+        <v>18.552789337222</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.134772662261152</v>
+        <v>-0.134772661241874</v>
       </c>
       <c r="O29" t="n">
-        <v>0.308991267684262</v>
+        <v>0.308991284377083</v>
       </c>
       <c r="P29" t="s">
         <v>23</v>
@@ -2191,13 +2191,13 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>25.9396036229984</v>
+        <v>25.9396728282327</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.27930890670535</v>
+        <v>-0.279328433842235</v>
       </c>
       <c r="O31" t="n">
-        <v>0.598258418024884</v>
+        <v>0.598233856707755</v>
       </c>
       <c r="P31" t="s">
         <v>23</v>
@@ -2241,13 +2241,13 @@
         <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>35.9453958070078</v>
+        <v>35.9453957791293</v>
       </c>
       <c r="N32" t="n">
-        <v>-0.427177117773613</v>
+        <v>-0.42717713570092</v>
       </c>
       <c r="O32" t="n">
-        <v>0.000053598015625151</v>
+        <v>0.0000535982091523411</v>
       </c>
       <c r="P32" t="s">
         <v>21</v>
@@ -2291,13 +2291,13 @@
         <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>42.516006174884</v>
+        <v>42.5154354067174</v>
       </c>
       <c r="N33" t="n">
-        <v>-0.481511166139247</v>
+        <v>-0.481472297581496</v>
       </c>
       <c r="O33" t="n">
-        <v>0.000000000600899754674316</v>
+        <v>0.000000000604370552252266</v>
       </c>
       <c r="P33" t="s">
         <v>21</v>
@@ -2341,13 +2341,13 @@
         <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.0338584136116649</v>
+        <v>-0.0338584442431049</v>
       </c>
       <c r="N34" t="n">
-        <v>0.00963406012485885</v>
+        <v>0.0096340617960582</v>
       </c>
       <c r="O34" t="n">
-        <v>0.102881512925586</v>
+        <v>0.102881423110622</v>
       </c>
       <c r="P34" t="s">
         <v>23</v>
@@ -2376,7 +2376,7 @@
         <v>58</v>
       </c>
       <c r="H35" t="n">
-        <v>11249</v>
+        <v>11252</v>
       </c>
       <c r="I35" t="n">
         <v>26</v>
@@ -2391,13 +2391,13 @@
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>10.7300595601416</v>
+        <v>10.7299717287469</v>
       </c>
       <c r="N35" t="n">
-        <v>-0.313698497351088</v>
+        <v>-0.313686425316573</v>
       </c>
       <c r="O35" t="n">
-        <v>0.000000497673940350208</v>
+        <v>0.000000494818421991087</v>
       </c>
       <c r="P35" t="s">
         <v>21</v>
@@ -2426,7 +2426,7 @@
         <v>60</v>
       </c>
       <c r="H36" t="n">
-        <v>13865</v>
+        <v>13868</v>
       </c>
       <c r="I36" t="n">
         <v>26</v>
@@ -2441,13 +2441,13 @@
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>8.20628315088408</v>
+        <v>8.20630451675424</v>
       </c>
       <c r="N36" t="n">
-        <v>-0.23154704325086</v>
+        <v>-0.23154800185622</v>
       </c>
       <c r="O36" t="n">
-        <v>0.00000613290236282766</v>
+        <v>0.00000610770243154178</v>
       </c>
       <c r="P36" t="s">
         <v>21</v>
@@ -2476,7 +2476,7 @@
         <v>60</v>
       </c>
       <c r="H37" t="n">
-        <v>40514</v>
+        <v>40526</v>
       </c>
       <c r="I37" t="n">
         <v>25</v>
@@ -2491,13 +2491,13 @@
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>0.668606372700147</v>
+        <v>0.668645792189909</v>
       </c>
       <c r="N37" t="n">
-        <v>-0.0227167001769804</v>
+        <v>-0.022717678236175</v>
       </c>
       <c r="O37" t="n">
-        <v>0.00941316007048729</v>
+        <v>0.00940484396388284</v>
       </c>
       <c r="P37" t="s">
         <v>21</v>
@@ -2526,7 +2526,7 @@
         <v>58</v>
       </c>
       <c r="H38" t="n">
-        <v>9335</v>
+        <v>9338</v>
       </c>
       <c r="I38" t="n">
         <v>20</v>
@@ -2570,7 +2570,7 @@
         <v>60</v>
       </c>
       <c r="H39" t="n">
-        <v>13788</v>
+        <v>13791</v>
       </c>
       <c r="I39" t="n">
         <v>26</v>
@@ -2585,13 +2585,13 @@
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>14.7507003028008</v>
+        <v>14.7500249367134</v>
       </c>
       <c r="N39" t="n">
-        <v>-0.370286460260618</v>
+        <v>-0.370260581585335</v>
       </c>
       <c r="O39" t="n">
-        <v>0.000282124323879578</v>
+        <v>0.000281397786247974</v>
       </c>
       <c r="P39" t="s">
         <v>21</v>
@@ -2620,7 +2620,7 @@
         <v>60</v>
       </c>
       <c r="H40" t="n">
-        <v>14080</v>
+        <v>14083</v>
       </c>
       <c r="I40" t="n">
         <v>26</v>
@@ -2635,13 +2635,13 @@
         <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>45.0504478399706</v>
+        <v>44.9650111183382</v>
       </c>
       <c r="N40" t="n">
-        <v>-1.37948295410189</v>
+        <v>-1.37407678080075</v>
       </c>
       <c r="O40" t="n">
-        <v>0.000000000000000000000000000230874001990556</v>
+        <v>0.000000000000000000000000000125679599318174</v>
       </c>
       <c r="P40" t="s">
         <v>21</v>
@@ -2670,7 +2670,7 @@
         <v>58</v>
       </c>
       <c r="H41" t="n">
-        <v>9399</v>
+        <v>9402</v>
       </c>
       <c r="I41" t="n">
         <v>26</v>
@@ -2685,13 +2685,13 @@
         <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>51.3012406323683</v>
+        <v>51.2374696438551</v>
       </c>
       <c r="N41" t="n">
-        <v>-0.210720901565839</v>
+        <v>-0.206500310474665</v>
       </c>
       <c r="O41" t="n">
-        <v>0.246747964706292</v>
+        <v>0.256494287264958</v>
       </c>
       <c r="P41" t="s">
         <v>23</v>
@@ -2720,7 +2720,7 @@
         <v>60</v>
       </c>
       <c r="H42" t="n">
-        <v>11998</v>
+        <v>12001</v>
       </c>
       <c r="I42" t="n">
         <v>20</v>
@@ -2735,13 +2735,13 @@
         <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>17.1668352676616</v>
+        <v>17.1355555254218</v>
       </c>
       <c r="N42" t="n">
-        <v>0.606021674072554</v>
+        <v>0.607696990107161</v>
       </c>
       <c r="O42" t="n">
-        <v>0.00127316757816461</v>
+        <v>0.00122802477495601</v>
       </c>
       <c r="P42" t="s">
         <v>50</v>
@@ -2829,13 +2829,13 @@
         <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>47.9776204495857</v>
+        <v>47.9776204495858</v>
       </c>
       <c r="N44" t="n">
-        <v>-0.198288963007622</v>
+        <v>-0.198288963007626</v>
       </c>
       <c r="O44" t="n">
-        <v>0.377609133307048</v>
+        <v>0.377609133307038</v>
       </c>
       <c r="P44" t="s">
         <v>23</v>
@@ -2967,13 +2967,13 @@
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>52.3263057424217</v>
+        <v>52.3267182771389</v>
       </c>
       <c r="N47" t="n">
-        <v>-0.496445020780152</v>
+        <v>-0.496461552365028</v>
       </c>
       <c r="O47" t="n">
-        <v>0.0492309598769332</v>
+        <v>0.0491914585084037</v>
       </c>
       <c r="P47" t="s">
         <v>21</v>
@@ -3105,13 +3105,13 @@
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>-11.4840673786696</v>
+        <v>-11.4840654985292</v>
       </c>
       <c r="N50" t="n">
-        <v>1.24661540748319</v>
+        <v>1.24661532602356</v>
       </c>
       <c r="O50" t="n">
-        <v>0.0166233333045051</v>
+        <v>0.0166233464754912</v>
       </c>
       <c r="P50" t="s">
         <v>50</v>
@@ -3155,13 +3155,13 @@
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>21.9819548961927</v>
+        <v>21.9823058362862</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.330012373168787</v>
+        <v>-0.330017781273232</v>
       </c>
       <c r="O51" t="n">
-        <v>0.348782449920717</v>
+        <v>0.348779258545112</v>
       </c>
       <c r="P51" t="s">
         <v>23</v>
@@ -3249,13 +3249,13 @@
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>31.3222862611413</v>
+        <v>31.3183097469319</v>
       </c>
       <c r="N53" t="n">
-        <v>-0.165135704523702</v>
+        <v>-0.164982613440194</v>
       </c>
       <c r="O53" t="n">
-        <v>0.831128064926257</v>
+        <v>0.83124841287508</v>
       </c>
       <c r="P53" t="s">
         <v>23</v>
@@ -3299,13 +3299,13 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>24.5778014751751</v>
+        <v>24.5774894460146</v>
       </c>
       <c r="N54" t="n">
-        <v>0.218495167677927</v>
+        <v>0.21849050167077</v>
       </c>
       <c r="O54" t="n">
-        <v>0.483422207860359</v>
+        <v>0.483437203484199</v>
       </c>
       <c r="P54" t="s">
         <v>23</v>
@@ -3349,13 +3349,13 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>31.2028300204007</v>
+        <v>31.2028301375394</v>
       </c>
       <c r="N55" t="n">
-        <v>-0.394610085552156</v>
+        <v>-0.394610092902706</v>
       </c>
       <c r="O55" t="n">
-        <v>0.320530875879872</v>
+        <v>0.320530874580492</v>
       </c>
       <c r="P55" t="s">
         <v>23</v>
@@ -3487,13 +3487,13 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>19.2210209388705</v>
+        <v>19.2210209918651</v>
       </c>
       <c r="N58" t="n">
-        <v>0.529458795534344</v>
+        <v>0.529458794026777</v>
       </c>
       <c r="O58" t="n">
-        <v>0.0159141933378494</v>
+        <v>0.0159141893678147</v>
       </c>
       <c r="P58" t="s">
         <v>50</v>
@@ -3581,13 +3581,13 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>35.7777232495791</v>
+        <v>35.7777215434534</v>
       </c>
       <c r="N60" t="n">
-        <v>0.825668232311731</v>
+        <v>0.825668344603955</v>
       </c>
       <c r="O60" t="n">
-        <v>0.0760965115153528</v>
+        <v>0.0760969879640776</v>
       </c>
       <c r="P60" t="s">
         <v>23</v>
@@ -3631,13 +3631,13 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>16.2416050985637</v>
+        <v>16.2416047164727</v>
       </c>
       <c r="N61" t="n">
-        <v>0.175117442874633</v>
+        <v>0.175117461352373</v>
       </c>
       <c r="O61" t="n">
-        <v>0.42480740143852</v>
+        <v>0.424807329805699</v>
       </c>
       <c r="P61" t="s">
         <v>23</v>
@@ -3725,13 +3725,13 @@
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>8.13470865386613</v>
+        <v>8.13470493366117</v>
       </c>
       <c r="N63" t="n">
-        <v>-0.201985152177262</v>
+        <v>-0.201984889529685</v>
       </c>
       <c r="O63" t="n">
-        <v>0.386178912889689</v>
+        <v>0.386180086961865</v>
       </c>
       <c r="P63" t="s">
         <v>23</v>
@@ -3775,13 +3775,13 @@
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>20.0363360971138</v>
+        <v>20.0363360880779</v>
       </c>
       <c r="N64" t="n">
-        <v>-0.287623337709177</v>
+        <v>-0.287623336006212</v>
       </c>
       <c r="O64" t="n">
-        <v>0.37852297795719</v>
+        <v>0.378522951480508</v>
       </c>
       <c r="P64" t="s">
         <v>23</v>
@@ -3825,13 +3825,13 @@
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>37.073941318164</v>
+        <v>37.0739399502456</v>
       </c>
       <c r="N65" t="n">
-        <v>-0.830567769864988</v>
+        <v>-0.830567730486169</v>
       </c>
       <c r="O65" t="n">
-        <v>0.00105845486851883</v>
+        <v>0.0010585081754943</v>
       </c>
       <c r="P65" t="s">
         <v>21</v>
@@ -3875,13 +3875,13 @@
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>18.8993364838794</v>
+        <v>18.8993364617153</v>
       </c>
       <c r="N66" t="n">
-        <v>-0.0551538065310624</v>
+        <v>-0.0551538224617119</v>
       </c>
       <c r="O66" t="n">
-        <v>0.922197373226081</v>
+        <v>0.92219735068256</v>
       </c>
       <c r="P66" t="s">
         <v>23</v>
@@ -4013,13 +4013,13 @@
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>26.9390954778279</v>
+        <v>26.9390749103907</v>
       </c>
       <c r="N69" t="n">
-        <v>-0.972095996812152</v>
+        <v>-0.972109067084369</v>
       </c>
       <c r="O69" t="n">
-        <v>0.351760435718147</v>
+        <v>0.351749557583809</v>
       </c>
       <c r="P69" t="s">
         <v>23</v>
@@ -4063,13 +4063,13 @@
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>22.4462541270106</v>
+        <v>22.4462540765769</v>
       </c>
       <c r="N70" t="n">
-        <v>-0.47904710977692</v>
+        <v>-0.479047107062301</v>
       </c>
       <c r="O70" t="n">
-        <v>0.0101183615661718</v>
+        <v>0.0101183628293739</v>
       </c>
       <c r="P70" t="s">
         <v>21</v>
@@ -4113,13 +4113,13 @@
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>47.6649674238452</v>
+        <v>47.6649674238473</v>
       </c>
       <c r="N71" t="n">
-        <v>-1.27036875345826</v>
+        <v>-1.27036875345833</v>
       </c>
       <c r="O71" t="n">
-        <v>0.0235055099480932</v>
+        <v>0.0235055099480849</v>
       </c>
       <c r="P71" t="s">
         <v>21</v>
@@ -4192,28 +4192,28 @@
         <v>56</v>
       </c>
       <c r="H73" t="n">
-        <v>9132</v>
+        <v>9660</v>
       </c>
       <c r="I73" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J73" t="n">
         <v>2008</v>
       </c>
       <c r="K73" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L73" t="b">
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>0.0758368299035063</v>
+        <v>0.0741863485323382</v>
       </c>
       <c r="N73" t="n">
-        <v>-0.00252875986567735</v>
+        <v>-0.00244914775312295</v>
       </c>
       <c r="O73" t="n">
-        <v>0.21189295104168</v>
+        <v>0.196740148903206</v>
       </c>
       <c r="P73" t="s">
         <v>23</v>
@@ -4242,28 +4242,28 @@
         <v>58</v>
       </c>
       <c r="H74" t="n">
-        <v>17509</v>
+        <v>18037</v>
       </c>
       <c r="I74" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J74" t="n">
         <v>1999</v>
       </c>
       <c r="K74" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L74" t="b">
         <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>9.03257305752796</v>
+        <v>8.74319566013521</v>
       </c>
       <c r="N74" t="n">
-        <v>-0.225030998869794</v>
+        <v>-0.20777732678382</v>
       </c>
       <c r="O74" t="n">
-        <v>0.0000182151319884356</v>
+        <v>0.0000785983600721293</v>
       </c>
       <c r="P74" t="s">
         <v>21</v>
@@ -4292,28 +4292,28 @@
         <v>77</v>
       </c>
       <c r="H75" t="n">
-        <v>18961</v>
+        <v>19551</v>
       </c>
       <c r="I75" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J75" t="n">
         <v>1996</v>
       </c>
       <c r="K75" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L75" t="b">
         <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>6.73486166531502</v>
+        <v>6.65893014025401</v>
       </c>
       <c r="N75" t="n">
-        <v>-0.249327439209218</v>
+        <v>-0.244005551617337</v>
       </c>
       <c r="O75" t="n">
-        <v>0.000222134049987985</v>
+        <v>0.000291230507719468</v>
       </c>
       <c r="P75" t="s">
         <v>21</v>
@@ -4342,28 +4342,28 @@
         <v>79</v>
       </c>
       <c r="H76" t="n">
-        <v>46762</v>
+        <v>47846</v>
       </c>
       <c r="I76" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J76" t="n">
         <v>2005</v>
       </c>
       <c r="K76" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L76" t="b">
         <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>0.0759972082175504</v>
+        <v>0.0693824791412447</v>
       </c>
       <c r="N76" t="n">
-        <v>-0.00236205422017377</v>
+        <v>-0.00186620090774331</v>
       </c>
       <c r="O76" t="n">
-        <v>0.303057711180532</v>
+        <v>0.413500371689689</v>
       </c>
       <c r="P76" t="s">
         <v>23</v>
@@ -4392,28 +4392,28 @@
         <v>81</v>
       </c>
       <c r="H77" t="n">
-        <v>17002</v>
+        <v>17558</v>
       </c>
       <c r="I77" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J77" t="n">
         <v>2005</v>
       </c>
       <c r="K77" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L77" t="b">
         <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>-0.037620182191274</v>
+        <v>-0.0286063078687182</v>
       </c>
       <c r="N77" t="n">
-        <v>0.00276837307072622</v>
+        <v>0.00220465781341062</v>
       </c>
       <c r="O77" t="n">
-        <v>0.104988262573557</v>
+        <v>0.127260017280868</v>
       </c>
       <c r="P77" t="s">
         <v>23</v>
@@ -4442,28 +4442,28 @@
         <v>77</v>
       </c>
       <c r="H78" t="n">
-        <v>18880</v>
+        <v>19436</v>
       </c>
       <c r="I78" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J78" t="n">
         <v>1996</v>
       </c>
       <c r="K78" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L78" t="b">
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>4.88761818989823</v>
+        <v>4.94124465717422</v>
       </c>
       <c r="N78" t="n">
-        <v>-0.106401736366778</v>
+        <v>-0.107991097626809</v>
       </c>
       <c r="O78" t="n">
-        <v>0.0205244100822212</v>
+        <v>0.0175021586314602</v>
       </c>
       <c r="P78" t="s">
         <v>21</v>
@@ -4492,28 +4492,28 @@
         <v>77</v>
       </c>
       <c r="H79" t="n">
-        <v>19201</v>
+        <v>19879</v>
       </c>
       <c r="I79" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J79" t="n">
         <v>1996</v>
       </c>
       <c r="K79" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L79" t="b">
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>43.3088390618793</v>
+        <v>42.2873517846192</v>
       </c>
       <c r="N79" t="n">
-        <v>-1.42664895537423</v>
+        <v>-1.38206015255954</v>
       </c>
       <c r="O79" t="n">
-        <v>0.00000000000000000000000000000198475441221113</v>
+        <v>0.000000000000000000000000000505749538387561</v>
       </c>
       <c r="P79" t="s">
         <v>21</v>
@@ -4542,28 +4542,28 @@
         <v>58</v>
       </c>
       <c r="H80" t="n">
-        <v>16233</v>
+        <v>16804</v>
       </c>
       <c r="I80" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J80" t="n">
         <v>1999</v>
       </c>
       <c r="K80" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L80" t="b">
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>31.6516899923504</v>
+        <v>31.2798285343373</v>
       </c>
       <c r="N80" t="n">
-        <v>0.215667371185139</v>
+        <v>0.237657083252429</v>
       </c>
       <c r="O80" t="n">
-        <v>0.164546093099561</v>
+        <v>0.116657820450709</v>
       </c>
       <c r="P80" t="s">
         <v>23</v>
@@ -4592,28 +4592,28 @@
         <v>79</v>
       </c>
       <c r="H81" t="n">
-        <v>15943</v>
+        <v>16627</v>
       </c>
       <c r="I81" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J81" t="n">
         <v>2005</v>
       </c>
       <c r="K81" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L81" t="b">
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>16.7192042598665</v>
+        <v>15.7746961170676</v>
       </c>
       <c r="N81" t="n">
-        <v>0.228935884807721</v>
+        <v>0.276558340253779</v>
       </c>
       <c r="O81" t="n">
-        <v>0.00953016845045274</v>
+        <v>0.00103336552605391</v>
       </c>
       <c r="P81" t="s">
         <v>50</v>
@@ -4642,7 +4642,7 @@
         <v>84</v>
       </c>
       <c r="H82" t="n">
-        <v>1206</v>
+        <v>1280</v>
       </c>
       <c r="I82" t="n">
         <v>10</v>
@@ -4657,13 +4657,13 @@
         <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>65.3698281914598</v>
+        <v>57.578898983305</v>
       </c>
       <c r="N82" t="n">
-        <v>-0.690905530896764</v>
+        <v>-0.376754052299389</v>
       </c>
       <c r="O82" t="n">
-        <v>0.0545337671929453</v>
+        <v>0.295357422338898</v>
       </c>
       <c r="P82" t="s">
         <v>23</v>
@@ -4692,7 +4692,7 @@
         <v>84</v>
       </c>
       <c r="H83" t="n">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="I83" t="n">
         <v>10</v>
@@ -4824,7 +4824,7 @@
         <v>84</v>
       </c>
       <c r="H86" t="n">
-        <v>744</v>
+        <v>799</v>
       </c>
       <c r="I86" t="n">
         <v>10</v>
@@ -4839,13 +4839,13 @@
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>19.5096247739125</v>
+        <v>24.5642568847679</v>
       </c>
       <c r="N86" t="n">
-        <v>1.07987826960051</v>
+        <v>0.873658294447068</v>
       </c>
       <c r="O86" t="n">
-        <v>0.0510252959384295</v>
+        <v>0.141337566141349</v>
       </c>
       <c r="P86" t="s">
         <v>23</v>
@@ -4874,7 +4874,7 @@
         <v>84</v>
       </c>
       <c r="H87" t="n">
-        <v>1481</v>
+        <v>1577</v>
       </c>
       <c r="I87" t="n">
         <v>10</v>
@@ -4889,13 +4889,13 @@
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>88.2665217996213</v>
+        <v>76.7899394419268</v>
       </c>
       <c r="N87" t="n">
-        <v>-1.0880291412905</v>
+        <v>-0.628213299436875</v>
       </c>
       <c r="O87" t="n">
-        <v>0.0665589908704265</v>
+        <v>0.219850271952525</v>
       </c>
       <c r="P87" t="s">
         <v>23</v>
@@ -4924,7 +4924,7 @@
         <v>84</v>
       </c>
       <c r="H88" t="n">
-        <v>1488</v>
+        <v>1584</v>
       </c>
       <c r="I88" t="n">
         <v>10</v>
@@ -4939,13 +4939,13 @@
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>81.4549321940367</v>
+        <v>69.8553875919234</v>
       </c>
       <c r="N88" t="n">
-        <v>-0.870800717005251</v>
+        <v>-0.406426083197994</v>
       </c>
       <c r="O88" t="n">
-        <v>0.162325709325709</v>
+        <v>0.446153345812438</v>
       </c>
       <c r="P88" t="s">
         <v>23</v>
@@ -4989,13 +4989,13 @@
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>-11.3752419427044</v>
+        <v>-11.3750931452145</v>
       </c>
       <c r="N89" t="n">
-        <v>0.911812319697717</v>
+        <v>0.911809230536335</v>
       </c>
       <c r="O89" t="n">
-        <v>0.257183683959014</v>
+        <v>0.257189987451246</v>
       </c>
       <c r="P89" t="s">
         <v>23</v>
@@ -5039,13 +5039,13 @@
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>8.35234095660149</v>
+        <v>8.35281139076768</v>
       </c>
       <c r="N90" t="n">
-        <v>0.370306147987355</v>
+        <v>0.370292305966821</v>
       </c>
       <c r="O90" t="n">
-        <v>0.179767123461435</v>
+        <v>0.179777077709195</v>
       </c>
       <c r="P90" t="s">
         <v>23</v>
@@ -5089,13 +5089,13 @@
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>20.7923996517557</v>
+        <v>20.7923996941562</v>
       </c>
       <c r="N91" t="n">
-        <v>-0.124768398790134</v>
+        <v>-0.124768401354064</v>
       </c>
       <c r="O91" t="n">
-        <v>0.0762040102975333</v>
+        <v>0.0762040357190241</v>
       </c>
       <c r="P91" t="s">
         <v>23</v>
@@ -5226,11 +5226,17 @@
       <c r="L94" t="b">
         <v>1</v>
       </c>
-      <c r="M94"/>
-      <c r="N94"/>
-      <c r="O94"/>
+      <c r="M94" t="n">
+        <v>4.26200141596094</v>
+      </c>
+      <c r="N94" t="n">
+        <v>-0.0392873673000695</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0.79552038130418</v>
+      </c>
       <c r="P94" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="95">
@@ -5271,13 +5277,13 @@
         <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>46.71552547721</v>
+        <v>46.7155255141935</v>
       </c>
       <c r="N95" t="n">
-        <v>-0.256647134401874</v>
+        <v>-0.25664713624158</v>
       </c>
       <c r="O95" t="n">
-        <v>0.622020809866009</v>
+        <v>0.622020803450261</v>
       </c>
       <c r="P95" t="s">
         <v>23</v>
@@ -5321,13 +5327,13 @@
         <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>32.4929157277508</v>
+        <v>32.4933425051872</v>
       </c>
       <c r="N96" t="n">
-        <v>-0.222486917305148</v>
+        <v>-0.222504844024384</v>
       </c>
       <c r="O96" t="n">
-        <v>0.13531248608327</v>
+        <v>0.135218056033289</v>
       </c>
       <c r="P96" t="s">
         <v>23</v>
@@ -5371,13 +5377,13 @@
         <v>1</v>
       </c>
       <c r="M97" t="n">
-        <v>25.2522880735145</v>
+        <v>25.2522887980839</v>
       </c>
       <c r="N97" t="n">
-        <v>-0.198908341061871</v>
+        <v>-0.198908399709913</v>
       </c>
       <c r="O97" t="n">
-        <v>0.00835907721159932</v>
+        <v>0.0083590244169381</v>
       </c>
       <c r="P97" t="s">
         <v>21</v>
@@ -5446,31 +5452,25 @@
         <v>43</v>
       </c>
       <c r="H99" t="n">
-        <v>15696</v>
+        <v>16571</v>
       </c>
       <c r="I99" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J99" t="n">
         <v>1997</v>
       </c>
       <c r="K99" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L99" t="b">
         <v>1</v>
       </c>
-      <c r="M99" t="n">
-        <v>32.8521341427534</v>
-      </c>
-      <c r="N99" t="n">
-        <v>-1.29609511066979</v>
-      </c>
-      <c r="O99" t="n">
-        <v>0.00000000000000000203314969174893</v>
-      </c>
+      <c r="M99"/>
+      <c r="N99"/>
+      <c r="O99"/>
       <c r="P99" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="100">
@@ -5496,28 +5496,28 @@
         <v>43</v>
       </c>
       <c r="H100" t="n">
-        <v>47168</v>
+        <v>49792</v>
       </c>
       <c r="I100" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J100" t="n">
         <v>1997</v>
       </c>
       <c r="K100" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L100" t="b">
         <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>0.5326841297858</v>
+        <v>0.486526056048551</v>
       </c>
       <c r="N100" t="n">
-        <v>-0.00517714511339364</v>
+        <v>-0.00182694608070625</v>
       </c>
       <c r="O100" t="n">
-        <v>0.470825738059433</v>
+        <v>0.790980253872378</v>
       </c>
       <c r="P100" t="s">
         <v>23</v>
@@ -5546,28 +5546,28 @@
         <v>43</v>
       </c>
       <c r="H101" t="n">
-        <v>15731</v>
+        <v>16606</v>
       </c>
       <c r="I101" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J101" t="n">
         <v>1997</v>
       </c>
       <c r="K101" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L101" t="b">
         <v>1</v>
       </c>
       <c r="M101" t="n">
-        <v>0.248551179646674</v>
+        <v>0.236691163978561</v>
       </c>
       <c r="N101" t="n">
-        <v>-0.0116683014031875</v>
+        <v>-0.0108992148815637</v>
       </c>
       <c r="O101" t="n">
-        <v>0.102660869939191</v>
+        <v>0.101584432953808</v>
       </c>
       <c r="P101" t="s">
         <v>23</v>
@@ -5596,28 +5596,28 @@
         <v>43</v>
       </c>
       <c r="H102" t="n">
-        <v>15713</v>
+        <v>16588</v>
       </c>
       <c r="I102" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J102" t="n">
         <v>1997</v>
       </c>
       <c r="K102" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L102" t="b">
         <v>1</v>
       </c>
       <c r="M102" t="n">
-        <v>5.71140192386024</v>
+        <v>5.51511737333523</v>
       </c>
       <c r="N102" t="n">
-        <v>-0.240739223450457</v>
+        <v>-0.226783227475027</v>
       </c>
       <c r="O102" t="n">
-        <v>0.00444282141171528</v>
+        <v>0.00433585695109475</v>
       </c>
       <c r="P102" t="s">
         <v>21</v>
@@ -5646,28 +5646,28 @@
         <v>43</v>
       </c>
       <c r="H103" t="n">
-        <v>15732</v>
+        <v>16607</v>
       </c>
       <c r="I103" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J103" t="n">
         <v>1997</v>
       </c>
       <c r="K103" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L103" t="b">
         <v>1</v>
       </c>
       <c r="M103" t="n">
-        <v>1.77734297189416</v>
+        <v>1.73354024142037</v>
       </c>
       <c r="N103" t="n">
-        <v>-0.0692776737501035</v>
+        <v>-0.0663118425822811</v>
       </c>
       <c r="O103" t="n">
-        <v>0.0975863166895465</v>
+        <v>0.0982887196272221</v>
       </c>
       <c r="P103" t="s">
         <v>23</v>
@@ -5696,28 +5696,28 @@
         <v>43</v>
       </c>
       <c r="H104" t="n">
-        <v>16847</v>
+        <v>17779</v>
       </c>
       <c r="I104" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J104" t="n">
         <v>1994</v>
       </c>
       <c r="K104" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L104" t="b">
         <v>1</v>
       </c>
       <c r="M104" t="n">
-        <v>40.9489597043255</v>
+        <v>39.5068520511913</v>
       </c>
       <c r="N104" t="n">
-        <v>-1.58756424936694</v>
+        <v>-1.47099758677916</v>
       </c>
       <c r="O104" t="n">
-        <v>0.000000000000000000000000375303601367998</v>
+        <v>0.000000000000000000000227816605153144</v>
       </c>
       <c r="P104" t="s">
         <v>21</v>
@@ -5826,28 +5826,28 @@
         <v>43</v>
       </c>
       <c r="H107" t="n">
-        <v>6282</v>
+        <v>6463</v>
       </c>
       <c r="I107" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J107" t="n">
         <v>1998</v>
       </c>
       <c r="K107" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L107" t="b">
         <v>1</v>
       </c>
       <c r="M107" t="n">
-        <v>28.9769326403196</v>
+        <v>27.8792723214916</v>
       </c>
       <c r="N107" t="n">
-        <v>-0.860722448728973</v>
+        <v>-0.781423231347227</v>
       </c>
       <c r="O107" t="n">
-        <v>0.000465450211115611</v>
+        <v>0.000692330268166631</v>
       </c>
       <c r="P107" t="s">
         <v>21</v>
@@ -5876,28 +5876,28 @@
         <v>43</v>
       </c>
       <c r="H108" t="n">
-        <v>18889</v>
+        <v>19432</v>
       </c>
       <c r="I108" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J108" t="n">
         <v>1998</v>
       </c>
       <c r="K108" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L108" t="b">
         <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>0.0856620604066337</v>
+        <v>0.122749951618511</v>
       </c>
       <c r="N108" t="n">
-        <v>0.0127947855670413</v>
+        <v>0.0100819714820314</v>
       </c>
       <c r="O108" t="n">
-        <v>0.051190785675201</v>
+        <v>0.0940962608088782</v>
       </c>
       <c r="P108" t="s">
         <v>23</v>
@@ -5926,28 +5926,28 @@
         <v>43</v>
       </c>
       <c r="H109" t="n">
-        <v>6301</v>
+        <v>6482</v>
       </c>
       <c r="I109" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J109" t="n">
         <v>1998</v>
       </c>
       <c r="K109" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L109" t="b">
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>0.132184335834842</v>
+        <v>0.12929124115708</v>
       </c>
       <c r="N109" t="n">
-        <v>-0.00512498893664424</v>
+        <v>-0.00491355372019899</v>
       </c>
       <c r="O109" t="n">
-        <v>0.118498663142494</v>
+        <v>0.117004457167443</v>
       </c>
       <c r="P109" t="s">
         <v>23</v>
@@ -5976,28 +5976,28 @@
         <v>43</v>
       </c>
       <c r="H110" t="n">
-        <v>6285</v>
+        <v>6466</v>
       </c>
       <c r="I110" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J110" t="n">
         <v>1998</v>
       </c>
       <c r="K110" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L110" t="b">
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>15.8420696008404</v>
+        <v>15.4835024422216</v>
       </c>
       <c r="N110" t="n">
-        <v>-0.572226245026019</v>
+        <v>-0.545921328667188</v>
       </c>
       <c r="O110" t="n">
-        <v>0.0419864765441194</v>
+        <v>0.0432676395822031</v>
       </c>
       <c r="P110" t="s">
         <v>21</v>
@@ -6026,28 +6026,28 @@
         <v>43</v>
       </c>
       <c r="H111" t="n">
-        <v>6284</v>
+        <v>6465</v>
       </c>
       <c r="I111" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J111" t="n">
         <v>1998</v>
       </c>
       <c r="K111" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L111" t="b">
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>5.71565828377176</v>
+        <v>5.64851568155711</v>
       </c>
       <c r="N111" t="n">
-        <v>-0.196830926179655</v>
+        <v>-0.191974164438094</v>
       </c>
       <c r="O111" t="n">
-        <v>0.0148174763903749</v>
+        <v>0.0143482789438823</v>
       </c>
       <c r="P111" t="s">
         <v>21</v>
@@ -6076,28 +6076,28 @@
         <v>43</v>
       </c>
       <c r="H112" t="n">
-        <v>6815</v>
+        <v>6996</v>
       </c>
       <c r="I112" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J112" t="n">
         <v>1994</v>
       </c>
       <c r="K112" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L112" t="b">
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>52.3021115018918</v>
+        <v>51.2627695986105</v>
       </c>
       <c r="N112" t="n">
-        <v>-1.69151017812222</v>
+        <v>-1.6030053316693</v>
       </c>
       <c r="O112" t="n">
-        <v>0.0000000000000000000403137535049784</v>
+        <v>0.000000000000000000379808349181876</v>
       </c>
       <c r="P112" t="s">
         <v>21</v>
@@ -6206,31 +6206,31 @@
         <v>90</v>
       </c>
       <c r="H115" t="n">
-        <v>5685</v>
+        <v>6524</v>
       </c>
       <c r="I115" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J115" t="n">
         <v>1997</v>
       </c>
       <c r="K115" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L115" t="b">
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>9.29711141295766</v>
+        <v>8.40851784757194</v>
       </c>
       <c r="N115" t="n">
-        <v>-0.212868634808103</v>
+        <v>-0.148105183067089</v>
       </c>
       <c r="O115" t="n">
-        <v>0.00405168065247469</v>
+        <v>0.0974653898461681</v>
       </c>
       <c r="P115" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="116">
@@ -6256,31 +6256,31 @@
         <v>90</v>
       </c>
       <c r="H116" t="n">
-        <v>17103</v>
+        <v>19627</v>
       </c>
       <c r="I116" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J116" t="n">
         <v>1997</v>
       </c>
       <c r="K116" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L116" t="b">
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>1.70960213659336</v>
+        <v>1.6572921266286</v>
       </c>
       <c r="N116" t="n">
-        <v>-0.0289760355144765</v>
+        <v>-0.0265739062221367</v>
       </c>
       <c r="O116" t="n">
-        <v>0.0448824668545934</v>
+        <v>0.0562321879273083</v>
       </c>
       <c r="P116" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="117">
@@ -6306,16 +6306,16 @@
         <v>43</v>
       </c>
       <c r="H117" t="n">
-        <v>5708</v>
+        <v>6550</v>
       </c>
       <c r="I117" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J117" t="n">
         <v>1997</v>
       </c>
       <c r="K117" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L117" t="b">
         <v>1</v>
@@ -6350,28 +6350,28 @@
         <v>90</v>
       </c>
       <c r="H118" t="n">
-        <v>5698</v>
+        <v>6539</v>
       </c>
       <c r="I118" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J118" t="n">
         <v>1997</v>
       </c>
       <c r="K118" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L118" t="b">
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>17.0121024167292</v>
+        <v>16.2742009880887</v>
       </c>
       <c r="N118" t="n">
-        <v>-0.601666634628676</v>
+        <v>-0.560687169914942</v>
       </c>
       <c r="O118" t="n">
-        <v>0.000235157766530186</v>
+        <v>0.000440849275728977</v>
       </c>
       <c r="P118" t="s">
         <v>21</v>
@@ -6400,28 +6400,28 @@
         <v>90</v>
       </c>
       <c r="H119" t="n">
-        <v>5704</v>
+        <v>6546</v>
       </c>
       <c r="I119" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J119" t="n">
         <v>1997</v>
       </c>
       <c r="K119" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L119" t="b">
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>3.15078674404518</v>
+        <v>3.15642486026929</v>
       </c>
       <c r="N119" t="n">
-        <v>-0.0902733509283717</v>
+        <v>-0.0916237650356675</v>
       </c>
       <c r="O119" t="n">
-        <v>0.0629403377939821</v>
+        <v>0.0657011378680577</v>
       </c>
       <c r="P119" t="s">
         <v>23</v>
@@ -6450,28 +6450,28 @@
         <v>43</v>
       </c>
       <c r="H120" t="n">
-        <v>6231</v>
+        <v>7130</v>
       </c>
       <c r="I120" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J120" t="n">
         <v>1994</v>
       </c>
       <c r="K120" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L120" t="b">
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>33.1820675646515</v>
+        <v>30.0048298261178</v>
       </c>
       <c r="N120" t="n">
-        <v>-0.932472937767339</v>
+        <v>-0.774268496697167</v>
       </c>
       <c r="O120" t="n">
-        <v>0.000000000909265706738429</v>
+        <v>0.0000155735740157106</v>
       </c>
       <c r="P120" t="s">
         <v>21</v>
@@ -6555,13 +6555,13 @@
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>-1.17225767267301</v>
+        <v>-1.17179361635508</v>
       </c>
       <c r="N122" t="n">
-        <v>0.471000050425961</v>
+        <v>0.470981420692621</v>
       </c>
       <c r="O122" t="n">
-        <v>0.260006328269154</v>
+        <v>0.26003557319771</v>
       </c>
       <c r="P122" t="s">
         <v>23</v>
@@ -6605,13 +6605,13 @@
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>22.5309932608729</v>
+        <v>22.5309932775823</v>
       </c>
       <c r="N123" t="n">
-        <v>-0.54427506679597</v>
+        <v>-0.544275067565711</v>
       </c>
       <c r="O123" t="n">
-        <v>0.0227362276911171</v>
+        <v>0.0227362274662352</v>
       </c>
       <c r="P123" t="s">
         <v>21</v>
@@ -6655,13 +6655,13 @@
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>28.6856935920826</v>
+        <v>28.6857141770335</v>
       </c>
       <c r="N124" t="n">
-        <v>0.18877470936749</v>
+        <v>0.188773694286756</v>
       </c>
       <c r="O124" t="n">
-        <v>0.598317226968351</v>
+        <v>0.598320943514704</v>
       </c>
       <c r="P124" t="s">
         <v>23</v>
@@ -6749,13 +6749,13 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>6.7838230486559</v>
+        <v>6.78381819418626</v>
       </c>
       <c r="N126" t="n">
-        <v>-0.00866126850207299</v>
+        <v>-0.00866100704994314</v>
       </c>
       <c r="O126" t="n">
-        <v>0.962696671246064</v>
+        <v>0.962697808501246</v>
       </c>
       <c r="P126" t="s">
         <v>23</v>
@@ -6799,13 +6799,13 @@
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>4.31520743264204</v>
+        <v>4.31520743264218</v>
       </c>
       <c r="N127" t="n">
-        <v>0.303859009487904</v>
+        <v>0.303859009487899</v>
       </c>
       <c r="O127" t="n">
-        <v>0.453703957656639</v>
+        <v>0.453703957656648</v>
       </c>
       <c r="P127" t="s">
         <v>23</v>
@@ -6849,13 +6849,13 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>26.6419579439412</v>
+        <v>26.6419579439417</v>
       </c>
       <c r="N128" t="n">
-        <v>0.549443451096866</v>
+        <v>0.549443451096848</v>
       </c>
       <c r="O128" t="n">
-        <v>0.246787900026726</v>
+        <v>0.246787900026742</v>
       </c>
       <c r="P128" t="s">
         <v>23</v>
@@ -6884,16 +6884,16 @@
         <v>96</v>
       </c>
       <c r="H129" t="n">
-        <v>102</v>
+        <v>164</v>
       </c>
       <c r="I129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J129" t="n">
         <v>2024</v>
       </c>
       <c r="K129" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L129" t="b">
         <v>0</v>
@@ -6928,16 +6928,16 @@
         <v>96</v>
       </c>
       <c r="H130" t="n">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="I130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J130" t="n">
         <v>2024</v>
       </c>
       <c r="K130" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L130" t="b">
         <v>0</v>
@@ -6972,16 +6972,16 @@
         <v>96</v>
       </c>
       <c r="H131" t="n">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="I131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J131" t="n">
         <v>2024</v>
       </c>
       <c r="K131" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L131" t="b">
         <v>0</v>
@@ -7016,16 +7016,16 @@
         <v>96</v>
       </c>
       <c r="H132" t="n">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="I132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J132" t="n">
         <v>2024</v>
       </c>
       <c r="K132" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L132" t="b">
         <v>0</v>
@@ -7060,16 +7060,16 @@
         <v>96</v>
       </c>
       <c r="H133" t="n">
-        <v>236</v>
+        <v>386</v>
       </c>
       <c r="I133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J133" t="n">
         <v>2024</v>
       </c>
       <c r="K133" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L133" t="b">
         <v>0</v>
@@ -7104,16 +7104,16 @@
         <v>96</v>
       </c>
       <c r="H134" t="n">
-        <v>239</v>
+        <v>395</v>
       </c>
       <c r="I134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J134" t="n">
         <v>2024</v>
       </c>
       <c r="K134" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L134" t="b">
         <v>0</v>
@@ -7188,28 +7188,28 @@
         <v>99</v>
       </c>
       <c r="H136" t="n">
-        <v>787</v>
+        <v>825</v>
       </c>
       <c r="I136" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J136" t="n">
         <v>1999</v>
       </c>
       <c r="K136" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L136" t="b">
         <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>20.2590676274871</v>
+        <v>20.19534170184</v>
       </c>
       <c r="N136" t="n">
-        <v>-0.585651209477301</v>
+        <v>-0.580645182704668</v>
       </c>
       <c r="O136" t="n">
-        <v>0.000000000612876949887699</v>
+        <v>0.00000000000192769985029779</v>
       </c>
       <c r="P136" t="s">
         <v>21</v>
@@ -7238,28 +7238,28 @@
         <v>99</v>
       </c>
       <c r="H137" t="n">
-        <v>2379</v>
+        <v>2493</v>
       </c>
       <c r="I137" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J137" t="n">
         <v>1999</v>
       </c>
       <c r="K137" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L137" t="b">
         <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>1.73766058924645</v>
+        <v>1.71485988102386</v>
       </c>
       <c r="N137" t="n">
-        <v>-0.0414814042766983</v>
+        <v>-0.0397867824814792</v>
       </c>
       <c r="O137" t="n">
-        <v>0.00089542577025922</v>
+        <v>0.00052505111566868</v>
       </c>
       <c r="P137" t="s">
         <v>21</v>
@@ -7288,16 +7288,16 @@
         <v>43</v>
       </c>
       <c r="H138" t="n">
-        <v>794</v>
+        <v>832</v>
       </c>
       <c r="I138" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J138" t="n">
         <v>1999</v>
       </c>
       <c r="K138" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L138" t="b">
         <v>1</v>
@@ -7332,28 +7332,28 @@
         <v>99</v>
       </c>
       <c r="H139" t="n">
-        <v>794</v>
+        <v>832</v>
       </c>
       <c r="I139" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J139" t="n">
         <v>1999</v>
       </c>
       <c r="K139" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L139" t="b">
         <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>2.54661101365288</v>
+        <v>2.53951567181357</v>
       </c>
       <c r="N139" t="n">
-        <v>-0.0783803494115895</v>
+        <v>-0.0779050940846131</v>
       </c>
       <c r="O139" t="n">
-        <v>0.341034362519376</v>
+        <v>0.336338821176729</v>
       </c>
       <c r="P139" t="s">
         <v>23</v>
@@ -7382,28 +7382,28 @@
         <v>99</v>
       </c>
       <c r="H140" t="n">
-        <v>794</v>
+        <v>832</v>
       </c>
       <c r="I140" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J140" t="n">
         <v>1999</v>
       </c>
       <c r="K140" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L140" t="b">
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>0.098278249125969</v>
+        <v>0.0937987919740479</v>
       </c>
       <c r="N140" t="n">
-        <v>-0.00433663859300799</v>
+        <v>-0.00400475632155672</v>
       </c>
       <c r="O140" t="n">
-        <v>0.300757978603717</v>
+        <v>0.30074758659337</v>
       </c>
       <c r="P140" t="s">
         <v>23</v>
@@ -7432,28 +7432,28 @@
         <v>43</v>
       </c>
       <c r="H141" t="n">
-        <v>801</v>
+        <v>839</v>
       </c>
       <c r="I141" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J141" t="n">
         <v>1999</v>
       </c>
       <c r="K141" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L141" t="b">
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>27.7613215210498</v>
+        <v>27.6619615739441</v>
       </c>
       <c r="N141" t="n">
-        <v>-0.805416122805826</v>
+        <v>-0.798741167412668</v>
       </c>
       <c r="O141" t="n">
-        <v>0.000000000000000111937158369317</v>
+        <v>0.00000000000000000216796064709784</v>
       </c>
       <c r="P141" t="s">
         <v>21</v>
@@ -7581,13 +7581,13 @@
         <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>-5.87122204063504</v>
+        <v>-5.87122250558736</v>
       </c>
       <c r="N144" t="n">
-        <v>1.10079105954384</v>
+        <v>1.10079108471336</v>
       </c>
       <c r="O144" t="n">
-        <v>0.104749045024336</v>
+        <v>0.10474902248809</v>
       </c>
       <c r="P144" t="s">
         <v>23</v>
@@ -7631,13 +7631,13 @@
         <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>19.6311429839962</v>
+        <v>19.6311429839964</v>
       </c>
       <c r="N145" t="n">
-        <v>0.076522796846791</v>
+        <v>0.076522796846781</v>
       </c>
       <c r="O145" t="n">
-        <v>0.880505716452414</v>
+        <v>0.88050571645243</v>
       </c>
       <c r="P145" t="s">
         <v>23</v>
@@ -7725,13 +7725,13 @@
         <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>2.64228139828149</v>
+        <v>2.64228139022739</v>
       </c>
       <c r="N147" t="n">
-        <v>0.068164801565837</v>
+        <v>0.0681648019802267</v>
       </c>
       <c r="O147" t="n">
-        <v>0.780887509020257</v>
+        <v>0.780887507542741</v>
       </c>
       <c r="P147" t="s">
         <v>23</v>
@@ -7903,13 +7903,13 @@
         <v>1</v>
       </c>
       <c r="M151" t="n">
-        <v>26.6035655592804</v>
+        <v>26.6035655592142</v>
       </c>
       <c r="N151" t="n">
-        <v>-0.476510204710198</v>
+        <v>-0.476510204712189</v>
       </c>
       <c r="O151" t="n">
-        <v>0.158331973909321</v>
+        <v>0.158331973904867</v>
       </c>
       <c r="P151" t="s">
         <v>23</v>
@@ -7953,13 +7953,13 @@
         <v>1</v>
       </c>
       <c r="M152" t="n">
-        <v>33.4466492799093</v>
+        <v>33.4466492799094</v>
       </c>
       <c r="N152" t="n">
-        <v>-0.526271498290103</v>
+        <v>-0.526271498290106</v>
       </c>
       <c r="O152" t="n">
-        <v>0.134250711812301</v>
+        <v>0.134250711812299</v>
       </c>
       <c r="P152" t="s">
         <v>23</v>
@@ -8072,31 +8072,31 @@
         <v>43</v>
       </c>
       <c r="H155" t="n">
-        <v>651</v>
+        <v>685</v>
       </c>
       <c r="I155" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J155" t="n">
         <v>2009</v>
       </c>
       <c r="K155" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L155" t="b">
         <v>1</v>
       </c>
       <c r="M155" t="n">
-        <v>23.024903019627</v>
+        <v>3.70618582273872</v>
       </c>
       <c r="N155" t="n">
-        <v>-0.773531254197164</v>
+        <v>0.206821431032827</v>
       </c>
       <c r="O155" t="n">
-        <v>0.0202146218231972</v>
+        <v>0.238304224446081</v>
       </c>
       <c r="P155" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="156">
@@ -8122,28 +8122,28 @@
         <v>43</v>
       </c>
       <c r="H156" t="n">
-        <v>1953</v>
+        <v>2055</v>
       </c>
       <c r="I156" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J156" t="n">
         <v>2009</v>
       </c>
       <c r="K156" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L156" t="b">
         <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>-0.0711150985564275</v>
+        <v>-0.053610494193918</v>
       </c>
       <c r="N156" t="n">
-        <v>0.00372022338125094</v>
+        <v>0.00283405115336671</v>
       </c>
       <c r="O156" t="n">
-        <v>0.167941461820667</v>
+        <v>0.161567647341493</v>
       </c>
       <c r="P156" t="s">
         <v>23</v>
@@ -8172,16 +8172,16 @@
         <v>43</v>
       </c>
       <c r="H157" t="n">
-        <v>651</v>
+        <v>685</v>
       </c>
       <c r="I157" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J157" t="n">
         <v>2009</v>
       </c>
       <c r="K157" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L157" t="b">
         <v>1</v>
@@ -8216,16 +8216,16 @@
         <v>43</v>
       </c>
       <c r="H158" t="n">
-        <v>651</v>
+        <v>685</v>
       </c>
       <c r="I158" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J158" t="n">
         <v>2009</v>
       </c>
       <c r="K158" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L158" t="b">
         <v>1</v>
@@ -8260,16 +8260,16 @@
         <v>43</v>
       </c>
       <c r="H159" t="n">
-        <v>651</v>
+        <v>685</v>
       </c>
       <c r="I159" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J159" t="n">
         <v>2009</v>
       </c>
       <c r="K159" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L159" t="b">
         <v>1</v>
@@ -8304,31 +8304,31 @@
         <v>43</v>
       </c>
       <c r="H160" t="n">
-        <v>651</v>
+        <v>685</v>
       </c>
       <c r="I160" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J160" t="n">
         <v>2009</v>
       </c>
       <c r="K160" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L160" t="b">
         <v>1</v>
       </c>
       <c r="M160" t="n">
-        <v>22.9814232107145</v>
+        <v>3.67438898821875</v>
       </c>
       <c r="N160" t="n">
-        <v>-0.771190976570732</v>
+        <v>0.208564609640469</v>
       </c>
       <c r="O160" t="n">
-        <v>0.0197959930482142</v>
+        <v>0.236718465491046</v>
       </c>
       <c r="P160" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="161">
@@ -8394,31 +8394,31 @@
         <v>52</v>
       </c>
       <c r="H162" t="n">
-        <v>3587</v>
+        <v>4768</v>
       </c>
       <c r="I162" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J162" t="n">
         <v>1997</v>
       </c>
       <c r="K162" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L162" t="b">
         <v>1</v>
       </c>
       <c r="M162" t="n">
-        <v>19.1499706613022</v>
+        <v>18.460796557458</v>
       </c>
       <c r="N162" t="n">
-        <v>-0.316165778379042</v>
+        <v>-0.319419682122757</v>
       </c>
       <c r="O162" t="n">
-        <v>0.0160054813216538</v>
+        <v>0.431503009244388</v>
       </c>
       <c r="P162" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="163">
@@ -8444,31 +8444,31 @@
         <v>52</v>
       </c>
       <c r="H163" t="n">
-        <v>1902</v>
+        <v>2561</v>
       </c>
       <c r="I163" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J163" t="n">
         <v>1997</v>
       </c>
       <c r="K163" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L163" t="b">
         <v>1</v>
       </c>
       <c r="M163" t="n">
-        <v>10.2242875322034</v>
+        <v>14.4442975501166</v>
       </c>
       <c r="N163" t="n">
-        <v>-0.0105453906843651</v>
+        <v>-0.166055290313739</v>
       </c>
       <c r="O163" t="n">
-        <v>0.870075455176696</v>
+        <v>0.038264187108685</v>
       </c>
       <c r="P163" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="164">
@@ -8494,28 +8494,28 @@
         <v>52</v>
       </c>
       <c r="H164" t="n">
-        <v>540</v>
+        <v>678</v>
       </c>
       <c r="I164" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J164" t="n">
         <v>1997</v>
       </c>
       <c r="K164" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L164" t="b">
         <v>1</v>
       </c>
       <c r="M164" t="n">
-        <v>8.34583588573481</v>
+        <v>8.7879312105827</v>
       </c>
       <c r="N164" t="n">
-        <v>0.122351783460449</v>
+        <v>0.0927755833398184</v>
       </c>
       <c r="O164" t="n">
-        <v>0.294839445823322</v>
+        <v>0.38946976613155</v>
       </c>
       <c r="P164" t="s">
         <v>23</v>
@@ -8544,16 +8544,16 @@
         <v>52</v>
       </c>
       <c r="H165" t="n">
-        <v>87</v>
+        <v>153</v>
       </c>
       <c r="I165" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J165" t="n">
         <v>1998</v>
       </c>
       <c r="K165" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L165" t="b">
         <v>1</v>
@@ -8588,28 +8588,28 @@
         <v>52</v>
       </c>
       <c r="H166" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I166" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J166" t="n">
         <v>1997</v>
       </c>
       <c r="K166" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L166" t="b">
         <v>1</v>
       </c>
       <c r="M166" t="n">
-        <v>-9.22516513824099</v>
+        <v>8.39152299448192</v>
       </c>
       <c r="N166" t="n">
-        <v>0.704825482924538</v>
+        <v>0.0442851066408185</v>
       </c>
       <c r="O166" t="n">
-        <v>0.746731107226386</v>
+        <v>0.969004325922695</v>
       </c>
       <c r="P166" t="s">
         <v>23</v>
@@ -8638,28 +8638,28 @@
         <v>52</v>
       </c>
       <c r="H167" t="n">
-        <v>2334</v>
+        <v>2664</v>
       </c>
       <c r="I167" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J167" t="n">
         <v>1997</v>
       </c>
       <c r="K167" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L167" t="b">
         <v>1</v>
       </c>
       <c r="M167" t="n">
-        <v>44.0732080683524</v>
+        <v>57.5162188256729</v>
       </c>
       <c r="N167" t="n">
-        <v>-1.05225252508132</v>
+        <v>-1.51153810685005</v>
       </c>
       <c r="O167" t="n">
-        <v>0.0095643740255073</v>
+        <v>0.00489236123899467</v>
       </c>
       <c r="P167" t="s">
         <v>21</v>
@@ -8688,28 +8688,28 @@
         <v>52</v>
       </c>
       <c r="H168" t="n">
-        <v>7480</v>
+        <v>9473</v>
       </c>
       <c r="I168" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J168" t="n">
         <v>1997</v>
       </c>
       <c r="K168" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L168" t="b">
         <v>1</v>
       </c>
       <c r="M168" t="n">
-        <v>108.013733201528</v>
+        <v>113.703116368091</v>
       </c>
       <c r="N168" t="n">
-        <v>-2.56973970312599</v>
+        <v>-2.76905746455337</v>
       </c>
       <c r="O168" t="n">
-        <v>0.00000000008376340262188</v>
+        <v>0.00000000000000480637576416575</v>
       </c>
       <c r="P168" t="s">
         <v>21</v>
@@ -8753,13 +8753,13 @@
         <v>1</v>
       </c>
       <c r="M169" t="n">
-        <v>18.4858461622144</v>
+        <v>18.4858461593842</v>
       </c>
       <c r="N169" t="n">
-        <v>-0.57107692313935</v>
+        <v>-0.57107692311824</v>
       </c>
       <c r="O169" t="n">
-        <v>0.0671357481774192</v>
+        <v>0.0671357480917357</v>
       </c>
       <c r="P169" t="s">
         <v>23</v>
@@ -8803,13 +8803,13 @@
         <v>1</v>
       </c>
       <c r="M170" t="n">
-        <v>12.12575641794</v>
+        <v>12.1257564173751</v>
       </c>
       <c r="N170" t="n">
-        <v>-0.0149842466920076</v>
+        <v>-0.0149842466671144</v>
       </c>
       <c r="O170" t="n">
-        <v>0.931856627545226</v>
+        <v>0.931856627659933</v>
       </c>
       <c r="P170" t="s">
         <v>23</v>
@@ -8853,13 +8853,13 @@
         <v>1</v>
       </c>
       <c r="M171" t="n">
-        <v>15.4432607125131</v>
+        <v>15.443260712513</v>
       </c>
       <c r="N171" t="n">
-        <v>0.430165149041331</v>
+        <v>0.430165149041334</v>
       </c>
       <c r="O171" t="n">
-        <v>0.219275347947408</v>
+        <v>0.219275347947406</v>
       </c>
       <c r="P171" t="s">
         <v>23</v>
@@ -9075,13 +9075,13 @@
         <v>1</v>
       </c>
       <c r="M176" t="n">
-        <v>20.588524859885</v>
+        <v>20.5885250687694</v>
       </c>
       <c r="N176" t="n">
-        <v>0.366270848891099</v>
+        <v>0.366270859299474</v>
       </c>
       <c r="O176" t="n">
-        <v>0.283296634236128</v>
+        <v>0.283296617342563</v>
       </c>
       <c r="P176" t="s">
         <v>23</v>
@@ -9125,13 +9125,13 @@
         <v>1</v>
       </c>
       <c r="M177" t="n">
-        <v>8.90779448258092</v>
+        <v>8.90778952009263</v>
       </c>
       <c r="N177" t="n">
-        <v>0.106397105863102</v>
+        <v>0.10639731584783</v>
       </c>
       <c r="O177" t="n">
-        <v>0.459517983463199</v>
+        <v>0.459517067678269</v>
       </c>
       <c r="P177" t="s">
         <v>23</v>
@@ -9175,13 +9175,13 @@
         <v>1</v>
       </c>
       <c r="M178" t="n">
-        <v>19.2737433657372</v>
+        <v>19.2737433657373</v>
       </c>
       <c r="N178" t="n">
-        <v>0.298326138204907</v>
+        <v>0.298326138204902</v>
       </c>
       <c r="O178" t="n">
-        <v>0.328421016947517</v>
+        <v>0.328421016947526</v>
       </c>
       <c r="P178" t="s">
         <v>23</v>
@@ -9225,13 +9225,13 @@
         <v>1</v>
       </c>
       <c r="M179" t="n">
-        <v>1.3465451752785</v>
+        <v>1.34638775200742</v>
       </c>
       <c r="N179" t="n">
-        <v>-0.0087296070060331</v>
+        <v>-0.00872276598730886</v>
       </c>
       <c r="O179" t="n">
-        <v>0.956323793332353</v>
+        <v>0.956357577347309</v>
       </c>
       <c r="P179" t="s">
         <v>23</v>
@@ -9260,28 +9260,28 @@
         <v>110</v>
       </c>
       <c r="H180" t="n">
-        <v>1022</v>
+        <v>1086</v>
       </c>
       <c r="I180" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J180" t="n">
         <v>2012</v>
       </c>
       <c r="K180" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L180" t="b">
         <v>1</v>
       </c>
       <c r="M180" t="n">
-        <v>-49.5920796655998</v>
+        <v>-49.761290412474</v>
       </c>
       <c r="N180" t="n">
-        <v>2.66186726637865</v>
+        <v>2.67373427225315</v>
       </c>
       <c r="O180" t="n">
-        <v>0.00000239090453057941</v>
+        <v>0.00000318809996200969</v>
       </c>
       <c r="P180" t="s">
         <v>50</v>
@@ -9310,28 +9310,28 @@
         <v>110</v>
       </c>
       <c r="H181" t="n">
-        <v>7113</v>
+        <v>7125</v>
       </c>
       <c r="I181" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J181" t="n">
         <v>1998</v>
       </c>
       <c r="K181" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L181" t="b">
         <v>1</v>
       </c>
       <c r="M181" t="n">
-        <v>23.4170769887968</v>
+        <v>23.582597929326</v>
       </c>
       <c r="N181" t="n">
-        <v>0.214241051756911</v>
+        <v>0.205904459580598</v>
       </c>
       <c r="O181" t="n">
-        <v>0.129962039390411</v>
+        <v>0.145713233948874</v>
       </c>
       <c r="P181" t="s">
         <v>23</v>
@@ -9404,16 +9404,16 @@
         <v>112</v>
       </c>
       <c r="H183" t="n">
-        <v>3935</v>
+        <v>3961</v>
       </c>
       <c r="I183" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J183" t="n">
         <v>1998</v>
       </c>
       <c r="K183" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L183" t="b">
         <v>1</v>
@@ -9463,13 +9463,13 @@
         <v>1</v>
       </c>
       <c r="M184" t="n">
-        <v>-20.7185464749576</v>
+        <v>-20.7179114764626</v>
       </c>
       <c r="N184" t="n">
-        <v>1.16038099050171</v>
+        <v>1.16034761795276</v>
       </c>
       <c r="O184" t="n">
-        <v>0.368350598684456</v>
+        <v>0.368359158553326</v>
       </c>
       <c r="P184" t="s">
         <v>23</v>
@@ -9498,28 +9498,28 @@
         <v>110</v>
       </c>
       <c r="H185" t="n">
-        <v>4590</v>
+        <v>4621</v>
       </c>
       <c r="I185" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J185" t="n">
         <v>1998</v>
       </c>
       <c r="K185" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L185" t="b">
         <v>1</v>
       </c>
       <c r="M185" t="n">
-        <v>19.3045368009947</v>
+        <v>19.9314858536334</v>
       </c>
       <c r="N185" t="n">
-        <v>0.357128673128779</v>
+        <v>0.326801795878895</v>
       </c>
       <c r="O185" t="n">
-        <v>0.078279096280564</v>
+        <v>0.114315322088279</v>
       </c>
       <c r="P185" t="s">
         <v>23</v>
@@ -9548,28 +9548,28 @@
         <v>110</v>
       </c>
       <c r="H186" t="n">
-        <v>4025</v>
+        <v>4071</v>
       </c>
       <c r="I186" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J186" t="n">
         <v>1998</v>
       </c>
       <c r="K186" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L186" t="b">
         <v>1</v>
       </c>
       <c r="M186" t="n">
-        <v>41.8688979916643</v>
+        <v>42.2151159553225</v>
       </c>
       <c r="N186" t="n">
-        <v>-0.195129154789458</v>
+        <v>-0.212197716071814</v>
       </c>
       <c r="O186" t="n">
-        <v>0.232466977105312</v>
+        <v>0.196587032046407</v>
       </c>
       <c r="P186" t="s">
         <v>23</v>
@@ -9613,13 +9613,13 @@
         <v>1</v>
       </c>
       <c r="M187" t="n">
-        <v>35.6054197123911</v>
+        <v>35.6054215170507</v>
       </c>
       <c r="N187" t="n">
-        <v>0.419915563194657</v>
+        <v>0.419915469481326</v>
       </c>
       <c r="O187" t="n">
-        <v>0.574127622659356</v>
+        <v>0.574127834383349</v>
       </c>
       <c r="P187" t="s">
         <v>23</v>
@@ -9663,13 +9663,13 @@
         <v>1</v>
       </c>
       <c r="M188" t="n">
-        <v>-1.6366623620019</v>
+        <v>-1.63664205039697</v>
       </c>
       <c r="N188" t="n">
-        <v>0.109313418689803</v>
+        <v>0.109312346931521</v>
       </c>
       <c r="O188" t="n">
-        <v>0.658163700860897</v>
+        <v>0.658167263124645</v>
       </c>
       <c r="P188" t="s">
         <v>23</v>
@@ -9713,13 +9713,13 @@
         <v>1</v>
       </c>
       <c r="M189" t="n">
-        <v>33.628723773395</v>
+        <v>33.6286656016465</v>
       </c>
       <c r="N189" t="n">
-        <v>-1.70910436858776</v>
+        <v>-1.70909816755082</v>
       </c>
       <c r="O189" t="n">
-        <v>0.254590618263364</v>
+        <v>0.254605077074609</v>
       </c>
       <c r="P189" t="s">
         <v>23</v>
@@ -9763,13 +9763,13 @@
         <v>1</v>
       </c>
       <c r="M190" t="n">
-        <v>-0.44456113092958</v>
+        <v>-0.444567344856501</v>
       </c>
       <c r="N190" t="n">
-        <v>0.0784241882663684</v>
+        <v>0.0784251979579704</v>
       </c>
       <c r="O190" t="n">
-        <v>0.356281826344633</v>
+        <v>0.356262072866792</v>
       </c>
       <c r="P190" t="s">
         <v>23</v>
@@ -9813,13 +9813,13 @@
         <v>1</v>
       </c>
       <c r="M191" t="n">
-        <v>3.53048070193436</v>
+        <v>3.53048514537169</v>
       </c>
       <c r="N191" t="n">
-        <v>-0.232326898201871</v>
+        <v>-0.23232673623941</v>
       </c>
       <c r="O191" t="n">
-        <v>0.44371379125858</v>
+        <v>0.443711658627369</v>
       </c>
       <c r="P191" t="s">
         <v>23</v>
@@ -9863,13 +9863,13 @@
         <v>1</v>
       </c>
       <c r="M192" t="n">
-        <v>16.1048036953012</v>
+        <v>16.1047804901159</v>
       </c>
       <c r="N192" t="n">
-        <v>-1.13438778746813</v>
+        <v>-1.13438365908922</v>
       </c>
       <c r="O192" t="n">
-        <v>0.40008285596946</v>
+        <v>0.400085578534954</v>
       </c>
       <c r="P192" t="s">
         <v>23</v>
@@ -9913,13 +9913,13 @@
         <v>1</v>
       </c>
       <c r="M193" t="n">
-        <v>36.9900137332185</v>
+        <v>36.9900159752838</v>
       </c>
       <c r="N193" t="n">
-        <v>-3.13814583526341</v>
+        <v>-3.13814594958305</v>
       </c>
       <c r="O193" t="n">
-        <v>0.0666608562339737</v>
+        <v>0.0666593236207905</v>
       </c>
       <c r="P193" t="s">
         <v>23</v>
@@ -9963,13 +9963,13 @@
         <v>1</v>
       </c>
       <c r="M194" t="n">
-        <v>68.369484917475</v>
+        <v>68.3692745038019</v>
       </c>
       <c r="N194" t="n">
-        <v>-4.52097026315786</v>
+        <v>-4.52094347983225</v>
       </c>
       <c r="O194" t="n">
-        <v>0.0166182622893285</v>
+        <v>0.0166190751416014</v>
       </c>
       <c r="P194" t="s">
         <v>21</v>
@@ -10013,13 +10013,13 @@
         <v>1</v>
       </c>
       <c r="M195" t="n">
-        <v>33.6286514164965</v>
+        <v>33.6286656016465</v>
       </c>
       <c r="N195" t="n">
-        <v>-1.70909712972767</v>
+        <v>-1.70909816755082</v>
       </c>
       <c r="O195" t="n">
-        <v>0.254620455536205</v>
+        <v>0.254605077074609</v>
       </c>
       <c r="P195" t="s">
         <v>23</v>
@@ -10063,13 +10063,13 @@
         <v>1</v>
       </c>
       <c r="M196" t="n">
-        <v>-0.444559760659897</v>
+        <v>-0.444567344856501</v>
       </c>
       <c r="N196" t="n">
-        <v>0.0784239357792856</v>
+        <v>0.0784251979579704</v>
       </c>
       <c r="O196" t="n">
-        <v>0.356289780424534</v>
+        <v>0.356262072866792</v>
       </c>
       <c r="P196" t="s">
         <v>23</v>
@@ -10113,13 +10113,13 @@
         <v>1</v>
       </c>
       <c r="M197" t="n">
-        <v>3.53048964166756</v>
+        <v>3.53048514537169</v>
       </c>
       <c r="N197" t="n">
-        <v>-0.232327351261614</v>
+        <v>-0.23232673623941</v>
       </c>
       <c r="O197" t="n">
-        <v>0.443714818400394</v>
+        <v>0.443711658627369</v>
       </c>
       <c r="P197" t="s">
         <v>23</v>
@@ -10163,13 +10163,13 @@
         <v>1</v>
       </c>
       <c r="M198" t="n">
-        <v>16.104786187905</v>
+        <v>16.1047804901159</v>
       </c>
       <c r="N198" t="n">
-        <v>-1.13438480926907</v>
+        <v>-1.13438365908922</v>
       </c>
       <c r="O198" t="n">
-        <v>0.400089904762928</v>
+        <v>0.400085578534954</v>
       </c>
       <c r="P198" t="s">
         <v>23</v>
@@ -10213,13 +10213,13 @@
         <v>1</v>
       </c>
       <c r="M199" t="n">
-        <v>36.9899401290369</v>
+        <v>36.9900159752838</v>
       </c>
       <c r="N199" t="n">
-        <v>-3.13813606811501</v>
+        <v>-3.13814594958305</v>
       </c>
       <c r="O199" t="n">
-        <v>0.0666627263574941</v>
+        <v>0.0666593236207905</v>
       </c>
       <c r="P199" t="s">
         <v>23</v>
@@ -10263,13 +10263,13 @@
         <v>1</v>
       </c>
       <c r="M200" t="n">
-        <v>68.3694284976308</v>
+        <v>68.3692745038019</v>
       </c>
       <c r="N200" t="n">
-        <v>-4.52096298854313</v>
+        <v>-4.52094347983225</v>
       </c>
       <c r="O200" t="n">
-        <v>0.0166183943820369</v>
+        <v>0.0166190751416014</v>
       </c>
       <c r="P200" t="s">
         <v>21</v>
@@ -10313,13 +10313,13 @@
         <v>1</v>
       </c>
       <c r="M201" t="n">
-        <v>84.4240519069693</v>
+        <v>84.4240521172969</v>
       </c>
       <c r="N201" t="n">
-        <v>-2.62425690745865</v>
+        <v>-2.62425691537163</v>
       </c>
       <c r="O201" t="n">
-        <v>0.0740357829782734</v>
+        <v>0.0740357853759614</v>
       </c>
       <c r="P201" t="s">
         <v>23</v>
@@ -10363,13 +10363,13 @@
         <v>1</v>
       </c>
       <c r="M202" t="n">
-        <v>11.9869803982023</v>
+        <v>11.986980400469</v>
       </c>
       <c r="N202" t="n">
-        <v>0.27052871967714</v>
+        <v>0.27052871960507</v>
       </c>
       <c r="O202" t="n">
-        <v>0.485492239784015</v>
+        <v>0.485492239666146</v>
       </c>
       <c r="P202" t="s">
         <v>23</v>
@@ -10457,13 +10457,13 @@
         <v>1</v>
       </c>
       <c r="M204" t="n">
-        <v>4.17278690398094</v>
+        <v>4.17278654215605</v>
       </c>
       <c r="N204" t="n">
-        <v>-0.151389667982695</v>
+        <v>-0.15138953086087</v>
       </c>
       <c r="O204" t="n">
-        <v>0.819593974777737</v>
+        <v>0.819593916025816</v>
       </c>
       <c r="P204" t="s">
         <v>23</v>
@@ -10507,13 +10507,13 @@
         <v>1</v>
       </c>
       <c r="M205" t="n">
-        <v>27.0389698918424</v>
+        <v>27.0389687993447</v>
       </c>
       <c r="N205" t="n">
-        <v>1.06249137834728</v>
+        <v>1.06249142248844</v>
       </c>
       <c r="O205" t="n">
-        <v>0.131535963264703</v>
+        <v>0.131535964561105</v>
       </c>
       <c r="P205" t="s">
         <v>23</v>
@@ -10557,13 +10557,13 @@
         <v>1</v>
       </c>
       <c r="M206" t="n">
-        <v>88.1358699273268</v>
+        <v>88.1362868491369</v>
       </c>
       <c r="N206" t="n">
-        <v>-1.52267574045742</v>
+        <v>-1.52272482880892</v>
       </c>
       <c r="O206" t="n">
-        <v>0.15021973127204</v>
+        <v>0.150214626938448</v>
       </c>
       <c r="P206" t="s">
         <v>23</v>
@@ -10607,13 +10607,13 @@
         <v>1</v>
       </c>
       <c r="M207" t="n">
-        <v>9.61203743636063</v>
+        <v>9.61203742621614</v>
       </c>
       <c r="N207" t="n">
-        <v>0.0838012513185918</v>
+        <v>0.0838012516893737</v>
       </c>
       <c r="O207" t="n">
-        <v>0.831389754186489</v>
+        <v>0.831389753629501</v>
       </c>
       <c r="P207" t="s">
         <v>23</v>
@@ -10657,13 +10657,13 @@
         <v>1</v>
       </c>
       <c r="M208" t="n">
-        <v>48.4483227974256</v>
+        <v>48.4483227947062</v>
       </c>
       <c r="N208" t="n">
-        <v>-0.491452101443074</v>
+        <v>-0.491452101326007</v>
       </c>
       <c r="O208" t="n">
-        <v>0.503221346965114</v>
+        <v>0.503221347188028</v>
       </c>
       <c r="P208" t="s">
         <v>23</v>
@@ -10751,13 +10751,13 @@
         <v>1</v>
       </c>
       <c r="M210" t="n">
-        <v>54.1977529427332</v>
+        <v>54.1971703449698</v>
       </c>
       <c r="N210" t="n">
-        <v>-0.898615908276998</v>
+        <v>-0.898587802225779</v>
       </c>
       <c r="O210" t="n">
-        <v>0.25668244223902</v>
+        <v>0.256698903785388</v>
       </c>
       <c r="P210" t="s">
         <v>23</v>
@@ -10801,13 +10801,13 @@
         <v>1</v>
       </c>
       <c r="M211" t="n">
-        <v>62.380384729702</v>
+        <v>62.3803683883504</v>
       </c>
       <c r="N211" t="n">
-        <v>-0.142093645741606</v>
+        <v>-0.142093117878052</v>
       </c>
       <c r="O211" t="n">
-        <v>0.687476149885152</v>
+        <v>0.687476157247382</v>
       </c>
       <c r="P211" t="s">
         <v>23</v>
@@ -10836,28 +10836,28 @@
         <v>52</v>
       </c>
       <c r="H212" t="n">
-        <v>1200</v>
+        <v>1328</v>
       </c>
       <c r="I212" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J212" t="n">
         <v>1997</v>
       </c>
       <c r="K212" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L212" t="b">
         <v>1</v>
       </c>
       <c r="M212" t="n">
-        <v>17.6001377016579</v>
+        <v>18.4230481020772</v>
       </c>
       <c r="N212" t="n">
-        <v>-0.177242116605302</v>
+        <v>-0.224003186251882</v>
       </c>
       <c r="O212" t="n">
-        <v>0.214505464474497</v>
+        <v>0.103428972363119</v>
       </c>
       <c r="P212" t="s">
         <v>23</v>
@@ -10886,28 +10886,28 @@
         <v>52</v>
       </c>
       <c r="H213" t="n">
-        <v>1488</v>
+        <v>1631</v>
       </c>
       <c r="I213" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J213" t="n">
         <v>1997</v>
       </c>
       <c r="K213" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L213" t="b">
         <v>1</v>
       </c>
       <c r="M213" t="n">
-        <v>24.3152173700395</v>
+        <v>27.1359792559161</v>
       </c>
       <c r="N213" t="n">
-        <v>-0.107824398497227</v>
+        <v>-0.261424059195711</v>
       </c>
       <c r="O213" t="n">
-        <v>0.554386983760942</v>
+        <v>0.1437116811893</v>
       </c>
       <c r="P213" t="s">
         <v>23</v>
@@ -10936,31 +10936,31 @@
         <v>52</v>
       </c>
       <c r="H214" t="n">
-        <v>468</v>
+        <v>503</v>
       </c>
       <c r="I214" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J214" t="n">
         <v>1997</v>
       </c>
       <c r="K214" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L214" t="b">
         <v>1</v>
       </c>
       <c r="M214" t="n">
-        <v>63.8891206981744</v>
+        <v>75.1431686053921</v>
       </c>
       <c r="N214" t="n">
-        <v>-1.75638883870463</v>
+        <v>-2.16214489044141</v>
       </c>
       <c r="O214" t="n">
-        <v>0.0916263907051741</v>
+        <v>0.044702954339368</v>
       </c>
       <c r="P214" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="215">
@@ -10986,16 +10986,16 @@
         <v>52</v>
       </c>
       <c r="H215" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="I215" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J215" t="n">
         <v>1997</v>
       </c>
       <c r="K215" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="L215" t="b">
         <v>1</v>
@@ -11030,28 +11030,28 @@
         <v>52</v>
       </c>
       <c r="H216" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I216" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J216" t="n">
         <v>1997</v>
       </c>
       <c r="K216" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L216" t="b">
         <v>1</v>
       </c>
       <c r="M216" t="n">
-        <v>23.3867558483777</v>
+        <v>23.5414554090611</v>
       </c>
       <c r="N216" t="n">
-        <v>-0.134009146040018</v>
+        <v>-0.163019815792196</v>
       </c>
       <c r="O216" t="n">
-        <v>0.724458235015615</v>
+        <v>0.664093711204479</v>
       </c>
       <c r="P216" t="s">
         <v>23</v>
@@ -11080,28 +11080,28 @@
         <v>52</v>
       </c>
       <c r="H217" t="n">
-        <v>722</v>
+        <v>747</v>
       </c>
       <c r="I217" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J217" t="n">
         <v>1997</v>
       </c>
       <c r="K217" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L217" t="b">
         <v>1</v>
       </c>
       <c r="M217" t="n">
-        <v>17.2241548079113</v>
+        <v>18.494359011557</v>
       </c>
       <c r="N217" t="n">
-        <v>-0.0625766221763471</v>
+        <v>-0.134124424203036</v>
       </c>
       <c r="O217" t="n">
-        <v>0.744519670631815</v>
+        <v>0.511251330606643</v>
       </c>
       <c r="P217" t="s">
         <v>23</v>
@@ -11130,28 +11130,28 @@
         <v>52</v>
       </c>
       <c r="H218" t="n">
-        <v>3169</v>
+        <v>3260</v>
       </c>
       <c r="I218" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J218" t="n">
         <v>1997</v>
       </c>
       <c r="K218" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L218" t="b">
         <v>1</v>
       </c>
       <c r="M218" t="n">
-        <v>34.9835958039344</v>
+        <v>36.1626677265256</v>
       </c>
       <c r="N218" t="n">
-        <v>-0.111791462313524</v>
+        <v>-0.183596335695938</v>
       </c>
       <c r="O218" t="n">
-        <v>0.468477051061486</v>
+        <v>0.249088171024273</v>
       </c>
       <c r="P218" t="s">
         <v>23</v>
@@ -11239,13 +11239,13 @@
         <v>1</v>
       </c>
       <c r="M220" t="n">
-        <v>25.7351476699093</v>
+        <v>25.7351476699092</v>
       </c>
       <c r="N220" t="n">
-        <v>0.862848997722571</v>
+        <v>0.862848997722573</v>
       </c>
       <c r="O220" t="n">
-        <v>0.0041757479179363</v>
+        <v>0.00417574791793629</v>
       </c>
       <c r="P220" t="s">
         <v>50</v>
@@ -11380,10 +11380,10 @@
         <v>36.5374750333897</v>
       </c>
       <c r="N223" t="n">
-        <v>0.141924957308237</v>
+        <v>0.141924957308238</v>
       </c>
       <c r="O223" t="n">
-        <v>0.708114476390104</v>
+        <v>0.708114476390101</v>
       </c>
       <c r="P223" t="s">
         <v>23</v>
@@ -11427,13 +11427,13 @@
         <v>1</v>
       </c>
       <c r="M224" t="n">
-        <v>34.4313177493422</v>
+        <v>34.4313177493427</v>
       </c>
       <c r="N224" t="n">
-        <v>0.22966300140264</v>
+        <v>0.229663001402628</v>
       </c>
       <c r="O224" t="n">
-        <v>0.446908276330284</v>
+        <v>0.446908276330308</v>
       </c>
       <c r="P224" t="s">
         <v>23</v>

--- a/SAV/output/website/SAV_BBpct_LMEresults_All.xlsx
+++ b/SAV/output/website/SAV_BBpct_LMEresults_All.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="128">
   <si>
     <t xml:space="preserve">AreaID</t>
   </si>
@@ -59,7 +59,10 @@
     <t xml:space="preserve">p</t>
   </si>
   <si>
-    <t xml:space="preserve">StatisticalTrend</t>
+    <t xml:space="preserve">TrendText</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TrendIcon</t>
   </si>
   <si>
     <t xml:space="preserve">Alligator Harbor Aquatic Preserve</t>
@@ -77,13 +80,13 @@
     <t xml:space="preserve">557, 558</t>
   </si>
   <si>
-    <t xml:space="preserve">Significantly decreasing trend</t>
+    <t xml:space="preserve">Decreasing trend</t>
   </si>
   <si>
     <t xml:space="preserve">Shoal grass</t>
   </si>
   <si>
-    <t xml:space="preserve">No significant trend</t>
+    <t xml:space="preserve">No detectable trend</t>
   </si>
   <si>
     <t xml:space="preserve">Star grass</t>
@@ -95,7 +98,7 @@
     <t xml:space="preserve">558</t>
   </si>
   <si>
-    <t xml:space="preserve">Insufficient data to calculate trend</t>
+    <t xml:space="preserve">Insufficient data</t>
   </si>
   <si>
     <t xml:space="preserve">No grass in quadrat</t>
@@ -164,7 +167,7 @@
     <t xml:space="preserve">559, 560</t>
   </si>
   <si>
-    <t xml:space="preserve">Significantly increasing trend</t>
+    <t xml:space="preserve">Increasing trend</t>
   </si>
   <si>
     <t xml:space="preserve">Big Bend Seagrasses &amp; Nature Coast Aquatic Preserves - Seagrass Monitoring</t>
@@ -737,6 +740,7 @@
     <col min="14" max="14" width="11.71" hidden="0" customWidth="1"/>
     <col min="15" max="15" width="11.71" hidden="0" customWidth="1"/>
     <col min="16" max="16" width="36.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="9.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -788,28 +792,31 @@
       <c r="P1" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H2" t="n">
         <v>144</v>
@@ -836,7 +843,10 @@
         <v>0.0273462910086319</v>
       </c>
       <c r="P2" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="3">
@@ -844,22 +854,22 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3" t="n">
         <v>263</v>
@@ -886,7 +896,10 @@
         <v>0.471691483034255</v>
       </c>
       <c r="P3" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -894,22 +907,22 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
@@ -930,7 +943,10 @@
       <c r="N4"/>
       <c r="O4"/>
       <c r="P4" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -938,22 +954,22 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H5" t="n">
         <v>1620</v>
@@ -974,7 +990,10 @@
       <c r="N5"/>
       <c r="O5"/>
       <c r="P5" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -982,22 +1001,22 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
@@ -1018,7 +1037,10 @@
       <c r="N6"/>
       <c r="O6"/>
       <c r="P6" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -1026,22 +1048,22 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H7" t="n">
         <v>800</v>
@@ -1068,7 +1090,10 @@
         <v>0.0253567825587495</v>
       </c>
       <c r="P7" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
@@ -1076,22 +1101,22 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H8" t="n">
         <v>686</v>
@@ -1118,7 +1143,10 @@
         <v>0.37785757960882</v>
       </c>
       <c r="P8" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1126,22 +1154,22 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E9" t="n">
         <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H9" t="n">
         <v>94</v>
@@ -1168,7 +1196,10 @@
         <v>0.00143440332984336</v>
       </c>
       <c r="P9" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="10">
@@ -1176,22 +1207,22 @@
         <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H10" t="n">
         <v>248</v>
@@ -1218,7 +1249,10 @@
         <v>0.487611201074338</v>
       </c>
       <c r="P10" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1226,22 +1260,22 @@
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E11" t="n">
         <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H11" t="n">
         <v>74</v>
@@ -1262,7 +1296,10 @@
       <c r="N11"/>
       <c r="O11"/>
       <c r="P11" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1270,22 +1307,22 @@
         <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E12" t="n">
         <v>2</v>
       </c>
       <c r="F12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H12" t="n">
         <v>52</v>
@@ -1306,7 +1343,10 @@
       <c r="N12"/>
       <c r="O12"/>
       <c r="P12" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1314,22 +1354,22 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E13" t="n">
         <v>2</v>
       </c>
       <c r="F13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H13" t="n">
         <v>125</v>
@@ -1356,7 +1396,10 @@
         <v>0.0314622501331645</v>
       </c>
       <c r="P13" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="14">
@@ -1364,22 +1407,22 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E14" t="n">
         <v>2</v>
       </c>
       <c r="F14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H14" t="n">
         <v>1021</v>
@@ -1406,7 +1449,10 @@
         <v>0.726844468394392</v>
       </c>
       <c r="P14" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1414,22 +1460,22 @@
         <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
@@ -1450,7 +1496,10 @@
       <c r="N15"/>
       <c r="O15"/>
       <c r="P15" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1458,22 +1507,22 @@
         <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E16" t="n">
         <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H16" t="n">
         <v>906</v>
@@ -1494,7 +1543,10 @@
       <c r="N16"/>
       <c r="O16"/>
       <c r="P16" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1502,22 +1554,22 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E17" t="n">
         <v>2</v>
       </c>
       <c r="F17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H17" t="n">
         <v>55</v>
@@ -1538,7 +1590,10 @@
       <c r="N17"/>
       <c r="O17"/>
       <c r="P17" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1546,22 +1601,22 @@
         <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H18" t="n">
         <v>44</v>
@@ -1582,7 +1637,10 @@
       <c r="N18"/>
       <c r="O18"/>
       <c r="P18" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1590,22 +1648,22 @@
         <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1622,7 +1680,10 @@
       <c r="N19"/>
       <c r="O19"/>
       <c r="P19" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1630,22 +1691,22 @@
         <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H20" t="n">
         <v>5129</v>
@@ -1672,7 +1733,10 @@
         <v>0.00000000000000000000000000234034760816071</v>
       </c>
       <c r="P20" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="21">
@@ -1680,22 +1744,22 @@
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="s">
+        <v>43</v>
+      </c>
+      <c r="G21" t="s">
         <v>44</v>
-      </c>
-      <c r="D21" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" t="s">
-        <v>42</v>
-      </c>
-      <c r="G21" t="s">
-        <v>43</v>
       </c>
       <c r="H21" t="n">
         <v>15441</v>
@@ -1722,7 +1786,10 @@
         <v>0.1417157133767</v>
       </c>
       <c r="P21" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1730,22 +1797,22 @@
         <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H22" t="n">
         <v>5131</v>
@@ -1772,7 +1839,10 @@
         <v>0.000230385165200919</v>
       </c>
       <c r="P22" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="23">
@@ -1780,22 +1850,22 @@
         <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H23" t="n">
         <v>5147</v>
@@ -1822,7 +1892,10 @@
         <v>0.0682854623978636</v>
       </c>
       <c r="P23" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1830,22 +1903,22 @@
         <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G24" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H24" t="n">
         <v>5147</v>
@@ -1866,7 +1939,10 @@
       <c r="N24"/>
       <c r="O24"/>
       <c r="P24" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1874,22 +1950,22 @@
         <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H25" t="n">
         <v>5382</v>
@@ -1916,7 +1992,10 @@
         <v>0.00000000000000000016644362385066</v>
       </c>
       <c r="P25" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="26">
@@ -1924,22 +2003,22 @@
         <v>4</v>
       </c>
       <c r="B26" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D26" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G26" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1956,7 +2035,10 @@
       <c r="N26"/>
       <c r="O26"/>
       <c r="P26" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1964,22 +2046,22 @@
         <v>5</v>
       </c>
       <c r="B27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E27" t="n">
         <v>2</v>
       </c>
       <c r="F27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H27" t="n">
         <v>3182</v>
@@ -2006,7 +2088,10 @@
         <v>0.000000874243938426819</v>
       </c>
       <c r="P27" t="s">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2014,22 +2099,22 @@
         <v>5</v>
       </c>
       <c r="B28" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E28" t="n">
         <v>2</v>
       </c>
       <c r="F28" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H28" t="n">
         <v>2552</v>
@@ -2056,7 +2141,10 @@
         <v>0.000128012104588442</v>
       </c>
       <c r="P28" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="29">
@@ -2064,22 +2152,22 @@
         <v>5</v>
       </c>
       <c r="B29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C29" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E29" t="n">
         <v>2</v>
       </c>
       <c r="F29" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G29" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H29" t="n">
         <v>848</v>
@@ -2106,7 +2194,10 @@
         <v>0.308991284377083</v>
       </c>
       <c r="P29" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2114,22 +2205,22 @@
         <v>5</v>
       </c>
       <c r="B30" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D30" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H30" t="n">
         <v>345</v>
@@ -2150,7 +2241,10 @@
       <c r="N30"/>
       <c r="O30"/>
       <c r="P30" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -2158,22 +2252,22 @@
         <v>5</v>
       </c>
       <c r="B31" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D31" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E31" t="n">
         <v>2</v>
       </c>
       <c r="F31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H31" t="n">
         <v>82</v>
@@ -2200,7 +2294,10 @@
         <v>0.598233856707755</v>
       </c>
       <c r="P31" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2208,22 +2305,22 @@
         <v>5</v>
       </c>
       <c r="B32" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C32" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E32" t="n">
         <v>2</v>
       </c>
       <c r="F32" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H32" t="n">
         <v>5411</v>
@@ -2250,7 +2347,10 @@
         <v>0.0000535982091523411</v>
       </c>
       <c r="P32" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="33">
@@ -2258,22 +2358,22 @@
         <v>5</v>
       </c>
       <c r="B33" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C33" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D33" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E33" t="n">
         <v>2</v>
       </c>
       <c r="F33" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G33" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H33" t="n">
         <v>12141</v>
@@ -2300,7 +2400,10 @@
         <v>0.000000000604370552252266</v>
       </c>
       <c r="P33" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="34">
@@ -2308,22 +2411,22 @@
         <v>6</v>
       </c>
       <c r="B34" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C34" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E34" t="n">
         <v>2</v>
       </c>
       <c r="F34" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G34" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H34" t="n">
         <v>2118</v>
@@ -2350,7 +2453,10 @@
         <v>0.102881423110622</v>
       </c>
       <c r="P34" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2358,22 +2464,22 @@
         <v>6</v>
       </c>
       <c r="B35" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C35" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D35" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E35" t="n">
         <v>3</v>
       </c>
       <c r="F35" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G35" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H35" t="n">
         <v>11252</v>
@@ -2400,7 +2506,10 @@
         <v>0.000000494818421991087</v>
       </c>
       <c r="P35" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="36">
@@ -2408,22 +2517,22 @@
         <v>6</v>
       </c>
       <c r="B36" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C36" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D36" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E36" t="n">
         <v>4</v>
       </c>
       <c r="F36" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G36" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H36" t="n">
         <v>13868</v>
@@ -2450,7 +2559,10 @@
         <v>0.00000610770243154178</v>
       </c>
       <c r="P36" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="37">
@@ -2458,22 +2570,22 @@
         <v>6</v>
       </c>
       <c r="B37" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C37" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D37" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E37" t="n">
         <v>4</v>
       </c>
       <c r="F37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G37" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H37" t="n">
         <v>40526</v>
@@ -2500,7 +2612,10 @@
         <v>0.00940484396388284</v>
       </c>
       <c r="P37" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="38">
@@ -2508,22 +2623,22 @@
         <v>6</v>
       </c>
       <c r="B38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C38" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D38" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E38" t="n">
         <v>3</v>
       </c>
       <c r="F38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G38" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H38" t="n">
         <v>9338</v>
@@ -2544,7 +2659,10 @@
       <c r="N38"/>
       <c r="O38"/>
       <c r="P38" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -2552,22 +2670,22 @@
         <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C39" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E39" t="n">
         <v>4</v>
       </c>
       <c r="F39" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H39" t="n">
         <v>13791</v>
@@ -2594,7 +2712,10 @@
         <v>0.000281397786247974</v>
       </c>
       <c r="P39" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="40">
@@ -2602,22 +2723,22 @@
         <v>6</v>
       </c>
       <c r="B40" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C40" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D40" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E40" t="n">
         <v>4</v>
       </c>
       <c r="F40" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G40" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H40" t="n">
         <v>14083</v>
@@ -2644,7 +2765,10 @@
         <v>0.000000000000000000000000000125679599318174</v>
       </c>
       <c r="P40" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="41">
@@ -2652,22 +2776,22 @@
         <v>6</v>
       </c>
       <c r="B41" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C41" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D41" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E41" t="n">
         <v>3</v>
       </c>
       <c r="F41" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G41" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H41" t="n">
         <v>9402</v>
@@ -2694,7 +2818,10 @@
         <v>0.256494287264958</v>
       </c>
       <c r="P41" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2702,22 +2829,22 @@
         <v>6</v>
       </c>
       <c r="B42" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C42" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D42" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E42" t="n">
         <v>4</v>
       </c>
       <c r="F42" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G42" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H42" t="n">
         <v>12001</v>
@@ -2744,7 +2871,10 @@
         <v>0.00122802477495601</v>
       </c>
       <c r="P42" t="s">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2752,22 +2882,22 @@
         <v>8</v>
       </c>
       <c r="B43" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C43" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D43" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E43" t="n">
         <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G43" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H43" t="n">
         <v>20</v>
@@ -2788,7 +2918,10 @@
       <c r="N43"/>
       <c r="O43"/>
       <c r="P43" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2796,22 +2929,22 @@
         <v>8</v>
       </c>
       <c r="B44" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D44" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E44" t="n">
         <v>2</v>
       </c>
       <c r="F44" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G44" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H44" t="n">
         <v>1352</v>
@@ -2838,7 +2971,10 @@
         <v>0.377609133307038</v>
       </c>
       <c r="P44" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2846,22 +2982,22 @@
         <v>8</v>
       </c>
       <c r="B45" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C45" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D45" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E45" t="n">
         <v>1</v>
       </c>
       <c r="F45" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G45" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H45" t="n">
         <v>381</v>
@@ -2882,7 +3018,10 @@
       <c r="N45"/>
       <c r="O45"/>
       <c r="P45" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -2890,22 +3029,22 @@
         <v>8</v>
       </c>
       <c r="B46" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C46" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D46" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E46" t="n">
         <v>2</v>
       </c>
       <c r="F46" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G46" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H46" t="n">
         <v>16</v>
@@ -2926,7 +3065,10 @@
       <c r="N46"/>
       <c r="O46"/>
       <c r="P46" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -2934,22 +3076,22 @@
         <v>8</v>
       </c>
       <c r="B47" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C47" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D47" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E47" t="n">
         <v>2</v>
       </c>
       <c r="F47" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G47" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H47" t="n">
         <v>1014</v>
@@ -2976,7 +3118,10 @@
         <v>0.0491914585084037</v>
       </c>
       <c r="P47" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="48">
@@ -2984,22 +3129,22 @@
         <v>8</v>
       </c>
       <c r="B48" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C48" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D48" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E48" t="n">
         <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G48" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H48" t="n">
         <v>1</v>
@@ -3020,7 +3165,10 @@
       <c r="N48"/>
       <c r="O48"/>
       <c r="P48" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3028,22 +3176,22 @@
         <v>9</v>
       </c>
       <c r="B49" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C49" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D49" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E49" t="n">
         <v>1</v>
       </c>
       <c r="F49" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G49" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H49" t="n">
         <v>1</v>
@@ -3064,7 +3212,10 @@
       <c r="N49"/>
       <c r="O49"/>
       <c r="P49" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3072,22 +3223,22 @@
         <v>9</v>
       </c>
       <c r="B50" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C50" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D50" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E50" t="n">
         <v>1</v>
       </c>
       <c r="F50" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H50" t="n">
         <v>113</v>
@@ -3114,7 +3265,10 @@
         <v>0.0166233464754912</v>
       </c>
       <c r="P50" t="s">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3122,22 +3276,22 @@
         <v>9</v>
       </c>
       <c r="B51" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C51" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D51" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E51" t="n">
         <v>1</v>
       </c>
       <c r="F51" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G51" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H51" t="n">
         <v>416</v>
@@ -3164,7 +3318,10 @@
         <v>0.348779258545112</v>
       </c>
       <c r="P51" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3172,22 +3329,22 @@
         <v>9</v>
       </c>
       <c r="B52" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C52" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D52" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E52" t="n">
         <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G52" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H52" t="n">
         <v>131</v>
@@ -3208,7 +3365,10 @@
       <c r="N52"/>
       <c r="O52"/>
       <c r="P52" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -3216,22 +3376,22 @@
         <v>9</v>
       </c>
       <c r="B53" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C53" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D53" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E53" t="n">
         <v>1</v>
       </c>
       <c r="F53" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G53" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H53" t="n">
         <v>96</v>
@@ -3258,7 +3418,10 @@
         <v>0.83124841287508</v>
       </c>
       <c r="P53" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3266,22 +3429,22 @@
         <v>9</v>
       </c>
       <c r="B54" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C54" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D54" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E54" t="n">
         <v>1</v>
       </c>
       <c r="F54" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G54" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H54" t="n">
         <v>307</v>
@@ -3308,7 +3471,10 @@
         <v>0.483437203484199</v>
       </c>
       <c r="P54" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3316,22 +3482,22 @@
         <v>9</v>
       </c>
       <c r="B55" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C55" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D55" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E55" t="n">
         <v>1</v>
       </c>
       <c r="F55" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G55" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H55" t="n">
         <v>666</v>
@@ -3358,7 +3524,10 @@
         <v>0.320530874580492</v>
       </c>
       <c r="P55" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3366,22 +3535,22 @@
         <v>11</v>
       </c>
       <c r="B56" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C56" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D56" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E56" t="n">
         <v>1</v>
       </c>
       <c r="F56" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G56" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H56" t="n">
         <v>1</v>
@@ -3402,7 +3571,10 @@
       <c r="N56"/>
       <c r="O56"/>
       <c r="P56" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3410,22 +3582,22 @@
         <v>11</v>
       </c>
       <c r="B57" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C57" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D57" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E57" t="n">
         <v>1</v>
       </c>
       <c r="F57" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G57" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H57" t="n">
         <v>82</v>
@@ -3446,7 +3618,10 @@
       <c r="N57"/>
       <c r="O57"/>
       <c r="P57" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3454,22 +3629,22 @@
         <v>11</v>
       </c>
       <c r="B58" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C58" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D58" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E58" t="n">
         <v>1</v>
       </c>
       <c r="F58" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G58" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H58" t="n">
         <v>572</v>
@@ -3496,7 +3671,10 @@
         <v>0.0159141893678147</v>
       </c>
       <c r="P58" t="s">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3504,22 +3682,22 @@
         <v>11</v>
       </c>
       <c r="B59" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C59" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D59" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E59" t="n">
         <v>1</v>
       </c>
       <c r="F59" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G59" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H59" t="n">
         <v>387</v>
@@ -3540,7 +3718,10 @@
       <c r="N59"/>
       <c r="O59"/>
       <c r="P59" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -3548,22 +3729,22 @@
         <v>11</v>
       </c>
       <c r="B60" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C60" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D60" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E60" t="n">
         <v>1</v>
       </c>
       <c r="F60" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G60" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H60" t="n">
         <v>392</v>
@@ -3590,7 +3771,10 @@
         <v>0.0760969879640776</v>
       </c>
       <c r="P60" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3598,22 +3782,22 @@
         <v>11</v>
       </c>
       <c r="B61" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C61" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D61" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E61" t="n">
         <v>1</v>
       </c>
       <c r="F61" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G61" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H61" t="n">
         <v>470</v>
@@ -3640,7 +3824,10 @@
         <v>0.424807329805699</v>
       </c>
       <c r="P61" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3648,22 +3835,22 @@
         <v>11</v>
       </c>
       <c r="B62" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C62" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D62" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E62" t="n">
         <v>1</v>
       </c>
       <c r="F62" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G62" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H62" t="n">
         <v>8</v>
@@ -3684,7 +3871,10 @@
       <c r="N62"/>
       <c r="O62"/>
       <c r="P62" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -3692,22 +3882,22 @@
         <v>14</v>
       </c>
       <c r="B63" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C63" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D63" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E63" t="n">
         <v>1</v>
       </c>
       <c r="F63" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G63" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H63" t="n">
         <v>21</v>
@@ -3734,7 +3924,10 @@
         <v>0.386180086961865</v>
       </c>
       <c r="P63" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -3742,22 +3935,22 @@
         <v>14</v>
       </c>
       <c r="B64" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C64" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D64" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E64" t="n">
         <v>1</v>
       </c>
       <c r="F64" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G64" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H64" t="n">
         <v>486</v>
@@ -3784,7 +3977,10 @@
         <v>0.378522951480508</v>
       </c>
       <c r="P64" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -3792,22 +3988,22 @@
         <v>14</v>
       </c>
       <c r="B65" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C65" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D65" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E65" t="n">
         <v>1</v>
       </c>
       <c r="F65" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G65" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H65" t="n">
         <v>848</v>
@@ -3834,7 +4030,10 @@
         <v>0.0010585081754943</v>
       </c>
       <c r="P65" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="66">
@@ -3842,22 +4041,22 @@
         <v>14</v>
       </c>
       <c r="B66" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C66" t="s">
+        <v>75</v>
+      </c>
+      <c r="D66" t="s">
+        <v>19</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" t="s">
+        <v>73</v>
+      </c>
+      <c r="G66" t="s">
         <v>74</v>
-      </c>
-      <c r="D66" t="s">
-        <v>18</v>
-      </c>
-      <c r="E66" t="n">
-        <v>1</v>
-      </c>
-      <c r="F66" t="s">
-        <v>72</v>
-      </c>
-      <c r="G66" t="s">
-        <v>73</v>
       </c>
       <c r="H66" t="n">
         <v>20</v>
@@ -3884,7 +4083,10 @@
         <v>0.92219735068256</v>
       </c>
       <c r="P66" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -3892,22 +4094,22 @@
         <v>14</v>
       </c>
       <c r="B67" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C67" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D67" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E67" t="n">
         <v>1</v>
       </c>
       <c r="F67" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G67" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H67" t="n">
         <v>15</v>
@@ -3928,7 +4130,10 @@
       <c r="N67"/>
       <c r="O67"/>
       <c r="P67" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -3936,22 +4141,22 @@
         <v>14</v>
       </c>
       <c r="B68" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C68" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D68" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E68" t="n">
         <v>1</v>
       </c>
       <c r="F68" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G68" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H68" t="n">
         <v>121</v>
@@ -3972,7 +4177,10 @@
       <c r="N68"/>
       <c r="O68"/>
       <c r="P68" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="69">
@@ -3980,22 +4188,22 @@
         <v>14</v>
       </c>
       <c r="B69" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C69" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D69" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E69" t="n">
         <v>1</v>
       </c>
       <c r="F69" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G69" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H69" t="n">
         <v>15</v>
@@ -4022,7 +4230,10 @@
         <v>0.351749557583809</v>
       </c>
       <c r="P69" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4030,22 +4241,22 @@
         <v>14</v>
       </c>
       <c r="B70" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C70" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D70" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E70" t="n">
         <v>1</v>
       </c>
       <c r="F70" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G70" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H70" t="n">
         <v>293</v>
@@ -4072,7 +4283,10 @@
         <v>0.0101183628293739</v>
       </c>
       <c r="P70" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="71">
@@ -4080,22 +4294,22 @@
         <v>14</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C71" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D71" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E71" t="n">
         <v>1</v>
       </c>
       <c r="F71" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G71" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H71" t="n">
         <v>888</v>
@@ -4122,7 +4336,10 @@
         <v>0.0235055099480849</v>
       </c>
       <c r="P71" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="72">
@@ -4130,22 +4347,22 @@
         <v>14</v>
       </c>
       <c r="B72" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C72" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D72" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E72" t="n">
         <v>1</v>
       </c>
       <c r="F72" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G72" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H72" t="n">
         <v>8</v>
@@ -4166,7 +4383,10 @@
       <c r="N72"/>
       <c r="O72"/>
       <c r="P72" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="73">
@@ -4174,22 +4394,22 @@
         <v>15</v>
       </c>
       <c r="B73" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C73" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D73" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E73" t="n">
         <v>2</v>
       </c>
       <c r="F73" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G73" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H73" t="n">
         <v>9660</v>
@@ -4216,7 +4436,10 @@
         <v>0.196740148903206</v>
       </c>
       <c r="P73" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -4224,22 +4447,22 @@
         <v>15</v>
       </c>
       <c r="B74" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C74" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D74" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E74" t="n">
         <v>3</v>
       </c>
       <c r="F74" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G74" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H74" t="n">
         <v>18037</v>
@@ -4266,7 +4489,10 @@
         <v>0.0000785983600721293</v>
       </c>
       <c r="P74" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="75">
@@ -4274,22 +4500,22 @@
         <v>15</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C75" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D75" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E75" t="n">
         <v>5</v>
       </c>
       <c r="F75" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G75" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H75" t="n">
         <v>19551</v>
@@ -4316,7 +4542,10 @@
         <v>0.000291230507719468</v>
       </c>
       <c r="P75" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="76">
@@ -4324,22 +4553,22 @@
         <v>15</v>
       </c>
       <c r="B76" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C76" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D76" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E76" t="n">
         <v>4</v>
       </c>
       <c r="F76" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G76" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H76" t="n">
         <v>47846</v>
@@ -4366,7 +4595,10 @@
         <v>0.413500371689689</v>
       </c>
       <c r="P76" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -4374,22 +4606,22 @@
         <v>15</v>
       </c>
       <c r="B77" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C77" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D77" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E77" t="n">
         <v>3</v>
       </c>
       <c r="F77" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G77" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H77" t="n">
         <v>17558</v>
@@ -4416,7 +4648,10 @@
         <v>0.127260017280868</v>
       </c>
       <c r="P77" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -4424,22 +4659,22 @@
         <v>15</v>
       </c>
       <c r="B78" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C78" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D78" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E78" t="n">
         <v>5</v>
       </c>
       <c r="F78" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G78" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H78" t="n">
         <v>19436</v>
@@ -4466,7 +4701,10 @@
         <v>0.0175021586314602</v>
       </c>
       <c r="P78" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="79">
@@ -4474,22 +4712,22 @@
         <v>15</v>
       </c>
       <c r="B79" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C79" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D79" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E79" t="n">
         <v>5</v>
       </c>
       <c r="F79" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G79" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H79" t="n">
         <v>19879</v>
@@ -4516,7 +4754,10 @@
         <v>0.000000000000000000000000000505749538387561</v>
       </c>
       <c r="P79" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="80">
@@ -4524,22 +4765,22 @@
         <v>15</v>
       </c>
       <c r="B80" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C80" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D80" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E80" t="n">
         <v>3</v>
       </c>
       <c r="F80" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G80" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H80" t="n">
         <v>16804</v>
@@ -4566,7 +4807,10 @@
         <v>0.116657820450709</v>
       </c>
       <c r="P80" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -4574,22 +4818,22 @@
         <v>15</v>
       </c>
       <c r="B81" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C81" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D81" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E81" t="n">
         <v>4</v>
       </c>
       <c r="F81" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G81" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H81" t="n">
         <v>16627</v>
@@ -4616,7 +4860,10 @@
         <v>0.00103336552605391</v>
       </c>
       <c r="P81" t="s">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -4624,22 +4871,22 @@
         <v>17</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C82" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D82" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E82" t="n">
         <v>1</v>
       </c>
       <c r="F82" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G82" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H82" t="n">
         <v>1280</v>
@@ -4666,7 +4913,10 @@
         <v>0.295357422338898</v>
       </c>
       <c r="P82" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -4674,22 +4924,22 @@
         <v>17</v>
       </c>
       <c r="B83" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C83" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D83" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E83" t="n">
         <v>1</v>
       </c>
       <c r="F83" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G83" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H83" t="n">
         <v>166</v>
@@ -4710,7 +4960,10 @@
       <c r="N83"/>
       <c r="O83"/>
       <c r="P83" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="84">
@@ -4718,22 +4971,22 @@
         <v>17</v>
       </c>
       <c r="B84" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C84" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D84" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E84" t="n">
         <v>1</v>
       </c>
       <c r="F84" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G84" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H84" t="n">
         <v>4</v>
@@ -4754,7 +5007,10 @@
       <c r="N84"/>
       <c r="O84"/>
       <c r="P84" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -4762,22 +5018,22 @@
         <v>17</v>
       </c>
       <c r="B85" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C85" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D85" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E85" t="n">
         <v>1</v>
       </c>
       <c r="F85" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G85" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H85" t="n">
         <v>3</v>
@@ -4798,7 +5054,10 @@
       <c r="N85"/>
       <c r="O85"/>
       <c r="P85" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -4806,22 +5065,22 @@
         <v>17</v>
       </c>
       <c r="B86" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C86" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D86" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E86" t="n">
         <v>1</v>
       </c>
       <c r="F86" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G86" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H86" t="n">
         <v>799</v>
@@ -4848,7 +5107,10 @@
         <v>0.141337566141349</v>
       </c>
       <c r="P86" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -4856,22 +5118,22 @@
         <v>17</v>
       </c>
       <c r="B87" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C87" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D87" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E87" t="n">
         <v>1</v>
       </c>
       <c r="F87" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G87" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H87" t="n">
         <v>1577</v>
@@ -4898,7 +5160,10 @@
         <v>0.219850271952525</v>
       </c>
       <c r="P87" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -4906,22 +5171,22 @@
         <v>17</v>
       </c>
       <c r="B88" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C88" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D88" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E88" t="n">
         <v>1</v>
       </c>
       <c r="F88" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G88" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H88" t="n">
         <v>1584</v>
@@ -4948,7 +5213,10 @@
         <v>0.446153345812438</v>
       </c>
       <c r="P88" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -4956,22 +5224,22 @@
         <v>18</v>
       </c>
       <c r="B89" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C89" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D89" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E89" t="n">
         <v>1</v>
       </c>
       <c r="F89" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G89" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H89" t="n">
         <v>26</v>
@@ -4998,7 +5266,10 @@
         <v>0.257189987451246</v>
       </c>
       <c r="P89" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -5006,22 +5277,22 @@
         <v>18</v>
       </c>
       <c r="B90" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C90" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D90" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E90" t="n">
         <v>1</v>
       </c>
       <c r="F90" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G90" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H90" t="n">
         <v>836</v>
@@ -5048,7 +5319,10 @@
         <v>0.179777077709195</v>
       </c>
       <c r="P90" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -5056,22 +5330,22 @@
         <v>18</v>
       </c>
       <c r="B91" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C91" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D91" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E91" t="n">
         <v>1</v>
       </c>
       <c r="F91" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G91" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H91" t="n">
         <v>2328</v>
@@ -5098,7 +5372,10 @@
         <v>0.0762040357190241</v>
       </c>
       <c r="P91" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -5106,22 +5383,22 @@
         <v>18</v>
       </c>
       <c r="B92" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C92" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D92" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E92" t="n">
         <v>1</v>
       </c>
       <c r="F92" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G92" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H92" t="n">
         <v>2</v>
@@ -5142,7 +5419,10 @@
       <c r="N92"/>
       <c r="O92"/>
       <c r="P92" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="93">
@@ -5150,22 +5430,22 @@
         <v>18</v>
       </c>
       <c r="B93" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C93" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D93" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E93" t="n">
         <v>1</v>
       </c>
       <c r="F93" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G93" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H93" t="n">
         <v>698</v>
@@ -5186,7 +5466,10 @@
       <c r="N93"/>
       <c r="O93"/>
       <c r="P93" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="94">
@@ -5194,22 +5477,22 @@
         <v>18</v>
       </c>
       <c r="B94" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C94" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D94" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E94" t="n">
         <v>1</v>
       </c>
       <c r="F94" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G94" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H94" t="n">
         <v>40</v>
@@ -5236,7 +5519,10 @@
         <v>0.79552038130418</v>
       </c>
       <c r="P94" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -5244,22 +5530,22 @@
         <v>18</v>
       </c>
       <c r="B95" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C95" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D95" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E95" t="n">
         <v>1</v>
       </c>
       <c r="F95" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G95" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H95" t="n">
         <v>249</v>
@@ -5286,7 +5572,10 @@
         <v>0.622020803450261</v>
       </c>
       <c r="P95" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -5294,22 +5583,22 @@
         <v>18</v>
       </c>
       <c r="B96" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C96" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D96" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E96" t="n">
         <v>1</v>
       </c>
       <c r="F96" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G96" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H96" t="n">
         <v>1083</v>
@@ -5336,7 +5625,10 @@
         <v>0.135218056033289</v>
       </c>
       <c r="P96" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -5344,22 +5636,22 @@
         <v>18</v>
       </c>
       <c r="B97" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C97" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D97" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E97" t="n">
         <v>1</v>
       </c>
       <c r="F97" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G97" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H97" t="n">
         <v>3401</v>
@@ -5386,7 +5678,10 @@
         <v>0.0083590244169381</v>
       </c>
       <c r="P97" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="98">
@@ -5394,22 +5689,22 @@
         <v>21</v>
       </c>
       <c r="B98" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C98" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D98" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E98" t="n">
         <v>1</v>
       </c>
       <c r="F98" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G98" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -5426,7 +5721,10 @@
       <c r="N98"/>
       <c r="O98"/>
       <c r="P98" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="99">
@@ -5434,22 +5732,22 @@
         <v>21</v>
       </c>
       <c r="B99" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C99" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D99" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E99" t="n">
         <v>1</v>
       </c>
       <c r="F99" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G99" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H99" t="n">
         <v>16571</v>
@@ -5470,7 +5768,10 @@
       <c r="N99"/>
       <c r="O99"/>
       <c r="P99" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="100">
@@ -5478,22 +5779,22 @@
         <v>21</v>
       </c>
       <c r="B100" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C100" t="s">
+        <v>45</v>
+      </c>
+      <c r="D100" t="s">
+        <v>19</v>
+      </c>
+      <c r="E100" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" t="s">
+        <v>43</v>
+      </c>
+      <c r="G100" t="s">
         <v>44</v>
-      </c>
-      <c r="D100" t="s">
-        <v>18</v>
-      </c>
-      <c r="E100" t="n">
-        <v>1</v>
-      </c>
-      <c r="F100" t="s">
-        <v>42</v>
-      </c>
-      <c r="G100" t="s">
-        <v>43</v>
       </c>
       <c r="H100" t="n">
         <v>49792</v>
@@ -5520,7 +5821,10 @@
         <v>0.790980253872378</v>
       </c>
       <c r="P100" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -5528,22 +5832,22 @@
         <v>21</v>
       </c>
       <c r="B101" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C101" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D101" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E101" t="n">
         <v>1</v>
       </c>
       <c r="F101" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G101" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H101" t="n">
         <v>16606</v>
@@ -5570,7 +5874,10 @@
         <v>0.101584432953808</v>
       </c>
       <c r="P101" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -5578,22 +5885,22 @@
         <v>21</v>
       </c>
       <c r="B102" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C102" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D102" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E102" t="n">
         <v>1</v>
       </c>
       <c r="F102" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G102" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H102" t="n">
         <v>16588</v>
@@ -5620,7 +5927,10 @@
         <v>0.00433585695109475</v>
       </c>
       <c r="P102" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="103">
@@ -5628,22 +5938,22 @@
         <v>21</v>
       </c>
       <c r="B103" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C103" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D103" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E103" t="n">
         <v>1</v>
       </c>
       <c r="F103" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G103" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H103" t="n">
         <v>16607</v>
@@ -5670,7 +5980,10 @@
         <v>0.0982887196272221</v>
       </c>
       <c r="P103" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -5678,22 +5991,22 @@
         <v>21</v>
       </c>
       <c r="B104" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C104" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D104" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E104" t="n">
         <v>1</v>
       </c>
       <c r="F104" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G104" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H104" t="n">
         <v>17779</v>
@@ -5720,7 +6033,10 @@
         <v>0.000000000000000000000227816605153144</v>
       </c>
       <c r="P104" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="105">
@@ -5728,22 +6044,22 @@
         <v>21</v>
       </c>
       <c r="B105" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C105" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D105" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E105" t="n">
         <v>1</v>
       </c>
       <c r="F105" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G105" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -5760,7 +6076,10 @@
       <c r="N105"/>
       <c r="O105"/>
       <c r="P105" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -5768,22 +6087,22 @@
         <v>22</v>
       </c>
       <c r="B106" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C106" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D106" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E106" t="n">
         <v>1</v>
       </c>
       <c r="F106" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G106" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -5800,7 +6119,10 @@
       <c r="N106"/>
       <c r="O106"/>
       <c r="P106" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -5808,22 +6130,22 @@
         <v>22</v>
       </c>
       <c r="B107" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C107" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D107" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E107" t="n">
         <v>1</v>
       </c>
       <c r="F107" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G107" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H107" t="n">
         <v>6463</v>
@@ -5850,7 +6172,10 @@
         <v>0.000692330268166631</v>
       </c>
       <c r="P107" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="108">
@@ -5858,22 +6183,22 @@
         <v>22</v>
       </c>
       <c r="B108" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C108" t="s">
+        <v>45</v>
+      </c>
+      <c r="D108" t="s">
+        <v>19</v>
+      </c>
+      <c r="E108" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" t="s">
+        <v>43</v>
+      </c>
+      <c r="G108" t="s">
         <v>44</v>
-      </c>
-      <c r="D108" t="s">
-        <v>18</v>
-      </c>
-      <c r="E108" t="n">
-        <v>1</v>
-      </c>
-      <c r="F108" t="s">
-        <v>42</v>
-      </c>
-      <c r="G108" t="s">
-        <v>43</v>
       </c>
       <c r="H108" t="n">
         <v>19432</v>
@@ -5900,7 +6225,10 @@
         <v>0.0940962608088782</v>
       </c>
       <c r="P108" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -5908,22 +6236,22 @@
         <v>22</v>
       </c>
       <c r="B109" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C109" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D109" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E109" t="n">
         <v>1</v>
       </c>
       <c r="F109" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G109" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H109" t="n">
         <v>6482</v>
@@ -5950,7 +6278,10 @@
         <v>0.117004457167443</v>
       </c>
       <c r="P109" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -5958,22 +6289,22 @@
         <v>22</v>
       </c>
       <c r="B110" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C110" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D110" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E110" t="n">
         <v>1</v>
       </c>
       <c r="F110" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G110" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H110" t="n">
         <v>6466</v>
@@ -6000,7 +6331,10 @@
         <v>0.0432676395822031</v>
       </c>
       <c r="P110" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="111">
@@ -6008,22 +6342,22 @@
         <v>22</v>
       </c>
       <c r="B111" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C111" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D111" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E111" t="n">
         <v>1</v>
       </c>
       <c r="F111" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G111" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H111" t="n">
         <v>6465</v>
@@ -6050,7 +6384,10 @@
         <v>0.0143482789438823</v>
       </c>
       <c r="P111" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="112">
@@ -6058,22 +6395,22 @@
         <v>22</v>
       </c>
       <c r="B112" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C112" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D112" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E112" t="n">
         <v>1</v>
       </c>
       <c r="F112" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G112" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H112" t="n">
         <v>6996</v>
@@ -6100,7 +6437,10 @@
         <v>0.000000000000000000379808349181876</v>
       </c>
       <c r="P112" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="113">
@@ -6108,22 +6448,22 @@
         <v>22</v>
       </c>
       <c r="B113" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C113" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D113" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E113" t="n">
         <v>1</v>
       </c>
       <c r="F113" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G113" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -6140,7 +6480,10 @@
       <c r="N113"/>
       <c r="O113"/>
       <c r="P113" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="114">
@@ -6148,22 +6491,22 @@
         <v>23</v>
       </c>
       <c r="B114" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C114" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D114" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E114" t="n">
         <v>1</v>
       </c>
       <c r="F114" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G114" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -6180,7 +6523,10 @@
       <c r="N114"/>
       <c r="O114"/>
       <c r="P114" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="115">
@@ -6188,22 +6534,22 @@
         <v>23</v>
       </c>
       <c r="B115" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C115" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D115" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E115" t="n">
         <v>2</v>
       </c>
       <c r="F115" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G115" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H115" t="n">
         <v>6524</v>
@@ -6230,7 +6576,10 @@
         <v>0.0974653898461681</v>
       </c>
       <c r="P115" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -6238,22 +6587,22 @@
         <v>23</v>
       </c>
       <c r="B116" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C116" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D116" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E116" t="n">
         <v>2</v>
       </c>
       <c r="F116" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G116" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H116" t="n">
         <v>19627</v>
@@ -6280,7 +6629,10 @@
         <v>0.0562321879273083</v>
       </c>
       <c r="P116" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -6288,22 +6640,22 @@
         <v>23</v>
       </c>
       <c r="B117" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C117" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D117" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E117" t="n">
         <v>1</v>
       </c>
       <c r="F117" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G117" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H117" t="n">
         <v>6550</v>
@@ -6324,7 +6676,10 @@
       <c r="N117"/>
       <c r="O117"/>
       <c r="P117" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="118">
@@ -6332,22 +6687,22 @@
         <v>23</v>
       </c>
       <c r="B118" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C118" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D118" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E118" t="n">
         <v>2</v>
       </c>
       <c r="F118" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G118" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H118" t="n">
         <v>6539</v>
@@ -6374,7 +6729,10 @@
         <v>0.000440849275728977</v>
       </c>
       <c r="P118" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="119">
@@ -6382,22 +6740,22 @@
         <v>23</v>
       </c>
       <c r="B119" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C119" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D119" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E119" t="n">
         <v>2</v>
       </c>
       <c r="F119" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G119" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H119" t="n">
         <v>6546</v>
@@ -6424,7 +6782,10 @@
         <v>0.0657011378680577</v>
       </c>
       <c r="P119" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -6432,22 +6793,22 @@
         <v>23</v>
       </c>
       <c r="B120" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C120" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D120" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E120" t="n">
         <v>1</v>
       </c>
       <c r="F120" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G120" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H120" t="n">
         <v>7130</v>
@@ -6474,7 +6835,10 @@
         <v>0.0000155735740157106</v>
       </c>
       <c r="P120" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="121">
@@ -6482,22 +6846,22 @@
         <v>23</v>
       </c>
       <c r="B121" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C121" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D121" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E121" t="n">
         <v>2</v>
       </c>
       <c r="F121" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G121" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -6514,7 +6878,10 @@
       <c r="N121"/>
       <c r="O121"/>
       <c r="P121" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="122">
@@ -6522,22 +6889,22 @@
         <v>25</v>
       </c>
       <c r="B122" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C122" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D122" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E122" t="n">
         <v>1</v>
       </c>
       <c r="F122" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G122" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H122" t="n">
         <v>65</v>
@@ -6564,7 +6931,10 @@
         <v>0.26003557319771</v>
       </c>
       <c r="P122" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -6572,22 +6942,22 @@
         <v>25</v>
       </c>
       <c r="B123" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C123" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D123" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E123" t="n">
         <v>1</v>
       </c>
       <c r="F123" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G123" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H123" t="n">
         <v>116</v>
@@ -6614,7 +6984,10 @@
         <v>0.0227362274662352</v>
       </c>
       <c r="P123" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="124">
@@ -6622,22 +6995,22 @@
         <v>25</v>
       </c>
       <c r="B124" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C124" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D124" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E124" t="n">
         <v>2</v>
       </c>
       <c r="F124" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G124" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H124" t="n">
         <v>960</v>
@@ -6664,7 +7037,10 @@
         <v>0.598320943514704</v>
       </c>
       <c r="P124" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -6672,22 +7048,22 @@
         <v>25</v>
       </c>
       <c r="B125" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C125" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D125" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E125" t="n">
         <v>1</v>
       </c>
       <c r="F125" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G125" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H125" t="n">
         <v>113</v>
@@ -6708,7 +7084,10 @@
       <c r="N125"/>
       <c r="O125"/>
       <c r="P125" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="126">
@@ -6716,22 +7095,22 @@
         <v>25</v>
       </c>
       <c r="B126" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C126" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D126" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E126" t="n">
         <v>2</v>
       </c>
       <c r="F126" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G126" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H126" t="n">
         <v>500</v>
@@ -6758,7 +7137,10 @@
         <v>0.962697808501246</v>
       </c>
       <c r="P126" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -6766,22 +7148,22 @@
         <v>25</v>
       </c>
       <c r="B127" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C127" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D127" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E127" t="n">
         <v>2</v>
       </c>
       <c r="F127" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G127" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H127" t="n">
         <v>671</v>
@@ -6808,7 +7190,10 @@
         <v>0.453703957656648</v>
       </c>
       <c r="P127" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -6816,22 +7201,22 @@
         <v>25</v>
       </c>
       <c r="B128" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C128" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D128" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E128" t="n">
         <v>2</v>
       </c>
       <c r="F128" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G128" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H128" t="n">
         <v>1181</v>
@@ -6858,7 +7243,10 @@
         <v>0.246787900026742</v>
       </c>
       <c r="P128" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -6866,22 +7254,22 @@
         <v>26</v>
       </c>
       <c r="B129" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C129" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D129" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E129" t="n">
         <v>1</v>
       </c>
       <c r="F129" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G129" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H129" t="n">
         <v>164</v>
@@ -6902,7 +7290,10 @@
       <c r="N129"/>
       <c r="O129"/>
       <c r="P129" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="130">
@@ -6910,22 +7301,22 @@
         <v>26</v>
       </c>
       <c r="B130" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C130" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D130" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E130" t="n">
         <v>1</v>
       </c>
       <c r="F130" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G130" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H130" t="n">
         <v>74</v>
@@ -6946,7 +7337,10 @@
       <c r="N130"/>
       <c r="O130"/>
       <c r="P130" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="131">
@@ -6954,22 +7348,22 @@
         <v>26</v>
       </c>
       <c r="B131" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C131" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D131" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E131" t="n">
         <v>1</v>
       </c>
       <c r="F131" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G131" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H131" t="n">
         <v>74</v>
@@ -6990,7 +7384,10 @@
       <c r="N131"/>
       <c r="O131"/>
       <c r="P131" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="132">
@@ -6998,22 +7395,22 @@
         <v>26</v>
       </c>
       <c r="B132" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C132" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D132" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E132" t="n">
         <v>1</v>
       </c>
       <c r="F132" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G132" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H132" t="n">
         <v>74</v>
@@ -7034,7 +7431,10 @@
       <c r="N132"/>
       <c r="O132"/>
       <c r="P132" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="133">
@@ -7042,22 +7442,22 @@
         <v>26</v>
       </c>
       <c r="B133" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C133" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D133" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E133" t="n">
         <v>1</v>
       </c>
       <c r="F133" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G133" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H133" t="n">
         <v>386</v>
@@ -7078,7 +7478,10 @@
       <c r="N133"/>
       <c r="O133"/>
       <c r="P133" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="134">
@@ -7086,22 +7489,22 @@
         <v>26</v>
       </c>
       <c r="B134" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C134" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D134" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E134" t="n">
         <v>1</v>
       </c>
       <c r="F134" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G134" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H134" t="n">
         <v>395</v>
@@ -7122,7 +7525,10 @@
       <c r="N134"/>
       <c r="O134"/>
       <c r="P134" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="135">
@@ -7130,22 +7536,22 @@
         <v>27</v>
       </c>
       <c r="B135" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C135" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D135" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E135" t="n">
         <v>1</v>
       </c>
       <c r="F135" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G135" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -7162,7 +7568,10 @@
       <c r="N135"/>
       <c r="O135"/>
       <c r="P135" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="136">
@@ -7170,22 +7579,22 @@
         <v>27</v>
       </c>
       <c r="B136" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C136" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D136" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E136" t="n">
         <v>3</v>
       </c>
       <c r="F136" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G136" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H136" t="n">
         <v>825</v>
@@ -7212,7 +7621,10 @@
         <v>0.00000000000192769985029779</v>
       </c>
       <c r="P136" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="137">
@@ -7220,22 +7632,22 @@
         <v>27</v>
       </c>
       <c r="B137" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C137" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D137" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E137" t="n">
         <v>3</v>
       </c>
       <c r="F137" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G137" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H137" t="n">
         <v>2493</v>
@@ -7262,7 +7674,10 @@
         <v>0.00052505111566868</v>
       </c>
       <c r="P137" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="138">
@@ -7270,22 +7685,22 @@
         <v>27</v>
       </c>
       <c r="B138" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C138" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D138" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E138" t="n">
         <v>1</v>
       </c>
       <c r="F138" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G138" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H138" t="n">
         <v>832</v>
@@ -7306,7 +7721,10 @@
       <c r="N138"/>
       <c r="O138"/>
       <c r="P138" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="139">
@@ -7314,22 +7732,22 @@
         <v>27</v>
       </c>
       <c r="B139" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C139" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D139" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E139" t="n">
         <v>3</v>
       </c>
       <c r="F139" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G139" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H139" t="n">
         <v>832</v>
@@ -7356,7 +7774,10 @@
         <v>0.336338821176729</v>
       </c>
       <c r="P139" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -7364,22 +7785,22 @@
         <v>27</v>
       </c>
       <c r="B140" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C140" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D140" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E140" t="n">
         <v>3</v>
       </c>
       <c r="F140" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G140" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H140" t="n">
         <v>832</v>
@@ -7406,7 +7827,10 @@
         <v>0.30074758659337</v>
       </c>
       <c r="P140" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -7414,22 +7838,22 @@
         <v>27</v>
       </c>
       <c r="B141" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C141" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D141" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E141" t="n">
         <v>1</v>
       </c>
       <c r="F141" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G141" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H141" t="n">
         <v>839</v>
@@ -7456,7 +7880,10 @@
         <v>0.00000000000000000216796064709784</v>
       </c>
       <c r="P141" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="142">
@@ -7464,22 +7891,22 @@
         <v>27</v>
       </c>
       <c r="B142" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C142" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D142" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E142" t="n">
         <v>3</v>
       </c>
       <c r="F142" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G142" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -7496,7 +7923,10 @@
       <c r="N142"/>
       <c r="O142"/>
       <c r="P142" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="143">
@@ -7504,22 +7934,22 @@
         <v>28</v>
       </c>
       <c r="B143" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C143" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D143" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E143" t="n">
         <v>1</v>
       </c>
       <c r="F143" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G143" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H143" t="n">
         <v>1</v>
@@ -7540,7 +7970,10 @@
       <c r="N143"/>
       <c r="O143"/>
       <c r="P143" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="144">
@@ -7548,22 +7981,22 @@
         <v>28</v>
       </c>
       <c r="B144" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C144" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D144" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E144" t="n">
         <v>1</v>
       </c>
       <c r="F144" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G144" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H144" t="n">
         <v>231</v>
@@ -7590,7 +8023,10 @@
         <v>0.10474902248809</v>
       </c>
       <c r="P144" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -7598,22 +8034,22 @@
         <v>28</v>
       </c>
       <c r="B145" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C145" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D145" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E145" t="n">
         <v>2</v>
       </c>
       <c r="F145" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G145" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H145" t="n">
         <v>570</v>
@@ -7640,7 +8076,10 @@
         <v>0.88050571645243</v>
       </c>
       <c r="P145" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -7648,22 +8087,22 @@
         <v>28</v>
       </c>
       <c r="B146" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C146" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D146" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E146" t="n">
         <v>1</v>
       </c>
       <c r="F146" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G146" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H146" t="n">
         <v>4</v>
@@ -7684,7 +8123,10 @@
       <c r="N146"/>
       <c r="O146"/>
       <c r="P146" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="147">
@@ -7692,22 +8134,22 @@
         <v>28</v>
       </c>
       <c r="B147" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C147" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D147" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E147" t="n">
         <v>1</v>
       </c>
       <c r="F147" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G147" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H147" t="n">
         <v>20</v>
@@ -7734,7 +8176,10 @@
         <v>0.780887507542741</v>
       </c>
       <c r="P147" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -7742,22 +8187,22 @@
         <v>28</v>
       </c>
       <c r="B148" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C148" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D148" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E148" t="n">
         <v>1</v>
       </c>
       <c r="F148" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G148" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H148" t="n">
         <v>112</v>
@@ -7778,7 +8223,10 @@
       <c r="N148"/>
       <c r="O148"/>
       <c r="P148" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="149">
@@ -7786,22 +8234,22 @@
         <v>28</v>
       </c>
       <c r="B149" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C149" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D149" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E149" t="n">
         <v>1</v>
       </c>
       <c r="F149" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G149" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H149" t="n">
         <v>2</v>
@@ -7822,7 +8270,10 @@
       <c r="N149"/>
       <c r="O149"/>
       <c r="P149" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="150">
@@ -7830,22 +8281,22 @@
         <v>28</v>
       </c>
       <c r="B150" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C150" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D150" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E150" t="n">
         <v>1</v>
       </c>
       <c r="F150" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G150" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -7862,7 +8313,10 @@
       <c r="N150"/>
       <c r="O150"/>
       <c r="P150" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="151">
@@ -7870,22 +8324,22 @@
         <v>28</v>
       </c>
       <c r="B151" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C151" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D151" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E151" t="n">
         <v>2</v>
       </c>
       <c r="F151" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G151" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H151" t="n">
         <v>172</v>
@@ -7912,7 +8366,10 @@
         <v>0.158331973904867</v>
       </c>
       <c r="P151" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -7920,22 +8377,22 @@
         <v>28</v>
       </c>
       <c r="B152" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C152" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D152" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E152" t="n">
         <v>1</v>
       </c>
       <c r="F152" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G152" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H152" t="n">
         <v>719</v>
@@ -7962,7 +8419,10 @@
         <v>0.134250711812299</v>
       </c>
       <c r="P152" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -7970,22 +8430,22 @@
         <v>28</v>
       </c>
       <c r="B153" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C153" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D153" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E153" t="n">
         <v>1</v>
       </c>
       <c r="F153" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G153" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H153" t="n">
         <v>4</v>
@@ -8006,7 +8466,10 @@
       <c r="N153"/>
       <c r="O153"/>
       <c r="P153" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="154">
@@ -8014,22 +8477,22 @@
         <v>29</v>
       </c>
       <c r="B154" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C154" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D154" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E154" t="n">
         <v>1</v>
       </c>
       <c r="F154" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G154" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -8046,7 +8509,10 @@
       <c r="N154"/>
       <c r="O154"/>
       <c r="P154" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="155">
@@ -8054,22 +8520,22 @@
         <v>29</v>
       </c>
       <c r="B155" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C155" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D155" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E155" t="n">
         <v>1</v>
       </c>
       <c r="F155" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G155" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H155" t="n">
         <v>685</v>
@@ -8096,7 +8562,10 @@
         <v>0.238304224446081</v>
       </c>
       <c r="P155" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -8104,22 +8573,22 @@
         <v>29</v>
       </c>
       <c r="B156" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C156" t="s">
+        <v>45</v>
+      </c>
+      <c r="D156" t="s">
+        <v>19</v>
+      </c>
+      <c r="E156" t="n">
+        <v>1</v>
+      </c>
+      <c r="F156" t="s">
+        <v>43</v>
+      </c>
+      <c r="G156" t="s">
         <v>44</v>
-      </c>
-      <c r="D156" t="s">
-        <v>18</v>
-      </c>
-      <c r="E156" t="n">
-        <v>1</v>
-      </c>
-      <c r="F156" t="s">
-        <v>42</v>
-      </c>
-      <c r="G156" t="s">
-        <v>43</v>
       </c>
       <c r="H156" t="n">
         <v>2055</v>
@@ -8146,7 +8615,10 @@
         <v>0.161567647341493</v>
       </c>
       <c r="P156" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -8154,22 +8626,22 @@
         <v>29</v>
       </c>
       <c r="B157" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C157" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D157" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E157" t="n">
         <v>1</v>
       </c>
       <c r="F157" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G157" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H157" t="n">
         <v>685</v>
@@ -8190,7 +8662,10 @@
       <c r="N157"/>
       <c r="O157"/>
       <c r="P157" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="158">
@@ -8198,22 +8673,22 @@
         <v>29</v>
       </c>
       <c r="B158" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C158" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D158" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E158" t="n">
         <v>1</v>
       </c>
       <c r="F158" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G158" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H158" t="n">
         <v>685</v>
@@ -8234,7 +8709,10 @@
       <c r="N158"/>
       <c r="O158"/>
       <c r="P158" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="159">
@@ -8242,22 +8720,22 @@
         <v>29</v>
       </c>
       <c r="B159" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C159" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D159" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E159" t="n">
         <v>1</v>
       </c>
       <c r="F159" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G159" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H159" t="n">
         <v>685</v>
@@ -8278,7 +8756,10 @@
       <c r="N159"/>
       <c r="O159"/>
       <c r="P159" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="160">
@@ -8286,22 +8767,22 @@
         <v>29</v>
       </c>
       <c r="B160" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C160" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D160" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E160" t="n">
         <v>1</v>
       </c>
       <c r="F160" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G160" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H160" t="n">
         <v>685</v>
@@ -8328,7 +8809,10 @@
         <v>0.236718465491046</v>
       </c>
       <c r="P160" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -8336,22 +8820,22 @@
         <v>29</v>
       </c>
       <c r="B161" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C161" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D161" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E161" t="n">
         <v>1</v>
       </c>
       <c r="F161" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G161" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -8368,7 +8852,10 @@
       <c r="N161"/>
       <c r="O161"/>
       <c r="P161" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="162">
@@ -8376,22 +8863,22 @@
         <v>48</v>
       </c>
       <c r="B162" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C162" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D162" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E162" t="n">
         <v>1</v>
       </c>
       <c r="F162" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G162" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H162" t="n">
         <v>4768</v>
@@ -8418,7 +8905,10 @@
         <v>0.431503009244388</v>
       </c>
       <c r="P162" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="163">
@@ -8426,22 +8916,22 @@
         <v>48</v>
       </c>
       <c r="B163" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C163" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D163" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E163" t="n">
         <v>1</v>
       </c>
       <c r="F163" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G163" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H163" t="n">
         <v>2561</v>
@@ -8468,7 +8958,10 @@
         <v>0.038264187108685</v>
       </c>
       <c r="P163" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="164">
@@ -8476,22 +8969,22 @@
         <v>48</v>
       </c>
       <c r="B164" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C164" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D164" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E164" t="n">
         <v>1</v>
       </c>
       <c r="F164" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G164" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H164" t="n">
         <v>678</v>
@@ -8518,7 +9011,10 @@
         <v>0.38946976613155</v>
       </c>
       <c r="P164" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -8526,22 +9022,22 @@
         <v>48</v>
       </c>
       <c r="B165" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C165" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D165" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E165" t="n">
         <v>1</v>
       </c>
       <c r="F165" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G165" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H165" t="n">
         <v>153</v>
@@ -8562,7 +9058,10 @@
       <c r="N165"/>
       <c r="O165"/>
       <c r="P165" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="166">
@@ -8570,22 +9069,22 @@
         <v>48</v>
       </c>
       <c r="B166" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C166" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D166" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E166" t="n">
         <v>1</v>
       </c>
       <c r="F166" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G166" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H166" t="n">
         <v>36</v>
@@ -8612,7 +9111,10 @@
         <v>0.969004325922695</v>
       </c>
       <c r="P166" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -8620,22 +9122,22 @@
         <v>48</v>
       </c>
       <c r="B167" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C167" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D167" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E167" t="n">
         <v>1</v>
       </c>
       <c r="F167" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G167" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H167" t="n">
         <v>2664</v>
@@ -8662,7 +9164,10 @@
         <v>0.00489236123899467</v>
       </c>
       <c r="P167" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="168">
@@ -8670,22 +9175,22 @@
         <v>48</v>
       </c>
       <c r="B168" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C168" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D168" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E168" t="n">
         <v>1</v>
       </c>
       <c r="F168" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G168" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H168" t="n">
         <v>9473</v>
@@ -8712,7 +9217,10 @@
         <v>0.00000000000000480637576416575</v>
       </c>
       <c r="P168" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="169">
@@ -8720,22 +9228,22 @@
         <v>34</v>
       </c>
       <c r="B169" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C169" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D169" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E169" t="n">
         <v>1</v>
       </c>
       <c r="F169" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G169" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H169" t="n">
         <v>21</v>
@@ -8762,7 +9270,10 @@
         <v>0.0671357480917357</v>
       </c>
       <c r="P169" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="170">
@@ -8770,22 +9281,22 @@
         <v>34</v>
       </c>
       <c r="B170" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C170" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D170" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E170" t="n">
         <v>1</v>
       </c>
       <c r="F170" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G170" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H170" t="n">
         <v>289</v>
@@ -8812,7 +9323,10 @@
         <v>0.931856627659933</v>
       </c>
       <c r="P170" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -8820,22 +9334,22 @@
         <v>34</v>
       </c>
       <c r="B171" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C171" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D171" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E171" t="n">
         <v>2</v>
       </c>
       <c r="F171" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G171" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H171" t="n">
         <v>698</v>
@@ -8862,7 +9376,10 @@
         <v>0.219275347947406</v>
       </c>
       <c r="P171" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="172">
@@ -8870,22 +9387,22 @@
         <v>34</v>
       </c>
       <c r="B172" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C172" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D172" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E172" t="n">
         <v>1</v>
       </c>
       <c r="F172" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G172" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H172" t="n">
         <v>4</v>
@@ -8906,7 +9423,10 @@
       <c r="N172"/>
       <c r="O172"/>
       <c r="P172" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="173">
@@ -8914,22 +9434,22 @@
         <v>34</v>
       </c>
       <c r="B173" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C173" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D173" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E173" t="n">
         <v>2</v>
       </c>
       <c r="F173" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G173" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H173" t="n">
         <v>3</v>
@@ -8950,7 +9470,10 @@
       <c r="N173"/>
       <c r="O173"/>
       <c r="P173" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -8958,22 +9481,22 @@
         <v>34</v>
       </c>
       <c r="B174" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C174" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D174" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E174" t="n">
         <v>1</v>
       </c>
       <c r="F174" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G174" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H174" t="n">
         <v>188</v>
@@ -8994,7 +9517,10 @@
       <c r="N174"/>
       <c r="O174"/>
       <c r="P174" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="175">
@@ -9002,22 +9528,22 @@
         <v>34</v>
       </c>
       <c r="B175" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C175" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D175" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E175" t="n">
         <v>1</v>
       </c>
       <c r="F175" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G175" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -9034,7 +9560,10 @@
       <c r="N175"/>
       <c r="O175"/>
       <c r="P175" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="176">
@@ -9042,22 +9571,22 @@
         <v>34</v>
       </c>
       <c r="B176" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C176" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D176" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E176" t="n">
         <v>2</v>
       </c>
       <c r="F176" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G176" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H176" t="n">
         <v>317</v>
@@ -9084,7 +9613,10 @@
         <v>0.283296617342563</v>
       </c>
       <c r="P176" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -9092,22 +9624,22 @@
         <v>34</v>
       </c>
       <c r="B177" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C177" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D177" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E177" t="n">
         <v>2</v>
       </c>
       <c r="F177" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G177" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H177" t="n">
         <v>746</v>
@@ -9134,7 +9666,10 @@
         <v>0.459517067678269</v>
       </c>
       <c r="P177" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -9142,22 +9677,22 @@
         <v>34</v>
       </c>
       <c r="B178" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C178" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D178" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E178" t="n">
         <v>1</v>
       </c>
       <c r="F178" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G178" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H178" t="n">
         <v>1333</v>
@@ -9184,7 +9719,10 @@
         <v>0.328421016947526</v>
       </c>
       <c r="P178" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="179">
@@ -9192,22 +9730,22 @@
         <v>35</v>
       </c>
       <c r="B179" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C179" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D179" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E179" t="n">
         <v>2</v>
       </c>
       <c r="F179" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G179" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H179" t="n">
         <v>445</v>
@@ -9234,7 +9772,10 @@
         <v>0.956357577347309</v>
       </c>
       <c r="P179" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="180">
@@ -9242,22 +9783,22 @@
         <v>35</v>
       </c>
       <c r="B180" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C180" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D180" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E180" t="n">
         <v>3</v>
       </c>
       <c r="F180" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G180" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H180" t="n">
         <v>1086</v>
@@ -9284,7 +9825,10 @@
         <v>0.00000318809996200969</v>
       </c>
       <c r="P180" t="s">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="181">
@@ -9292,22 +9836,22 @@
         <v>35</v>
       </c>
       <c r="B181" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C181" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D181" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E181" t="n">
         <v>3</v>
       </c>
       <c r="F181" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G181" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H181" t="n">
         <v>7125</v>
@@ -9334,7 +9878,10 @@
         <v>0.145713233948874</v>
       </c>
       <c r="P181" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -9342,22 +9889,22 @@
         <v>35</v>
       </c>
       <c r="B182" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C182" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D182" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E182" t="n">
         <v>1</v>
       </c>
       <c r="F182" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G182" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H182" t="n">
         <v>8</v>
@@ -9378,7 +9925,10 @@
       <c r="N182"/>
       <c r="O182"/>
       <c r="P182" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -9386,22 +9936,22 @@
         <v>35</v>
       </c>
       <c r="B183" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C183" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D183" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E183" t="n">
         <v>2</v>
       </c>
       <c r="F183" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G183" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H183" t="n">
         <v>3961</v>
@@ -9422,7 +9972,10 @@
       <c r="N183"/>
       <c r="O183"/>
       <c r="P183" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="184">
@@ -9430,22 +9983,22 @@
         <v>35</v>
       </c>
       <c r="B184" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C184" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D184" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E184" t="n">
         <v>2</v>
       </c>
       <c r="F184" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G184" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H184" t="n">
         <v>719</v>
@@ -9472,7 +10025,10 @@
         <v>0.368359158553326</v>
       </c>
       <c r="P184" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q184" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="185">
@@ -9480,22 +10036,22 @@
         <v>35</v>
       </c>
       <c r="B185" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C185" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D185" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E185" t="n">
         <v>3</v>
       </c>
       <c r="F185" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G185" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H185" t="n">
         <v>4621</v>
@@ -9522,7 +10078,10 @@
         <v>0.114315322088279</v>
       </c>
       <c r="P185" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q185" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="186">
@@ -9530,22 +10089,22 @@
         <v>35</v>
       </c>
       <c r="B186" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C186" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D186" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E186" t="n">
         <v>3</v>
       </c>
       <c r="F186" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G186" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H186" t="n">
         <v>4071</v>
@@ -9572,7 +10131,10 @@
         <v>0.196587032046407</v>
       </c>
       <c r="P186" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q186" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="187">
@@ -9580,22 +10142,22 @@
         <v>35</v>
       </c>
       <c r="B187" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C187" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D187" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E187" t="n">
         <v>1</v>
       </c>
       <c r="F187" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G187" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H187" t="n">
         <v>2602</v>
@@ -9622,7 +10184,10 @@
         <v>0.574127834383349</v>
       </c>
       <c r="P187" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q187" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="188">
@@ -9630,22 +10195,22 @@
         <v>35</v>
       </c>
       <c r="B188" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C188" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D188" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E188" t="n">
         <v>2</v>
       </c>
       <c r="F188" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G188" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H188" t="n">
         <v>519</v>
@@ -9672,7 +10237,10 @@
         <v>0.658167263124645</v>
       </c>
       <c r="P188" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q188" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="189">
@@ -9680,22 +10248,22 @@
         <v>38</v>
       </c>
       <c r="B189" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C189" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D189" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E189" t="n">
         <v>1</v>
       </c>
       <c r="F189" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G189" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H189" t="n">
         <v>222</v>
@@ -9722,7 +10290,10 @@
         <v>0.254605077074609</v>
       </c>
       <c r="P189" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q189" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="190">
@@ -9730,22 +10301,22 @@
         <v>38</v>
       </c>
       <c r="B190" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C190" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D190" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E190" t="n">
         <v>1</v>
       </c>
       <c r="F190" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G190" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H190" t="n">
         <v>113</v>
@@ -9772,7 +10343,10 @@
         <v>0.356262072866792</v>
       </c>
       <c r="P190" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q190" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="191">
@@ -9780,22 +10354,22 @@
         <v>38</v>
       </c>
       <c r="B191" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C191" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D191" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E191" t="n">
         <v>1</v>
       </c>
       <c r="F191" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G191" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H191" t="n">
         <v>222</v>
@@ -9822,7 +10396,10 @@
         <v>0.443711658627369</v>
       </c>
       <c r="P191" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q191" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="192">
@@ -9830,22 +10407,22 @@
         <v>38</v>
       </c>
       <c r="B192" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C192" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D192" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E192" t="n">
         <v>1</v>
       </c>
       <c r="F192" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G192" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H192" t="n">
         <v>221</v>
@@ -9872,7 +10449,10 @@
         <v>0.400085578534954</v>
       </c>
       <c r="P192" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="193">
@@ -9880,22 +10460,22 @@
         <v>38</v>
       </c>
       <c r="B193" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C193" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D193" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E193" t="n">
         <v>1</v>
       </c>
       <c r="F193" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G193" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H193" t="n">
         <v>222</v>
@@ -9922,7 +10502,10 @@
         <v>0.0666593236207905</v>
       </c>
       <c r="P193" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="194">
@@ -9930,22 +10513,22 @@
         <v>38</v>
       </c>
       <c r="B194" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C194" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D194" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E194" t="n">
         <v>1</v>
       </c>
       <c r="F194" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G194" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H194" t="n">
         <v>220</v>
@@ -9972,7 +10555,10 @@
         <v>0.0166190751416014</v>
       </c>
       <c r="P194" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q194" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="195">
@@ -9980,22 +10566,22 @@
         <v>39</v>
       </c>
       <c r="B195" t="s">
+        <v>119</v>
+      </c>
+      <c r="C195" t="s">
+        <v>23</v>
+      </c>
+      <c r="D195" t="s">
+        <v>19</v>
+      </c>
+      <c r="E195" t="n">
+        <v>1</v>
+      </c>
+      <c r="F195" t="s">
+        <v>117</v>
+      </c>
+      <c r="G195" t="s">
         <v>118</v>
-      </c>
-      <c r="C195" t="s">
-        <v>22</v>
-      </c>
-      <c r="D195" t="s">
-        <v>18</v>
-      </c>
-      <c r="E195" t="n">
-        <v>1</v>
-      </c>
-      <c r="F195" t="s">
-        <v>116</v>
-      </c>
-      <c r="G195" t="s">
-        <v>117</v>
       </c>
       <c r="H195" t="n">
         <v>222</v>
@@ -10022,7 +10608,10 @@
         <v>0.254605077074609</v>
       </c>
       <c r="P195" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q195" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="196">
@@ -10030,22 +10619,22 @@
         <v>39</v>
       </c>
       <c r="B196" t="s">
+        <v>119</v>
+      </c>
+      <c r="C196" t="s">
+        <v>75</v>
+      </c>
+      <c r="D196" t="s">
+        <v>19</v>
+      </c>
+      <c r="E196" t="n">
+        <v>1</v>
+      </c>
+      <c r="F196" t="s">
+        <v>117</v>
+      </c>
+      <c r="G196" t="s">
         <v>118</v>
-      </c>
-      <c r="C196" t="s">
-        <v>74</v>
-      </c>
-      <c r="D196" t="s">
-        <v>18</v>
-      </c>
-      <c r="E196" t="n">
-        <v>1</v>
-      </c>
-      <c r="F196" t="s">
-        <v>116</v>
-      </c>
-      <c r="G196" t="s">
-        <v>117</v>
       </c>
       <c r="H196" t="n">
         <v>113</v>
@@ -10072,7 +10661,10 @@
         <v>0.356262072866792</v>
       </c>
       <c r="P196" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q196" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="197">
@@ -10080,22 +10672,22 @@
         <v>39</v>
       </c>
       <c r="B197" t="s">
+        <v>119</v>
+      </c>
+      <c r="C197" t="s">
+        <v>25</v>
+      </c>
+      <c r="D197" t="s">
+        <v>19</v>
+      </c>
+      <c r="E197" t="n">
+        <v>1</v>
+      </c>
+      <c r="F197" t="s">
+        <v>117</v>
+      </c>
+      <c r="G197" t="s">
         <v>118</v>
-      </c>
-      <c r="C197" t="s">
-        <v>24</v>
-      </c>
-      <c r="D197" t="s">
-        <v>18</v>
-      </c>
-      <c r="E197" t="n">
-        <v>1</v>
-      </c>
-      <c r="F197" t="s">
-        <v>116</v>
-      </c>
-      <c r="G197" t="s">
-        <v>117</v>
       </c>
       <c r="H197" t="n">
         <v>222</v>
@@ -10122,7 +10714,10 @@
         <v>0.443711658627369</v>
       </c>
       <c r="P197" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q197" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="198">
@@ -10130,22 +10725,22 @@
         <v>39</v>
       </c>
       <c r="B198" t="s">
+        <v>119</v>
+      </c>
+      <c r="C198" t="s">
+        <v>32</v>
+      </c>
+      <c r="D198" t="s">
+        <v>19</v>
+      </c>
+      <c r="E198" t="n">
+        <v>1</v>
+      </c>
+      <c r="F198" t="s">
+        <v>117</v>
+      </c>
+      <c r="G198" t="s">
         <v>118</v>
-      </c>
-      <c r="C198" t="s">
-        <v>31</v>
-      </c>
-      <c r="D198" t="s">
-        <v>18</v>
-      </c>
-      <c r="E198" t="n">
-        <v>1</v>
-      </c>
-      <c r="F198" t="s">
-        <v>116</v>
-      </c>
-      <c r="G198" t="s">
-        <v>117</v>
       </c>
       <c r="H198" t="n">
         <v>221</v>
@@ -10172,7 +10767,10 @@
         <v>0.400085578534954</v>
       </c>
       <c r="P198" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q198" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="199">
@@ -10180,22 +10778,22 @@
         <v>39</v>
       </c>
       <c r="B199" t="s">
+        <v>119</v>
+      </c>
+      <c r="C199" t="s">
+        <v>33</v>
+      </c>
+      <c r="D199" t="s">
+        <v>19</v>
+      </c>
+      <c r="E199" t="n">
+        <v>1</v>
+      </c>
+      <c r="F199" t="s">
+        <v>117</v>
+      </c>
+      <c r="G199" t="s">
         <v>118</v>
-      </c>
-      <c r="C199" t="s">
-        <v>32</v>
-      </c>
-      <c r="D199" t="s">
-        <v>18</v>
-      </c>
-      <c r="E199" t="n">
-        <v>1</v>
-      </c>
-      <c r="F199" t="s">
-        <v>116</v>
-      </c>
-      <c r="G199" t="s">
-        <v>117</v>
       </c>
       <c r="H199" t="n">
         <v>222</v>
@@ -10222,7 +10820,10 @@
         <v>0.0666593236207905</v>
       </c>
       <c r="P199" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q199" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="200">
@@ -10230,22 +10831,22 @@
         <v>39</v>
       </c>
       <c r="B200" t="s">
+        <v>119</v>
+      </c>
+      <c r="C200" t="s">
+        <v>47</v>
+      </c>
+      <c r="D200" t="s">
+        <v>19</v>
+      </c>
+      <c r="E200" t="n">
+        <v>1</v>
+      </c>
+      <c r="F200" t="s">
+        <v>117</v>
+      </c>
+      <c r="G200" t="s">
         <v>118</v>
-      </c>
-      <c r="C200" t="s">
-        <v>46</v>
-      </c>
-      <c r="D200" t="s">
-        <v>18</v>
-      </c>
-      <c r="E200" t="n">
-        <v>1</v>
-      </c>
-      <c r="F200" t="s">
-        <v>116</v>
-      </c>
-      <c r="G200" t="s">
-        <v>117</v>
       </c>
       <c r="H200" t="n">
         <v>220</v>
@@ -10272,7 +10873,10 @@
         <v>0.0166190751416014</v>
       </c>
       <c r="P200" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="201">
@@ -10280,22 +10884,22 @@
         <v>40</v>
       </c>
       <c r="B201" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C201" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D201" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E201" t="n">
         <v>1</v>
       </c>
       <c r="F201" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G201" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H201" t="n">
         <v>133</v>
@@ -10322,7 +10926,10 @@
         <v>0.0740357853759614</v>
       </c>
       <c r="P201" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q201" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="202">
@@ -10330,22 +10937,22 @@
         <v>40</v>
       </c>
       <c r="B202" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C202" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D202" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E202" t="n">
         <v>2</v>
       </c>
       <c r="F202" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G202" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H202" t="n">
         <v>460</v>
@@ -10372,7 +10979,10 @@
         <v>0.485492239666146</v>
       </c>
       <c r="P202" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q202" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="203">
@@ -10380,22 +10990,22 @@
         <v>40</v>
       </c>
       <c r="B203" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C203" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D203" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E203" t="n">
         <v>1</v>
       </c>
       <c r="F203" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G203" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H203" t="n">
         <v>76</v>
@@ -10416,7 +11026,10 @@
       <c r="N203"/>
       <c r="O203"/>
       <c r="P203" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="Q203" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="204">
@@ -10424,22 +11037,22 @@
         <v>40</v>
       </c>
       <c r="B204" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C204" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D204" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E204" t="n">
         <v>2</v>
       </c>
       <c r="F204" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G204" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H204" t="n">
         <v>432</v>
@@ -10466,7 +11079,10 @@
         <v>0.819593916025816</v>
       </c>
       <c r="P204" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q204" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="205">
@@ -10474,22 +11090,22 @@
         <v>40</v>
       </c>
       <c r="B205" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C205" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D205" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E205" t="n">
         <v>2</v>
       </c>
       <c r="F205" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G205" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H205" t="n">
         <v>841</v>
@@ -10516,7 +11132,10 @@
         <v>0.131535964561105</v>
       </c>
       <c r="P205" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q205" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="206">
@@ -10524,22 +11143,22 @@
         <v>40</v>
       </c>
       <c r="B206" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C206" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D206" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E206" t="n">
         <v>1</v>
       </c>
       <c r="F206" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G206" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H206" t="n">
         <v>413</v>
@@ -10566,7 +11185,10 @@
         <v>0.150214626938448</v>
       </c>
       <c r="P206" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q206" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="207">
@@ -10574,22 +11196,22 @@
         <v>41</v>
       </c>
       <c r="B207" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C207" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D207" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E207" t="n">
         <v>1</v>
       </c>
       <c r="F207" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G207" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H207" t="n">
         <v>243</v>
@@ -10616,7 +11238,10 @@
         <v>0.831389753629501</v>
       </c>
       <c r="P207" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q207" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="208">
@@ -10624,22 +11249,22 @@
         <v>41</v>
       </c>
       <c r="B208" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C208" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D208" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E208" t="n">
         <v>1</v>
       </c>
       <c r="F208" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G208" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H208" t="n">
         <v>53</v>
@@ -10666,7 +11291,10 @@
         <v>0.503221347188028</v>
       </c>
       <c r="P208" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="209">
@@ -10674,22 +11302,22 @@
         <v>41</v>
       </c>
       <c r="B209" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C209" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D209" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E209" t="n">
         <v>1</v>
       </c>
       <c r="F209" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G209" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H209" t="n">
         <v>21</v>
@@ -10710,7 +11338,10 @@
       <c r="N209"/>
       <c r="O209"/>
       <c r="P209" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="210">
@@ -10718,22 +11349,22 @@
         <v>41</v>
       </c>
       <c r="B210" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C210" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D210" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E210" t="n">
         <v>1</v>
       </c>
       <c r="F210" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G210" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H210" t="n">
         <v>90</v>
@@ -10760,7 +11391,10 @@
         <v>0.256698903785388</v>
       </c>
       <c r="P210" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="211">
@@ -10768,22 +11402,22 @@
         <v>41</v>
       </c>
       <c r="B211" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C211" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D211" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E211" t="n">
         <v>1</v>
       </c>
       <c r="F211" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G211" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H211" t="n">
         <v>865</v>
@@ -10810,7 +11444,10 @@
         <v>0.687476157247382</v>
       </c>
       <c r="P211" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q211" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="212">
@@ -10818,22 +11455,22 @@
         <v>43</v>
       </c>
       <c r="B212" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C212" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D212" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E212" t="n">
         <v>1</v>
       </c>
       <c r="F212" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G212" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H212" t="n">
         <v>1328</v>
@@ -10860,7 +11497,10 @@
         <v>0.103428972363119</v>
       </c>
       <c r="P212" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="213">
@@ -10868,22 +11508,22 @@
         <v>43</v>
       </c>
       <c r="B213" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C213" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D213" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E213" t="n">
         <v>1</v>
       </c>
       <c r="F213" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G213" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H213" t="n">
         <v>1631</v>
@@ -10910,7 +11550,10 @@
         <v>0.1437116811893</v>
       </c>
       <c r="P213" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q213" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="214">
@@ -10918,22 +11561,22 @@
         <v>43</v>
       </c>
       <c r="B214" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C214" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D214" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E214" t="n">
         <v>1</v>
       </c>
       <c r="F214" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G214" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H214" t="n">
         <v>503</v>
@@ -10960,7 +11603,10 @@
         <v>0.044702954339368</v>
       </c>
       <c r="P214" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="215">
@@ -10968,22 +11614,22 @@
         <v>43</v>
       </c>
       <c r="B215" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C215" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D215" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E215" t="n">
         <v>1</v>
       </c>
       <c r="F215" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G215" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H215" t="n">
         <v>31</v>
@@ -11004,7 +11650,10 @@
       <c r="N215"/>
       <c r="O215"/>
       <c r="P215" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="Q215" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="216">
@@ -11012,22 +11661,22 @@
         <v>43</v>
       </c>
       <c r="B216" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C216" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D216" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E216" t="n">
         <v>1</v>
       </c>
       <c r="F216" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G216" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H216" t="n">
         <v>144</v>
@@ -11054,7 +11703,10 @@
         <v>0.664093711204479</v>
       </c>
       <c r="P216" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="217">
@@ -11062,22 +11714,22 @@
         <v>43</v>
       </c>
       <c r="B217" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C217" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D217" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E217" t="n">
         <v>1</v>
       </c>
       <c r="F217" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G217" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H217" t="n">
         <v>747</v>
@@ -11104,7 +11756,10 @@
         <v>0.511251330606643</v>
       </c>
       <c r="P217" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="218">
@@ -11112,22 +11767,22 @@
         <v>43</v>
       </c>
       <c r="B218" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C218" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D218" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E218" t="n">
         <v>1</v>
       </c>
       <c r="F218" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G218" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H218" t="n">
         <v>3260</v>
@@ -11154,7 +11809,10 @@
         <v>0.249088171024273</v>
       </c>
       <c r="P218" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q218" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="219">
@@ -11162,22 +11820,22 @@
         <v>44</v>
       </c>
       <c r="B219" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C219" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D219" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E219" t="n">
         <v>1</v>
       </c>
       <c r="F219" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G219" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H219" t="n">
         <v>16</v>
@@ -11198,7 +11856,10 @@
       <c r="N219"/>
       <c r="O219"/>
       <c r="P219" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q219" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="220">
@@ -11206,22 +11867,22 @@
         <v>44</v>
       </c>
       <c r="B220" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C220" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D220" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E220" t="n">
         <v>1</v>
       </c>
       <c r="F220" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G220" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H220" t="n">
         <v>743</v>
@@ -11248,7 +11909,10 @@
         <v>0.00417574791793629</v>
       </c>
       <c r="P220" t="s">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="Q220" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="221">
@@ -11256,22 +11920,22 @@
         <v>44</v>
       </c>
       <c r="B221" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C221" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D221" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E221" t="n">
         <v>1</v>
       </c>
       <c r="F221" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G221" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H221" t="n">
         <v>987</v>
@@ -11292,7 +11956,10 @@
       <c r="N221"/>
       <c r="O221"/>
       <c r="P221" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="222">
@@ -11300,22 +11967,22 @@
         <v>44</v>
       </c>
       <c r="B222" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C222" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D222" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E222" t="n">
         <v>1</v>
       </c>
       <c r="F222" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G222" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H222" t="n">
         <v>2</v>
@@ -11336,7 +12003,10 @@
       <c r="N222"/>
       <c r="O222"/>
       <c r="P222" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="223">
@@ -11344,22 +12014,22 @@
         <v>44</v>
       </c>
       <c r="B223" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C223" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D223" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E223" t="n">
         <v>1</v>
       </c>
       <c r="F223" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G223" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H223" t="n">
         <v>559</v>
@@ -11386,7 +12056,10 @@
         <v>0.708114476390101</v>
       </c>
       <c r="P223" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q223" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="224">
@@ -11394,22 +12067,22 @@
         <v>44</v>
       </c>
       <c r="B224" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C224" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D224" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E224" t="n">
         <v>1</v>
       </c>
       <c r="F224" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G224" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H224" t="n">
         <v>1707</v>
@@ -11436,7 +12109,10 @@
         <v>0.446908276330308</v>
       </c>
       <c r="P224" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="Q224" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="225">
@@ -11444,22 +12120,22 @@
         <v>44</v>
       </c>
       <c r="B225" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C225" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D225" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E225" t="n">
         <v>1</v>
       </c>
       <c r="F225" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G225" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H225" t="n">
         <v>3</v>
@@ -11480,7 +12156,10 @@
       <c r="N225"/>
       <c r="O225"/>
       <c r="P225" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Q225" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/SAV/output/website/SAV_BBpct_LMEresults_All.xlsx
+++ b/SAV/output/website/SAV_BBpct_LMEresults_All.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="128">
   <si>
     <t xml:space="preserve">AreaID</t>
   </si>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">Banana River Aquatic Preserve</t>
   </si>
   <si>
-    <t xml:space="preserve">Seagrass (SJRWMD)</t>
+    <t xml:space="preserve">Indian River Lagoon fixed seagrass transects (SJRWMD)</t>
   </si>
   <si>
     <t xml:space="preserve">3013</t>
@@ -239,6 +239,12 @@
     <t xml:space="preserve">571</t>
   </si>
   <si>
+    <t xml:space="preserve">Estero Bay Seagrass Monitoring, SCCF Seagrass Surveys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">571, 3015</t>
+  </si>
+  <si>
     <t xml:space="preserve">Paddle grass</t>
   </si>
   <si>
@@ -284,7 +290,7 @@
     <t xml:space="preserve">Jensen Beach to Jupiter Inlet Aquatic Preserve</t>
   </si>
   <si>
-    <t xml:space="preserve">Loxahatchee River District Bi-Monthly Seagrass Monitoring, Seagrass (SJRWMD)</t>
+    <t xml:space="preserve">Indian River Lagoon fixed seagrass transects (SJRWMD), Loxahatchee River District Bi-Monthly Seagrass Monitoring</t>
   </si>
   <si>
     <t xml:space="preserve">3013, 3017</t>
@@ -311,7 +317,7 @@
     <t xml:space="preserve">Loxahatchee River-Lake Worth Creek Aquatic Preserve</t>
   </si>
   <si>
-    <t xml:space="preserve">Loxahatchee River District Bi-Monthly Seagrass Monitoring, Loxahatchee River District Landscape-Scale Seagrass Mapping Area, Seagrass (SJRWMD)</t>
+    <t xml:space="preserve">Indian River Lagoon fixed seagrass transects (SJRWMD), Loxahatchee River District Bi-Monthly Seagrass Monitoring, Loxahatchee River District Landscape-Scale Seagrass Mapping Area</t>
   </si>
   <si>
     <t xml:space="preserve">3013, 3017, 10001</t>
@@ -813,28 +819,28 @@
         <v>21</v>
       </c>
       <c r="H2" t="n">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J2" t="n">
         <v>2009</v>
       </c>
       <c r="K2" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="L2" t="b">
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>79.4024458379973</v>
+        <v>61.8670400816717</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.3562408050717</v>
+        <v>-1.69540171897956</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0273462910086319</v>
+        <v>0.0222067261630777</v>
       </c>
       <c r="P2" t="s">
         <v>22</v>
@@ -866,28 +872,28 @@
         <v>21</v>
       </c>
       <c r="H3" t="n">
-        <v>263</v>
+        <v>288</v>
       </c>
       <c r="I3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J3" t="n">
         <v>2008</v>
       </c>
       <c r="K3" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="L3" t="b">
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>29.7876385227131</v>
+        <v>29.3017112673545</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.499366822442305</v>
+        <v>-0.400485147470436</v>
       </c>
       <c r="O3" t="n">
-        <v>0.471691483034255</v>
+        <v>0.485400870121798</v>
       </c>
       <c r="P3" t="s">
         <v>24</v>
@@ -966,16 +972,16 @@
         <v>21</v>
       </c>
       <c r="H5" t="n">
-        <v>1620</v>
+        <v>1638</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J5" t="n">
         <v>2009</v>
       </c>
       <c r="K5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="L5" t="b">
         <v>1</v>
@@ -1060,34 +1066,34 @@
         <v>21</v>
       </c>
       <c r="H7" t="n">
-        <v>800</v>
+        <v>828</v>
       </c>
       <c r="I7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J7" t="n">
         <v>2008</v>
       </c>
       <c r="K7" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="L7" t="b">
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>47.8583559827204</v>
+        <v>41.9506319059467</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.22814510144716</v>
+        <v>-0.955640214830587</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0253567825587495</v>
+        <v>0.0807612636480904</v>
       </c>
       <c r="P7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1113,28 +1119,28 @@
         <v>21</v>
       </c>
       <c r="H8" t="n">
-        <v>686</v>
+        <v>724</v>
       </c>
       <c r="I8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J8" t="n">
         <v>2008</v>
       </c>
       <c r="K8" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="L8" t="b">
         <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>30.9690281919503</v>
+        <v>26.30420485164</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.453089114504738</v>
+        <v>-0.202050947881108</v>
       </c>
       <c r="O8" t="n">
-        <v>0.37785757960882</v>
+        <v>0.71873916037683</v>
       </c>
       <c r="P8" t="s">
         <v>24</v>
@@ -1166,28 +1172,28 @@
         <v>36</v>
       </c>
       <c r="H9" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
         <v>2003</v>
       </c>
       <c r="K9" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="L9" t="b">
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>84.8219501837185</v>
+        <v>82.0571655916211</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.63095713712759</v>
+        <v>-2.49001700631657</v>
       </c>
       <c r="O9" t="n">
-        <v>0.00143440332984336</v>
+        <v>0.00210369550047683</v>
       </c>
       <c r="P9" t="s">
         <v>22</v>
@@ -1219,28 +1225,28 @@
         <v>38</v>
       </c>
       <c r="H10" t="n">
-        <v>248</v>
+        <v>289</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J10" t="n">
         <v>2008</v>
       </c>
       <c r="K10" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="L10" t="b">
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>31.6899376314409</v>
+        <v>44.9166102074163</v>
       </c>
       <c r="N10" t="n">
-        <v>0.916393045143222</v>
+        <v>0.395873940180509</v>
       </c>
       <c r="O10" t="n">
-        <v>0.487611201074338</v>
+        <v>0.701805860175166</v>
       </c>
       <c r="P10" t="s">
         <v>24</v>
@@ -1272,16 +1278,16 @@
         <v>36</v>
       </c>
       <c r="H11" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
         <v>2003</v>
       </c>
       <c r="K11" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="L11" t="b">
         <v>1</v>
@@ -1366,28 +1372,28 @@
         <v>36</v>
       </c>
       <c r="H13" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="I13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J13" t="n">
         <v>2003</v>
       </c>
       <c r="K13" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="L13" t="b">
         <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>60.3086992409572</v>
+        <v>61.414822682012</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.83629600396035</v>
+        <v>-1.76924757717076</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0314622501331645</v>
+        <v>0.0180442767281392</v>
       </c>
       <c r="P13" t="s">
         <v>22</v>
@@ -1419,28 +1425,28 @@
         <v>21</v>
       </c>
       <c r="H14" t="n">
-        <v>1021</v>
+        <v>1108</v>
       </c>
       <c r="I14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J14" t="n">
         <v>2008</v>
       </c>
       <c r="K14" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="L14" t="b">
         <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>42.9808695316888</v>
+        <v>39.254401740276</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.244492117921787</v>
+        <v>-0.106280283066863</v>
       </c>
       <c r="O14" t="n">
-        <v>0.726844468394392</v>
+        <v>0.862285504874476</v>
       </c>
       <c r="P14" t="s">
         <v>24</v>
@@ -1519,16 +1525,16 @@
         <v>41</v>
       </c>
       <c r="H16" t="n">
-        <v>906</v>
+        <v>915</v>
       </c>
       <c r="I16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J16" t="n">
         <v>2003</v>
       </c>
       <c r="K16" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="L16" t="b">
         <v>1</v>
@@ -1675,13 +1681,13 @@
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>32.7066091430685</v>
+        <v>32.7066091430681</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.27421024612962</v>
+        <v>-1.2742102461296</v>
       </c>
       <c r="O19" t="n">
-        <v>0.00000000000000000000000000234034760816071</v>
+        <v>0.00000000000000000000000000234034760816984</v>
       </c>
       <c r="P19" t="s">
         <v>22</v>
@@ -1728,13 +1734,13 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>0.499717286812712</v>
+        <v>0.4997172868127</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0130908444524584</v>
+        <v>-0.0130908444524576</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1417157133767</v>
+        <v>0.141715713376745</v>
       </c>
       <c r="P20" t="s">
         <v>24</v>
@@ -1781,13 +1787,13 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>7.79828345677389</v>
+        <v>7.79828345529968</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.344328370167375</v>
+        <v>-0.344328370066705</v>
       </c>
       <c r="O21" t="n">
-        <v>0.000230385165200919</v>
+        <v>0.000230385164633635</v>
       </c>
       <c r="P21" t="s">
         <v>22</v>
@@ -1834,13 +1840,13 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0924090068810235</v>
+        <v>0.0924090060103735</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.00286056085647991</v>
+        <v>-0.00286056085511069</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0682854623978636</v>
+        <v>0.0682853088905076</v>
       </c>
       <c r="P22" t="s">
         <v>24</v>
@@ -1934,13 +1940,13 @@
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>39.0719765042805</v>
+        <v>39.0719765042826</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.51988946018712</v>
+        <v>-1.5198894601872</v>
       </c>
       <c r="O24" t="n">
-        <v>0.00000000000000000016644362385066</v>
+        <v>0.000000000000000000166443623849838</v>
       </c>
       <c r="P24" t="s">
         <v>22</v>
@@ -1972,28 +1978,28 @@
         <v>49</v>
       </c>
       <c r="H25" t="n">
-        <v>3182</v>
+        <v>3656</v>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J25" t="n">
         <v>2000</v>
       </c>
       <c r="K25" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L25" t="b">
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>5.4539122005051</v>
+        <v>9.02603039720952</v>
       </c>
       <c r="N25" t="n">
-        <v>0.812732920657474</v>
+        <v>0.660207608606611</v>
       </c>
       <c r="O25" t="n">
-        <v>0.000000874243938426819</v>
+        <v>0.00000245764999882379</v>
       </c>
       <c r="P25" t="s">
         <v>50</v>
@@ -2025,28 +2031,28 @@
         <v>49</v>
       </c>
       <c r="H26" t="n">
-        <v>2552</v>
+        <v>2885</v>
       </c>
       <c r="I26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J26" t="n">
         <v>2000</v>
       </c>
       <c r="K26" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L26" t="b">
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>24.8297465486173</v>
+        <v>25.7840495989877</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.431455084497684</v>
+        <v>-0.490042927509</v>
       </c>
       <c r="O26" t="n">
-        <v>0.000128012104588442</v>
+        <v>0.00000102934983611883</v>
       </c>
       <c r="P26" t="s">
         <v>22</v>
@@ -2078,28 +2084,28 @@
         <v>49</v>
       </c>
       <c r="H27" t="n">
-        <v>848</v>
+        <v>910</v>
       </c>
       <c r="I27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J27" t="n">
         <v>2000</v>
       </c>
       <c r="K27" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L27" t="b">
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>18.552789337222</v>
+        <v>20.6226433661185</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.134772661241874</v>
+        <v>-0.246282710245002</v>
       </c>
       <c r="O27" t="n">
-        <v>0.308991284377083</v>
+        <v>0.0528721461070993</v>
       </c>
       <c r="P27" t="s">
         <v>24</v>
@@ -2131,16 +2137,16 @@
         <v>52</v>
       </c>
       <c r="H28" t="n">
-        <v>345</v>
+        <v>403</v>
       </c>
       <c r="I28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J28" t="n">
         <v>2004</v>
       </c>
       <c r="K28" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L28" t="b">
         <v>1</v>
@@ -2178,28 +2184,28 @@
         <v>49</v>
       </c>
       <c r="H29" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="I29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J29" t="n">
         <v>2001</v>
       </c>
       <c r="K29" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L29" t="b">
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>25.9396728282327</v>
+        <v>24.4141397488665</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.279328433842235</v>
+        <v>-0.1700483580095</v>
       </c>
       <c r="O29" t="n">
-        <v>0.598233856707755</v>
+        <v>0.708418893726101</v>
       </c>
       <c r="P29" t="s">
         <v>24</v>
@@ -2231,28 +2237,28 @@
         <v>49</v>
       </c>
       <c r="H30" t="n">
-        <v>5411</v>
+        <v>5960</v>
       </c>
       <c r="I30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J30" t="n">
         <v>2000</v>
       </c>
       <c r="K30" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L30" t="b">
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>35.9453957791293</v>
+        <v>37.7908936472154</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.42717713570092</v>
+        <v>-0.526720216977605</v>
       </c>
       <c r="O30" t="n">
-        <v>0.0000535982091523411</v>
+        <v>0.00000202484255218162</v>
       </c>
       <c r="P30" t="s">
         <v>22</v>
@@ -2284,28 +2290,28 @@
         <v>49</v>
       </c>
       <c r="H31" t="n">
-        <v>12141</v>
+        <v>13619</v>
       </c>
       <c r="I31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J31" t="n">
         <v>2000</v>
       </c>
       <c r="K31" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L31" t="b">
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>42.5154354067174</v>
+        <v>42.6812829669626</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.481472297581496</v>
+        <v>-0.493620517719675</v>
       </c>
       <c r="O31" t="n">
-        <v>0.000000000604370552252266</v>
+        <v>0.0000000000532339843320681</v>
       </c>
       <c r="P31" t="s">
         <v>22</v>
@@ -2352,13 +2358,13 @@
         <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.0338584442431049</v>
+        <v>-0.0338584432755453</v>
       </c>
       <c r="N32" t="n">
-        <v>0.0096340617960582</v>
+        <v>0.00963406173230785</v>
       </c>
       <c r="O32" t="n">
-        <v>0.102881423110622</v>
+        <v>0.102881422519506</v>
       </c>
       <c r="P32" t="s">
         <v>24</v>
@@ -2405,13 +2411,13 @@
         <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>10.7299717287469</v>
+        <v>10.7299713245486</v>
       </c>
       <c r="N33" t="n">
-        <v>-0.313686425316573</v>
+        <v>-0.313686411470303</v>
       </c>
       <c r="O33" t="n">
-        <v>0.000000494818421991087</v>
+        <v>0.000000494820630094203</v>
       </c>
       <c r="P33" t="s">
         <v>22</v>
@@ -2458,13 +2464,13 @@
         <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>8.20630451675424</v>
+        <v>8.20630468626299</v>
       </c>
       <c r="N34" t="n">
-        <v>-0.23154800185622</v>
+        <v>-0.23154801133696</v>
       </c>
       <c r="O34" t="n">
-        <v>0.00000610770243154178</v>
+        <v>0.00000610770297038296</v>
       </c>
       <c r="P34" t="s">
         <v>22</v>
@@ -2511,13 +2517,13 @@
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>0.668645792189909</v>
+        <v>0.668645791371325</v>
       </c>
       <c r="N35" t="n">
-        <v>-0.022717678236175</v>
+        <v>-0.0227176781855818</v>
       </c>
       <c r="O35" t="n">
-        <v>0.00940484396388284</v>
+        <v>0.00940484342557694</v>
       </c>
       <c r="P35" t="s">
         <v>22</v>
@@ -2611,13 +2617,13 @@
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>14.7500249367134</v>
+        <v>14.750018148186</v>
       </c>
       <c r="N37" t="n">
-        <v>-0.370260581585335</v>
+        <v>-0.370260283556471</v>
       </c>
       <c r="O37" t="n">
-        <v>0.000281397786247974</v>
+        <v>0.000281401961232601</v>
       </c>
       <c r="P37" t="s">
         <v>22</v>
@@ -2664,13 +2670,13 @@
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>44.9650111183382</v>
+        <v>44.9650093427713</v>
       </c>
       <c r="N38" t="n">
-        <v>-1.37407678080075</v>
+        <v>-1.37407669814343</v>
       </c>
       <c r="O38" t="n">
-        <v>0.000000000000000000000000000125679599318174</v>
+        <v>0.000000000000000000000000000125685688976499</v>
       </c>
       <c r="P38" t="s">
         <v>22</v>
@@ -2717,13 +2723,13 @@
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>51.2374696438551</v>
+        <v>51.2374653354048</v>
       </c>
       <c r="N39" t="n">
-        <v>-0.206500310474665</v>
+        <v>-0.206500161917888</v>
       </c>
       <c r="O39" t="n">
-        <v>0.256494287264958</v>
+        <v>0.256494342101214</v>
       </c>
       <c r="P39" t="s">
         <v>24</v>
@@ -2770,13 +2776,13 @@
         <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>17.1355555254218</v>
+        <v>17.1357640841417</v>
       </c>
       <c r="N40" t="n">
-        <v>0.607696990107161</v>
+        <v>0.607687622912365</v>
       </c>
       <c r="O40" t="n">
-        <v>0.00122802477495601</v>
+        <v>0.00122838987639503</v>
       </c>
       <c r="P40" t="s">
         <v>50</v>
@@ -2855,28 +2861,28 @@
         <v>66</v>
       </c>
       <c r="H42" t="n">
-        <v>1352</v>
+        <v>1416</v>
       </c>
       <c r="I42" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J42" t="n">
         <v>1998</v>
       </c>
       <c r="K42" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L42" t="b">
         <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>47.9776204495858</v>
+        <v>49.7334156383442</v>
       </c>
       <c r="N42" t="n">
-        <v>-0.198288963007626</v>
+        <v>-0.345887959455809</v>
       </c>
       <c r="O42" t="n">
-        <v>0.377609133307038</v>
+        <v>0.054949956337579</v>
       </c>
       <c r="P42" t="s">
         <v>24</v>
@@ -2908,16 +2914,16 @@
         <v>64</v>
       </c>
       <c r="H43" t="n">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="I43" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J43" t="n">
         <v>1998</v>
       </c>
       <c r="K43" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L43" t="b">
         <v>1</v>
@@ -2955,16 +2961,16 @@
         <v>66</v>
       </c>
       <c r="H44" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I44" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J44" t="n">
         <v>2003</v>
       </c>
       <c r="K44" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L44" t="b">
         <v>1</v>
@@ -3002,28 +3008,28 @@
         <v>66</v>
       </c>
       <c r="H45" t="n">
-        <v>1014</v>
+        <v>1070</v>
       </c>
       <c r="I45" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J45" t="n">
         <v>1998</v>
       </c>
       <c r="K45" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L45" t="b">
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>52.3267182771389</v>
+        <v>54.1082455390122</v>
       </c>
       <c r="N45" t="n">
-        <v>-0.496461552365028</v>
+        <v>-0.625190541315996</v>
       </c>
       <c r="O45" t="n">
-        <v>0.0491914585084037</v>
+        <v>0.0152358549755163</v>
       </c>
       <c r="P45" t="s">
         <v>22</v>
@@ -3149,34 +3155,34 @@
         <v>70</v>
       </c>
       <c r="H48" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="I48" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J48" t="n">
         <v>2003</v>
       </c>
       <c r="K48" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L48" t="b">
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>-11.4840654985292</v>
+        <v>-4.72683972225375</v>
       </c>
       <c r="N48" t="n">
-        <v>1.24661532602356</v>
+        <v>0.870495902508964</v>
       </c>
       <c r="O48" t="n">
-        <v>0.0166233464754912</v>
+        <v>0.116351897688827</v>
       </c>
       <c r="P48" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="Q48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3202,28 +3208,28 @@
         <v>70</v>
       </c>
       <c r="H49" t="n">
-        <v>416</v>
+        <v>433</v>
       </c>
       <c r="I49" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J49" t="n">
         <v>1998</v>
       </c>
       <c r="K49" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L49" t="b">
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>21.9823058362862</v>
+        <v>22.3272149556663</v>
       </c>
       <c r="N49" t="n">
-        <v>-0.330017781273232</v>
+        <v>-0.347925750606938</v>
       </c>
       <c r="O49" t="n">
-        <v>0.348779258545112</v>
+        <v>0.284714246946418</v>
       </c>
       <c r="P49" t="s">
         <v>24</v>
@@ -3255,16 +3261,16 @@
         <v>70</v>
       </c>
       <c r="H50" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="I50" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J50" t="n">
         <v>1998</v>
       </c>
       <c r="K50" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L50" t="b">
         <v>1</v>
@@ -3302,28 +3308,28 @@
         <v>70</v>
       </c>
       <c r="H51" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="I51" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J51" t="n">
         <v>1998</v>
       </c>
       <c r="K51" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L51" t="b">
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>31.3183097469319</v>
+        <v>32.8694542734786</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.164982613440194</v>
+        <v>-0.248140239152269</v>
       </c>
       <c r="O51" t="n">
-        <v>0.83124841287508</v>
+        <v>0.743000135665345</v>
       </c>
       <c r="P51" t="s">
         <v>24</v>
@@ -3355,28 +3361,28 @@
         <v>70</v>
       </c>
       <c r="H52" t="n">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="I52" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J52" t="n">
         <v>1998</v>
       </c>
       <c r="K52" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L52" t="b">
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>24.5774894460146</v>
+        <v>25.4908878025848</v>
       </c>
       <c r="N52" t="n">
-        <v>0.21849050167077</v>
+        <v>0.161060115764253</v>
       </c>
       <c r="O52" t="n">
-        <v>0.483437203484199</v>
+        <v>0.616556500169603</v>
       </c>
       <c r="P52" t="s">
         <v>24</v>
@@ -3408,28 +3414,28 @@
         <v>70</v>
       </c>
       <c r="H53" t="n">
-        <v>666</v>
+        <v>701</v>
       </c>
       <c r="I53" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J53" t="n">
         <v>1998</v>
       </c>
       <c r="K53" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L53" t="b">
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>31.2028301375394</v>
+        <v>32.7201300323958</v>
       </c>
       <c r="N53" t="n">
-        <v>-0.394610092902706</v>
+        <v>-0.483596161589513</v>
       </c>
       <c r="O53" t="n">
-        <v>0.320530874580492</v>
+        <v>0.206201685323354</v>
       </c>
       <c r="P53" t="s">
         <v>24</v>
@@ -3555,34 +3561,34 @@
         <v>64</v>
       </c>
       <c r="H56" t="n">
-        <v>572</v>
+        <v>608</v>
       </c>
       <c r="I56" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J56" t="n">
         <v>2000</v>
       </c>
       <c r="K56" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L56" t="b">
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>19.2210209918651</v>
+        <v>20.6852555147252</v>
       </c>
       <c r="N56" t="n">
-        <v>0.529458794026777</v>
+        <v>0.416179639720273</v>
       </c>
       <c r="O56" t="n">
-        <v>0.0159141893678147</v>
+        <v>0.0518948289563447</v>
       </c>
       <c r="P56" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="Q56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3608,16 +3614,16 @@
         <v>64</v>
       </c>
       <c r="H57" t="n">
-        <v>387</v>
+        <v>406</v>
       </c>
       <c r="I57" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J57" t="n">
         <v>2000</v>
       </c>
       <c r="K57" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L57" t="b">
         <v>1</v>
@@ -3655,34 +3661,34 @@
         <v>64</v>
       </c>
       <c r="H58" t="n">
-        <v>392</v>
+        <v>430</v>
       </c>
       <c r="I58" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J58" t="n">
         <v>2000</v>
       </c>
       <c r="K58" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L58" t="b">
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>35.7777215434534</v>
+        <v>39.6603299141651</v>
       </c>
       <c r="N58" t="n">
-        <v>0.825668344603955</v>
+        <v>0.574146466107835</v>
       </c>
       <c r="O58" t="n">
-        <v>0.0760969879640776</v>
+        <v>0.019774410151489</v>
       </c>
       <c r="P58" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3708,28 +3714,28 @@
         <v>64</v>
       </c>
       <c r="H59" t="n">
-        <v>470</v>
+        <v>508</v>
       </c>
       <c r="I59" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J59" t="n">
         <v>2000</v>
       </c>
       <c r="K59" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L59" t="b">
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>16.2416047164727</v>
+        <v>17.8673686086597</v>
       </c>
       <c r="N59" t="n">
-        <v>0.175117461352373</v>
+        <v>0.0496471849201271</v>
       </c>
       <c r="O59" t="n">
-        <v>0.424807329805699</v>
+        <v>0.801693364075803</v>
       </c>
       <c r="P59" t="s">
         <v>24</v>
@@ -3823,13 +3829,13 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>8.13470493366117</v>
+        <v>8.13469688040933</v>
       </c>
       <c r="N61" t="n">
-        <v>-0.201984889529685</v>
+        <v>-0.201984410597739</v>
       </c>
       <c r="O61" t="n">
-        <v>0.386180086961865</v>
+        <v>0.386181038725073</v>
       </c>
       <c r="P61" t="s">
         <v>24</v>
@@ -3861,28 +3867,28 @@
         <v>74</v>
       </c>
       <c r="H62" t="n">
-        <v>486</v>
+        <v>517</v>
       </c>
       <c r="I62" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J62" t="n">
         <v>2002</v>
       </c>
       <c r="K62" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L62" t="b">
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>20.0363360880779</v>
+        <v>21.4156855594513</v>
       </c>
       <c r="N62" t="n">
-        <v>-0.287623336006212</v>
+        <v>-0.361722016273873</v>
       </c>
       <c r="O62" t="n">
-        <v>0.378522951480508</v>
+        <v>0.234498528961476</v>
       </c>
       <c r="P62" t="s">
         <v>24</v>
@@ -3905,37 +3911,37 @@
         <v>19</v>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F63" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G63" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H63" t="n">
-        <v>848</v>
+        <v>889</v>
       </c>
       <c r="I63" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J63" t="n">
         <v>2002</v>
       </c>
       <c r="K63" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L63" t="b">
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>37.0739399502456</v>
+        <v>36.996513155134</v>
       </c>
       <c r="N63" t="n">
-        <v>-0.830567730486169</v>
+        <v>-0.824863486637636</v>
       </c>
       <c r="O63" t="n">
-        <v>0.0010585081754943</v>
+        <v>0.00116053800398161</v>
       </c>
       <c r="P63" t="s">
         <v>22</v>
@@ -3952,7 +3958,7 @@
         <v>72</v>
       </c>
       <c r="C64" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D64" t="s">
         <v>19</v>
@@ -3982,13 +3988,13 @@
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>18.8993364617153</v>
+        <v>18.8993364938145</v>
       </c>
       <c r="N64" t="n">
-        <v>-0.0551538224617119</v>
+        <v>-0.0551537988426763</v>
       </c>
       <c r="O64" t="n">
-        <v>0.92219735068256</v>
+        <v>0.922197384115008</v>
       </c>
       <c r="P64" t="s">
         <v>24</v>
@@ -4020,16 +4026,16 @@
         <v>74</v>
       </c>
       <c r="H65" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I65" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J65" t="n">
         <v>2002</v>
       </c>
       <c r="K65" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="L65" t="b">
         <v>1</v>
@@ -4067,16 +4073,16 @@
         <v>74</v>
       </c>
       <c r="H66" t="n">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="I66" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J66" t="n">
         <v>2002</v>
       </c>
       <c r="K66" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L66" t="b">
         <v>1</v>
@@ -4129,13 +4135,13 @@
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>26.9390749103907</v>
+        <v>26.9390608632158</v>
       </c>
       <c r="N67" t="n">
-        <v>-0.972109067084369</v>
+        <v>-0.972108403399248</v>
       </c>
       <c r="O67" t="n">
-        <v>0.351749557583809</v>
+        <v>0.35175555436338</v>
       </c>
       <c r="P67" t="s">
         <v>24</v>
@@ -4158,37 +4164,37 @@
         <v>19</v>
       </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G68" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H68" t="n">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="I68" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J68" t="n">
         <v>2002</v>
       </c>
       <c r="K68" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L68" t="b">
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>22.4462540765769</v>
+        <v>22.4790989565816</v>
       </c>
       <c r="N68" t="n">
-        <v>-0.479047107062301</v>
+        <v>-0.480995864980439</v>
       </c>
       <c r="O68" t="n">
-        <v>0.0101183628293739</v>
+        <v>0.00838844275608132</v>
       </c>
       <c r="P68" t="s">
         <v>22</v>
@@ -4220,28 +4226,28 @@
         <v>74</v>
       </c>
       <c r="H69" t="n">
-        <v>888</v>
+        <v>938</v>
       </c>
       <c r="I69" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J69" t="n">
         <v>2006</v>
       </c>
       <c r="K69" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L69" t="b">
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>47.6649674238473</v>
+        <v>46.3746586984609</v>
       </c>
       <c r="N69" t="n">
-        <v>-1.27036875345833</v>
+        <v>-1.2011568048155</v>
       </c>
       <c r="O69" t="n">
-        <v>0.0235055099480849</v>
+        <v>0.027937436252115</v>
       </c>
       <c r="P69" t="s">
         <v>22</v>
@@ -4302,7 +4308,7 @@
         <v>15</v>
       </c>
       <c r="B71" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C71" t="s">
         <v>54</v>
@@ -4335,13 +4341,13 @@
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>0.0741863485323382</v>
+        <v>0.0741837766836102</v>
       </c>
       <c r="N71" t="n">
-        <v>-0.00244914775312295</v>
+        <v>-0.00244902200902416</v>
       </c>
       <c r="O71" t="n">
-        <v>0.196740148903206</v>
+        <v>0.196740439744983</v>
       </c>
       <c r="P71" t="s">
         <v>24</v>
@@ -4355,7 +4361,7 @@
         <v>15</v>
       </c>
       <c r="B72" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C72" t="s">
         <v>18</v>
@@ -4388,13 +4394,13 @@
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>8.74319566013521</v>
+        <v>8.74319661151512</v>
       </c>
       <c r="N72" t="n">
-        <v>-0.20777732678382</v>
+        <v>-0.207777401643563</v>
       </c>
       <c r="O72" t="n">
-        <v>0.0000785983600721293</v>
+        <v>0.0000785997368146697</v>
       </c>
       <c r="P72" t="s">
         <v>22</v>
@@ -4408,7 +4414,7 @@
         <v>15</v>
       </c>
       <c r="B73" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C73" t="s">
         <v>23</v>
@@ -4420,10 +4426,10 @@
         <v>5</v>
       </c>
       <c r="F73" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G73" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H73" t="n">
         <v>19551</v>
@@ -4441,13 +4447,13 @@
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>6.65893014025401</v>
+        <v>6.65891163497827</v>
       </c>
       <c r="N73" t="n">
-        <v>-0.244005551617337</v>
+        <v>-0.244004441404777</v>
       </c>
       <c r="O73" t="n">
-        <v>0.000291230507719468</v>
+        <v>0.000291237382101617</v>
       </c>
       <c r="P73" t="s">
         <v>22</v>
@@ -4461,7 +4467,7 @@
         <v>15</v>
       </c>
       <c r="B74" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C74" t="s">
         <v>45</v>
@@ -4473,10 +4479,10 @@
         <v>4</v>
       </c>
       <c r="F74" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G74" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H74" t="n">
         <v>47846</v>
@@ -4494,13 +4500,13 @@
         <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>0.0693824791412447</v>
+        <v>0.0693823921383015</v>
       </c>
       <c r="N74" t="n">
-        <v>-0.00186620090774331</v>
+        <v>-0.00186619890112549</v>
       </c>
       <c r="O74" t="n">
-        <v>0.413500371689689</v>
+        <v>0.413509828720947</v>
       </c>
       <c r="P74" t="s">
         <v>24</v>
@@ -4514,7 +4520,7 @@
         <v>15</v>
       </c>
       <c r="B75" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C75" t="s">
         <v>31</v>
@@ -4526,10 +4532,10 @@
         <v>3</v>
       </c>
       <c r="F75" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G75" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H75" t="n">
         <v>17558</v>
@@ -4547,13 +4553,13 @@
         <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>-0.0286063078687182</v>
+        <v>-0.0286082793374007</v>
       </c>
       <c r="N75" t="n">
-        <v>0.00220465781341062</v>
+        <v>0.00220478953462989</v>
       </c>
       <c r="O75" t="n">
-        <v>0.127260017280868</v>
+        <v>0.127181663601449</v>
       </c>
       <c r="P75" t="s">
         <v>24</v>
@@ -4567,7 +4573,7 @@
         <v>15</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C76" t="s">
         <v>32</v>
@@ -4579,10 +4585,10 @@
         <v>5</v>
       </c>
       <c r="F76" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G76" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H76" t="n">
         <v>19436</v>
@@ -4600,13 +4606,13 @@
         <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>4.94124465717422</v>
+        <v>4.94124901518653</v>
       </c>
       <c r="N76" t="n">
-        <v>-0.107991097626809</v>
+        <v>-0.107990989122168</v>
       </c>
       <c r="O76" t="n">
-        <v>0.0175021586314602</v>
+        <v>0.0175009117538121</v>
       </c>
       <c r="P76" t="s">
         <v>22</v>
@@ -4620,7 +4626,7 @@
         <v>15</v>
       </c>
       <c r="B77" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C77" t="s">
         <v>33</v>
@@ -4632,10 +4638,10 @@
         <v>5</v>
       </c>
       <c r="F77" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G77" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H77" t="n">
         <v>19879</v>
@@ -4653,13 +4659,13 @@
         <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>42.2873517846192</v>
+        <v>42.2873600414155</v>
       </c>
       <c r="N77" t="n">
-        <v>-1.38206015255954</v>
+        <v>-1.38206160513919</v>
       </c>
       <c r="O77" t="n">
-        <v>0.000000000000000000000000000505749538387561</v>
+        <v>0.000000000000000000000000000507076319972249</v>
       </c>
       <c r="P77" t="s">
         <v>22</v>
@@ -4673,7 +4679,7 @@
         <v>15</v>
       </c>
       <c r="B78" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C78" t="s">
         <v>46</v>
@@ -4706,13 +4712,13 @@
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>31.2798285343373</v>
+        <v>31.2796444958821</v>
       </c>
       <c r="N78" t="n">
-        <v>0.237657083252429</v>
+        <v>0.237683341872276</v>
       </c>
       <c r="O78" t="n">
-        <v>0.116657820450709</v>
+        <v>0.116611779914993</v>
       </c>
       <c r="P78" t="s">
         <v>24</v>
@@ -4726,7 +4732,7 @@
         <v>15</v>
       </c>
       <c r="B79" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C79" t="s">
         <v>61</v>
@@ -4738,10 +4744,10 @@
         <v>4</v>
       </c>
       <c r="F79" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G79" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H79" t="n">
         <v>16627</v>
@@ -4759,13 +4765,13 @@
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>15.7746961170676</v>
+        <v>15.7746956927541</v>
       </c>
       <c r="N79" t="n">
-        <v>0.276558340253779</v>
+        <v>0.276558367676138</v>
       </c>
       <c r="O79" t="n">
-        <v>0.00103336552605391</v>
+        <v>0.00103336506865519</v>
       </c>
       <c r="P79" t="s">
         <v>50</v>
@@ -4779,7 +4785,7 @@
         <v>17</v>
       </c>
       <c r="B80" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C80" t="s">
         <v>23</v>
@@ -4791,10 +4797,10 @@
         <v>1</v>
       </c>
       <c r="F80" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G80" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H80" t="n">
         <v>1280</v>
@@ -4812,13 +4818,13 @@
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>57.578898983305</v>
+        <v>57.5789041487846</v>
       </c>
       <c r="N80" t="n">
-        <v>-0.376754052299389</v>
+        <v>-0.376754267119497</v>
       </c>
       <c r="O80" t="n">
-        <v>0.295357422338898</v>
+        <v>0.295357550046998</v>
       </c>
       <c r="P80" t="s">
         <v>24</v>
@@ -4832,7 +4838,7 @@
         <v>17</v>
       </c>
       <c r="B81" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C81" t="s">
         <v>29</v>
@@ -4844,10 +4850,10 @@
         <v>1</v>
       </c>
       <c r="F81" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G81" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H81" t="n">
         <v>166</v>
@@ -4879,7 +4885,7 @@
         <v>17</v>
       </c>
       <c r="B82" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C82" t="s">
         <v>31</v>
@@ -4891,10 +4897,10 @@
         <v>1</v>
       </c>
       <c r="F82" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G82" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H82" t="n">
         <v>4</v>
@@ -4926,7 +4932,7 @@
         <v>17</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C83" t="s">
         <v>32</v>
@@ -4938,10 +4944,10 @@
         <v>1</v>
       </c>
       <c r="F83" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G83" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H83" t="n">
         <v>3</v>
@@ -4973,7 +4979,7 @@
         <v>17</v>
       </c>
       <c r="B84" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C84" t="s">
         <v>33</v>
@@ -4985,10 +4991,10 @@
         <v>1</v>
       </c>
       <c r="F84" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G84" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H84" t="n">
         <v>799</v>
@@ -5006,13 +5012,13 @@
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>24.5642568847679</v>
+        <v>24.5642570677399</v>
       </c>
       <c r="N84" t="n">
-        <v>0.873658294447068</v>
+        <v>0.873658287449462</v>
       </c>
       <c r="O84" t="n">
-        <v>0.141337566141349</v>
+        <v>0.141337588145644</v>
       </c>
       <c r="P84" t="s">
         <v>24</v>
@@ -5026,7 +5032,7 @@
         <v>17</v>
       </c>
       <c r="B85" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C85" t="s">
         <v>46</v>
@@ -5038,10 +5044,10 @@
         <v>1</v>
       </c>
       <c r="F85" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G85" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H85" t="n">
         <v>1577</v>
@@ -5059,13 +5065,13 @@
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>76.7899394419268</v>
+        <v>76.7899395102377</v>
       </c>
       <c r="N85" t="n">
-        <v>-0.628213299436875</v>
+        <v>-0.628213301823383</v>
       </c>
       <c r="O85" t="n">
-        <v>0.219850271952525</v>
+        <v>0.219850278351554</v>
       </c>
       <c r="P85" t="s">
         <v>24</v>
@@ -5079,7 +5085,7 @@
         <v>17</v>
       </c>
       <c r="B86" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C86" t="s">
         <v>61</v>
@@ -5091,10 +5097,10 @@
         <v>1</v>
       </c>
       <c r="F86" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G86" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H86" t="n">
         <v>1584</v>
@@ -5112,13 +5118,13 @@
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>69.8553875919234</v>
+        <v>69.8553876166734</v>
       </c>
       <c r="N86" t="n">
-        <v>-0.406426083197994</v>
+        <v>-0.40642608406873</v>
       </c>
       <c r="O86" t="n">
-        <v>0.446153345812438</v>
+        <v>0.446153341245982</v>
       </c>
       <c r="P86" t="s">
         <v>24</v>
@@ -5132,7 +5138,7 @@
         <v>18</v>
       </c>
       <c r="B87" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C87" t="s">
         <v>54</v>
@@ -5150,28 +5156,28 @@
         <v>70</v>
       </c>
       <c r="H87" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I87" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J87" t="n">
         <v>2007</v>
       </c>
       <c r="K87" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L87" t="b">
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>-11.3750931452145</v>
+        <v>-8.3194367666774</v>
       </c>
       <c r="N87" t="n">
-        <v>0.911809230536335</v>
+        <v>0.681041549846033</v>
       </c>
       <c r="O87" t="n">
-        <v>0.257189987451246</v>
+        <v>0.255705867518806</v>
       </c>
       <c r="P87" t="s">
         <v>24</v>
@@ -5185,7 +5191,7 @@
         <v>18</v>
       </c>
       <c r="B88" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C88" t="s">
         <v>18</v>
@@ -5203,28 +5209,28 @@
         <v>70</v>
       </c>
       <c r="H88" t="n">
-        <v>836</v>
+        <v>859</v>
       </c>
       <c r="I88" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J88" t="n">
         <v>1999</v>
       </c>
       <c r="K88" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L88" t="b">
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>8.35281139076768</v>
+        <v>9.88068854603729</v>
       </c>
       <c r="N88" t="n">
-        <v>0.370292305966821</v>
+        <v>0.282668148925188</v>
       </c>
       <c r="O88" t="n">
-        <v>0.179777077709195</v>
+        <v>0.280879242064466</v>
       </c>
       <c r="P88" t="s">
         <v>24</v>
@@ -5238,7 +5244,7 @@
         <v>18</v>
       </c>
       <c r="B89" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C89" t="s">
         <v>23</v>
@@ -5256,34 +5262,34 @@
         <v>70</v>
       </c>
       <c r="H89" t="n">
-        <v>2328</v>
+        <v>2409</v>
       </c>
       <c r="I89" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J89" t="n">
         <v>1998</v>
       </c>
       <c r="K89" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L89" t="b">
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>20.7923996941562</v>
+        <v>21.5876969604618</v>
       </c>
       <c r="N89" t="n">
-        <v>-0.124768401354064</v>
+        <v>-0.183223109209443</v>
       </c>
       <c r="O89" t="n">
-        <v>0.0762040357190241</v>
+        <v>0.00579894923566995</v>
       </c>
       <c r="P89" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="90">
@@ -5291,7 +5297,7 @@
         <v>18</v>
       </c>
       <c r="B90" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C90" t="s">
         <v>25</v>
@@ -5338,7 +5344,7 @@
         <v>18</v>
       </c>
       <c r="B91" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C91" t="s">
         <v>29</v>
@@ -5356,16 +5362,16 @@
         <v>70</v>
       </c>
       <c r="H91" t="n">
-        <v>698</v>
+        <v>748</v>
       </c>
       <c r="I91" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J91" t="n">
         <v>1998</v>
       </c>
       <c r="K91" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L91" t="b">
         <v>1</v>
@@ -5385,7 +5391,7 @@
         <v>18</v>
       </c>
       <c r="B92" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C92" t="s">
         <v>31</v>
@@ -5403,28 +5409,28 @@
         <v>70</v>
       </c>
       <c r="H92" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I92" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J92" t="n">
         <v>1998</v>
       </c>
       <c r="K92" t="n">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="L92" t="b">
         <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>4.26200141596094</v>
+        <v>4.53832730527662</v>
       </c>
       <c r="N92" t="n">
-        <v>-0.0392873673000695</v>
+        <v>-0.0542305884642309</v>
       </c>
       <c r="O92" t="n">
-        <v>0.79552038130418</v>
+        <v>0.696062433530853</v>
       </c>
       <c r="P92" t="s">
         <v>24</v>
@@ -5438,7 +5444,7 @@
         <v>18</v>
       </c>
       <c r="B93" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C93" t="s">
         <v>32</v>
@@ -5456,28 +5462,28 @@
         <v>70</v>
       </c>
       <c r="H93" t="n">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="I93" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J93" t="n">
         <v>1998</v>
       </c>
       <c r="K93" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L93" t="b">
         <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>46.7155255141935</v>
+        <v>47.0253988464966</v>
       </c>
       <c r="N93" t="n">
-        <v>-0.25664713624158</v>
+        <v>-0.278061434214652</v>
       </c>
       <c r="O93" t="n">
-        <v>0.622020803450261</v>
+        <v>0.556998256850247</v>
       </c>
       <c r="P93" t="s">
         <v>24</v>
@@ -5491,7 +5497,7 @@
         <v>18</v>
       </c>
       <c r="B94" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C94" t="s">
         <v>33</v>
@@ -5509,34 +5515,34 @@
         <v>70</v>
       </c>
       <c r="H94" t="n">
-        <v>1083</v>
+        <v>1121</v>
       </c>
       <c r="I94" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J94" t="n">
         <v>1998</v>
       </c>
       <c r="K94" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L94" t="b">
         <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>32.4933425051872</v>
+        <v>33.5137756265788</v>
       </c>
       <c r="N94" t="n">
-        <v>-0.222504844024384</v>
+        <v>-0.290102881821012</v>
       </c>
       <c r="O94" t="n">
-        <v>0.135218056033289</v>
+        <v>0.0247650062813919</v>
       </c>
       <c r="P94" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="95">
@@ -5544,7 +5550,7 @@
         <v>18</v>
       </c>
       <c r="B95" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C95" t="s">
         <v>61</v>
@@ -5562,28 +5568,28 @@
         <v>70</v>
       </c>
       <c r="H95" t="n">
-        <v>3401</v>
+        <v>3558</v>
       </c>
       <c r="I95" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J95" t="n">
         <v>1998</v>
       </c>
       <c r="K95" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L95" t="b">
         <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>25.2522887980839</v>
+        <v>26.7798484820617</v>
       </c>
       <c r="N95" t="n">
-        <v>-0.198908399709913</v>
+        <v>-0.297675692961475</v>
       </c>
       <c r="O95" t="n">
-        <v>0.0083590244169381</v>
+        <v>0.000109535123584571</v>
       </c>
       <c r="P95" t="s">
         <v>22</v>
@@ -5597,7 +5603,7 @@
         <v>21</v>
       </c>
       <c r="B96" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C96" t="s">
         <v>23</v>
@@ -5629,14 +5635,20 @@
       <c r="L96" t="b">
         <v>1</v>
       </c>
-      <c r="M96"/>
-      <c r="N96"/>
-      <c r="O96"/>
+      <c r="M96" t="n">
+        <v>31.1207216489607</v>
+      </c>
+      <c r="N96" t="n">
+        <v>-1.17409544909016</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0.000000000000000265052921405449</v>
+      </c>
       <c r="P96" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="Q96" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="97">
@@ -5644,7 +5656,7 @@
         <v>21</v>
       </c>
       <c r="B97" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C97" t="s">
         <v>45</v>
@@ -5677,13 +5689,13 @@
         <v>1</v>
       </c>
       <c r="M97" t="n">
-        <v>0.486526056048551</v>
+        <v>0.486526056048515</v>
       </c>
       <c r="N97" t="n">
-        <v>-0.00182694608070625</v>
+        <v>-0.00182694608070505</v>
       </c>
       <c r="O97" t="n">
-        <v>0.790980253872378</v>
+        <v>0.790980253872525</v>
       </c>
       <c r="P97" t="s">
         <v>24</v>
@@ -5697,7 +5709,7 @@
         <v>21</v>
       </c>
       <c r="B98" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C98" t="s">
         <v>31</v>
@@ -5730,13 +5742,13 @@
         <v>1</v>
       </c>
       <c r="M98" t="n">
-        <v>0.236691163978561</v>
+        <v>0.236691155504886</v>
       </c>
       <c r="N98" t="n">
-        <v>-0.0108992148815637</v>
+        <v>-0.0108992147917577</v>
       </c>
       <c r="O98" t="n">
-        <v>0.101584432953808</v>
+        <v>0.101584457182029</v>
       </c>
       <c r="P98" t="s">
         <v>24</v>
@@ -5750,7 +5762,7 @@
         <v>21</v>
       </c>
       <c r="B99" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C99" t="s">
         <v>32</v>
@@ -5783,13 +5795,13 @@
         <v>1</v>
       </c>
       <c r="M99" t="n">
-        <v>5.51511737333523</v>
+        <v>5.51511737333431</v>
       </c>
       <c r="N99" t="n">
-        <v>-0.226783227475027</v>
+        <v>-0.226783227474991</v>
       </c>
       <c r="O99" t="n">
-        <v>0.00433585695109475</v>
+        <v>0.00433585695110403</v>
       </c>
       <c r="P99" t="s">
         <v>22</v>
@@ -5803,7 +5815,7 @@
         <v>21</v>
       </c>
       <c r="B100" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C100" t="s">
         <v>33</v>
@@ -5836,13 +5848,13 @@
         <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>1.73354024142037</v>
+        <v>1.7335402414207</v>
       </c>
       <c r="N100" t="n">
-        <v>-0.0663118425822811</v>
+        <v>-0.0663118425822937</v>
       </c>
       <c r="O100" t="n">
-        <v>0.0982887196272221</v>
+        <v>0.098288719627162</v>
       </c>
       <c r="P100" t="s">
         <v>24</v>
@@ -5856,7 +5868,7 @@
         <v>21</v>
       </c>
       <c r="B101" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C101" t="s">
         <v>46</v>
@@ -5889,13 +5901,13 @@
         <v>1</v>
       </c>
       <c r="M101" t="n">
-        <v>39.5068520511913</v>
+        <v>39.5068520511929</v>
       </c>
       <c r="N101" t="n">
-        <v>-1.47099758677916</v>
+        <v>-1.47099758677923</v>
       </c>
       <c r="O101" t="n">
-        <v>0.000000000000000000000227816605153144</v>
+        <v>0.000000000000000000000227816605151645</v>
       </c>
       <c r="P101" t="s">
         <v>22</v>
@@ -5909,7 +5921,7 @@
         <v>22</v>
       </c>
       <c r="B102" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C102" t="s">
         <v>23</v>
@@ -5942,13 +5954,13 @@
         <v>1</v>
       </c>
       <c r="M102" t="n">
-        <v>27.8792723214916</v>
+        <v>27.8792723214935</v>
       </c>
       <c r="N102" t="n">
-        <v>-0.781423231347227</v>
+        <v>-0.781423231347289</v>
       </c>
       <c r="O102" t="n">
-        <v>0.000692330268166631</v>
+        <v>0.000692330268165886</v>
       </c>
       <c r="P102" t="s">
         <v>22</v>
@@ -5962,7 +5974,7 @@
         <v>22</v>
       </c>
       <c r="B103" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C103" t="s">
         <v>45</v>
@@ -5995,13 +6007,13 @@
         <v>1</v>
       </c>
       <c r="M103" t="n">
-        <v>0.122749951618511</v>
+        <v>0.122749953599383</v>
       </c>
       <c r="N103" t="n">
-        <v>0.0100819714820314</v>
+        <v>0.0100819713712992</v>
       </c>
       <c r="O103" t="n">
-        <v>0.0940962608088782</v>
+        <v>0.0940962644154574</v>
       </c>
       <c r="P103" t="s">
         <v>24</v>
@@ -6015,7 +6027,7 @@
         <v>22</v>
       </c>
       <c r="B104" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C104" t="s">
         <v>31</v>
@@ -6048,13 +6060,13 @@
         <v>1</v>
       </c>
       <c r="M104" t="n">
-        <v>0.12929124115708</v>
+        <v>0.129291243386427</v>
       </c>
       <c r="N104" t="n">
-        <v>-0.00491355372019899</v>
+        <v>-0.00491355384795132</v>
       </c>
       <c r="O104" t="n">
-        <v>0.117004457167443</v>
+        <v>0.117004373429679</v>
       </c>
       <c r="P104" t="s">
         <v>24</v>
@@ -6068,7 +6080,7 @@
         <v>22</v>
       </c>
       <c r="B105" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C105" t="s">
         <v>32</v>
@@ -6101,13 +6113,13 @@
         <v>1</v>
       </c>
       <c r="M105" t="n">
-        <v>15.4835024422216</v>
+        <v>15.4835024422215</v>
       </c>
       <c r="N105" t="n">
-        <v>-0.545921328667188</v>
+        <v>-0.545921328667183</v>
       </c>
       <c r="O105" t="n">
-        <v>0.0432676395822031</v>
+        <v>0.0432676395822189</v>
       </c>
       <c r="P105" t="s">
         <v>22</v>
@@ -6121,7 +6133,7 @@
         <v>22</v>
       </c>
       <c r="B106" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C106" t="s">
         <v>33</v>
@@ -6154,13 +6166,13 @@
         <v>1</v>
       </c>
       <c r="M106" t="n">
-        <v>5.64851568155711</v>
+        <v>5.6485155287419</v>
       </c>
       <c r="N106" t="n">
-        <v>-0.191974164438094</v>
+        <v>-0.191974153502877</v>
       </c>
       <c r="O106" t="n">
-        <v>0.0143482789438823</v>
+        <v>0.0143482574601422</v>
       </c>
       <c r="P106" t="s">
         <v>22</v>
@@ -6174,7 +6186,7 @@
         <v>22</v>
       </c>
       <c r="B107" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C107" t="s">
         <v>46</v>
@@ -6207,13 +6219,13 @@
         <v>1</v>
       </c>
       <c r="M107" t="n">
-        <v>51.2627695986105</v>
+        <v>51.2627695986094</v>
       </c>
       <c r="N107" t="n">
-        <v>-1.6030053316693</v>
+        <v>-1.60300533166926</v>
       </c>
       <c r="O107" t="n">
-        <v>0.000000000000000000379808349181876</v>
+        <v>0.0000000000000000003798083491821</v>
       </c>
       <c r="P107" t="s">
         <v>22</v>
@@ -6227,7 +6239,7 @@
         <v>23</v>
       </c>
       <c r="B108" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C108" t="s">
         <v>23</v>
@@ -6239,10 +6251,10 @@
         <v>2</v>
       </c>
       <c r="F108" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G108" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H108" t="n">
         <v>6524</v>
@@ -6260,13 +6272,13 @@
         <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>8.40851784757194</v>
+        <v>8.40853298435882</v>
       </c>
       <c r="N108" t="n">
-        <v>-0.148105183067089</v>
+        <v>-0.148105750138053</v>
       </c>
       <c r="O108" t="n">
-        <v>0.0974653898461681</v>
+        <v>0.0974605277357036</v>
       </c>
       <c r="P108" t="s">
         <v>24</v>
@@ -6280,7 +6292,7 @@
         <v>23</v>
       </c>
       <c r="B109" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C109" t="s">
         <v>45</v>
@@ -6292,10 +6304,10 @@
         <v>2</v>
       </c>
       <c r="F109" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G109" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H109" t="n">
         <v>19627</v>
@@ -6313,13 +6325,13 @@
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>1.6572921266286</v>
+        <v>1.65729212662859</v>
       </c>
       <c r="N109" t="n">
-        <v>-0.0265739062221367</v>
+        <v>-0.0265739062221364</v>
       </c>
       <c r="O109" t="n">
-        <v>0.0562321879273083</v>
+        <v>0.0562321879272954</v>
       </c>
       <c r="P109" t="s">
         <v>24</v>
@@ -6333,7 +6345,7 @@
         <v>23</v>
       </c>
       <c r="B110" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C110" t="s">
         <v>31</v>
@@ -6380,7 +6392,7 @@
         <v>23</v>
       </c>
       <c r="B111" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C111" t="s">
         <v>32</v>
@@ -6392,10 +6404,10 @@
         <v>2</v>
       </c>
       <c r="F111" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G111" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H111" t="n">
         <v>6539</v>
@@ -6413,13 +6425,13 @@
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>16.2742009880887</v>
+        <v>16.2742030890204</v>
       </c>
       <c r="N111" t="n">
-        <v>-0.560687169914942</v>
+        <v>-0.560687239374349</v>
       </c>
       <c r="O111" t="n">
-        <v>0.000440849275728977</v>
+        <v>0.000440828645399294</v>
       </c>
       <c r="P111" t="s">
         <v>22</v>
@@ -6433,7 +6445,7 @@
         <v>23</v>
       </c>
       <c r="B112" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C112" t="s">
         <v>33</v>
@@ -6445,10 +6457,10 @@
         <v>2</v>
       </c>
       <c r="F112" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G112" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H112" t="n">
         <v>6546</v>
@@ -6466,13 +6478,13 @@
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>3.15642486026929</v>
+        <v>3.15642483350953</v>
       </c>
       <c r="N112" t="n">
-        <v>-0.0916237650356675</v>
+        <v>-0.091623763989168</v>
       </c>
       <c r="O112" t="n">
-        <v>0.0657011378680577</v>
+        <v>0.0657011646476633</v>
       </c>
       <c r="P112" t="s">
         <v>24</v>
@@ -6486,7 +6498,7 @@
         <v>23</v>
       </c>
       <c r="B113" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C113" t="s">
         <v>46</v>
@@ -6519,13 +6531,13 @@
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>30.0048298261178</v>
+        <v>30.0048298261169</v>
       </c>
       <c r="N113" t="n">
-        <v>-0.774268496697167</v>
+        <v>-0.774268496697138</v>
       </c>
       <c r="O113" t="n">
-        <v>0.0000155735740157106</v>
+        <v>0.0000155735740157279</v>
       </c>
       <c r="P113" t="s">
         <v>22</v>
@@ -6539,7 +6551,7 @@
         <v>25</v>
       </c>
       <c r="B114" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C114" t="s">
         <v>54</v>
@@ -6572,13 +6584,13 @@
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>-1.17179361635508</v>
+        <v>-1.17215246622099</v>
       </c>
       <c r="N114" t="n">
-        <v>0.470981420692621</v>
+        <v>0.470994911797988</v>
       </c>
       <c r="O114" t="n">
-        <v>0.26003557319771</v>
+        <v>0.26000988155792</v>
       </c>
       <c r="P114" t="s">
         <v>24</v>
@@ -6592,7 +6604,7 @@
         <v>25</v>
       </c>
       <c r="B115" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C115" t="s">
         <v>18</v>
@@ -6610,28 +6622,28 @@
         <v>70</v>
       </c>
       <c r="H115" t="n">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="I115" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J115" t="n">
         <v>1999</v>
       </c>
       <c r="K115" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L115" t="b">
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>22.5309932775823</v>
+        <v>21.8468335793792</v>
       </c>
       <c r="N115" t="n">
-        <v>-0.544275067565711</v>
+        <v>-0.495085978987594</v>
       </c>
       <c r="O115" t="n">
-        <v>0.0227362274662352</v>
+        <v>0.0212910359867257</v>
       </c>
       <c r="P115" t="s">
         <v>22</v>
@@ -6645,7 +6657,7 @@
         <v>25</v>
       </c>
       <c r="B116" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C116" t="s">
         <v>23</v>
@@ -6657,34 +6669,34 @@
         <v>2</v>
       </c>
       <c r="F116" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G116" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H116" t="n">
-        <v>960</v>
+        <v>982</v>
       </c>
       <c r="I116" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J116" t="n">
         <v>1998</v>
       </c>
       <c r="K116" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L116" t="b">
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>28.6857141770335</v>
+        <v>28.8688351537933</v>
       </c>
       <c r="N116" t="n">
-        <v>0.188773694286756</v>
+        <v>0.176890782477276</v>
       </c>
       <c r="O116" t="n">
-        <v>0.598320943514704</v>
+        <v>0.62275701990486</v>
       </c>
       <c r="P116" t="s">
         <v>24</v>
@@ -6698,7 +6710,7 @@
         <v>25</v>
       </c>
       <c r="B117" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C117" t="s">
         <v>29</v>
@@ -6716,16 +6728,16 @@
         <v>70</v>
       </c>
       <c r="H117" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="I117" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J117" t="n">
         <v>1998</v>
       </c>
       <c r="K117" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L117" t="b">
         <v>1</v>
@@ -6745,7 +6757,7 @@
         <v>25</v>
       </c>
       <c r="B118" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C118" t="s">
         <v>32</v>
@@ -6757,34 +6769,34 @@
         <v>2</v>
       </c>
       <c r="F118" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G118" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H118" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="I118" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J118" t="n">
         <v>1998</v>
       </c>
       <c r="K118" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L118" t="b">
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>6.78381819418626</v>
+        <v>6.35928226054728</v>
       </c>
       <c r="N118" t="n">
-        <v>-0.00866100704994314</v>
+        <v>0.0168076039828135</v>
       </c>
       <c r="O118" t="n">
-        <v>0.962697808501246</v>
+        <v>0.909166567340944</v>
       </c>
       <c r="P118" t="s">
         <v>24</v>
@@ -6798,7 +6810,7 @@
         <v>25</v>
       </c>
       <c r="B119" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C119" t="s">
         <v>33</v>
@@ -6810,34 +6822,34 @@
         <v>2</v>
       </c>
       <c r="F119" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G119" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H119" t="n">
-        <v>671</v>
+        <v>682</v>
       </c>
       <c r="I119" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J119" t="n">
         <v>1998</v>
       </c>
       <c r="K119" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L119" t="b">
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>4.31520743264218</v>
+        <v>4.39776485450028</v>
       </c>
       <c r="N119" t="n">
-        <v>0.303859009487899</v>
+        <v>0.297569318935857</v>
       </c>
       <c r="O119" t="n">
-        <v>0.453703957656648</v>
+        <v>0.457118367966285</v>
       </c>
       <c r="P119" t="s">
         <v>24</v>
@@ -6851,7 +6863,7 @@
         <v>25</v>
       </c>
       <c r="B120" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C120" t="s">
         <v>61</v>
@@ -6863,34 +6875,34 @@
         <v>2</v>
       </c>
       <c r="F120" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G120" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H120" t="n">
-        <v>1181</v>
+        <v>1218</v>
       </c>
       <c r="I120" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J120" t="n">
         <v>1998</v>
       </c>
       <c r="K120" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L120" t="b">
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>26.6419579439417</v>
+        <v>27.4690277640858</v>
       </c>
       <c r="N120" t="n">
-        <v>0.549443451096848</v>
+        <v>0.495977919023034</v>
       </c>
       <c r="O120" t="n">
-        <v>0.246787900026742</v>
+        <v>0.301550430880142</v>
       </c>
       <c r="P120" t="s">
         <v>24</v>
@@ -6904,7 +6916,7 @@
         <v>26</v>
       </c>
       <c r="B121" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C121" t="s">
         <v>23</v>
@@ -6916,10 +6928,10 @@
         <v>1</v>
       </c>
       <c r="F121" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G121" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H121" t="n">
         <v>164</v>
@@ -6951,7 +6963,7 @@
         <v>26</v>
       </c>
       <c r="B122" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C122" t="s">
         <v>25</v>
@@ -6963,10 +6975,10 @@
         <v>1</v>
       </c>
       <c r="F122" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G122" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H122" t="n">
         <v>74</v>
@@ -6998,7 +7010,7 @@
         <v>26</v>
       </c>
       <c r="B123" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C123" t="s">
         <v>31</v>
@@ -7010,10 +7022,10 @@
         <v>1</v>
       </c>
       <c r="F123" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G123" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H123" t="n">
         <v>74</v>
@@ -7045,7 +7057,7 @@
         <v>26</v>
       </c>
       <c r="B124" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C124" t="s">
         <v>32</v>
@@ -7057,10 +7069,10 @@
         <v>1</v>
       </c>
       <c r="F124" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G124" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H124" t="n">
         <v>74</v>
@@ -7092,7 +7104,7 @@
         <v>26</v>
       </c>
       <c r="B125" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C125" t="s">
         <v>33</v>
@@ -7104,10 +7116,10 @@
         <v>1</v>
       </c>
       <c r="F125" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G125" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H125" t="n">
         <v>386</v>
@@ -7139,7 +7151,7 @@
         <v>26</v>
       </c>
       <c r="B126" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C126" t="s">
         <v>61</v>
@@ -7151,10 +7163,10 @@
         <v>1</v>
       </c>
       <c r="F126" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G126" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H126" t="n">
         <v>395</v>
@@ -7186,7 +7198,7 @@
         <v>27</v>
       </c>
       <c r="B127" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C127" t="s">
         <v>23</v>
@@ -7198,10 +7210,10 @@
         <v>3</v>
       </c>
       <c r="F127" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G127" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H127" t="n">
         <v>825</v>
@@ -7219,13 +7231,13 @@
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>20.19534170184</v>
+        <v>20.1953416623801</v>
       </c>
       <c r="N127" t="n">
-        <v>-0.580645182704668</v>
+        <v>-0.580645178032871</v>
       </c>
       <c r="O127" t="n">
-        <v>0.00000000000192769985029779</v>
+        <v>0.00000000000192768499513503</v>
       </c>
       <c r="P127" t="s">
         <v>22</v>
@@ -7239,7 +7251,7 @@
         <v>27</v>
       </c>
       <c r="B128" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C128" t="s">
         <v>45</v>
@@ -7251,10 +7263,10 @@
         <v>3</v>
       </c>
       <c r="F128" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G128" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H128" t="n">
         <v>2493</v>
@@ -7272,13 +7284,13 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>1.71485988102386</v>
+        <v>1.71485988096244</v>
       </c>
       <c r="N128" t="n">
-        <v>-0.0397867824814792</v>
+        <v>-0.039786782480632</v>
       </c>
       <c r="O128" t="n">
-        <v>0.00052505111566868</v>
+        <v>0.00052505111579932</v>
       </c>
       <c r="P128" t="s">
         <v>22</v>
@@ -7292,7 +7304,7 @@
         <v>27</v>
       </c>
       <c r="B129" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C129" t="s">
         <v>31</v>
@@ -7339,7 +7351,7 @@
         <v>27</v>
       </c>
       <c r="B130" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C130" t="s">
         <v>32</v>
@@ -7351,10 +7363,10 @@
         <v>3</v>
       </c>
       <c r="F130" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G130" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H130" t="n">
         <v>832</v>
@@ -7372,13 +7384,13 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>2.53951567181357</v>
+        <v>2.53951567007665</v>
       </c>
       <c r="N130" t="n">
-        <v>-0.0779050940846131</v>
+        <v>-0.0779050939895322</v>
       </c>
       <c r="O130" t="n">
-        <v>0.336338821176729</v>
+        <v>0.336338828416032</v>
       </c>
       <c r="P130" t="s">
         <v>24</v>
@@ -7392,7 +7404,7 @@
         <v>27</v>
       </c>
       <c r="B131" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C131" t="s">
         <v>33</v>
@@ -7404,10 +7416,10 @@
         <v>3</v>
       </c>
       <c r="F131" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G131" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H131" t="n">
         <v>832</v>
@@ -7425,13 +7437,13 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>0.0937987919740479</v>
+        <v>0.0937987920414367</v>
       </c>
       <c r="N131" t="n">
-        <v>-0.00400475632155672</v>
+        <v>-0.00400475632363555</v>
       </c>
       <c r="O131" t="n">
-        <v>0.30074758659337</v>
+        <v>0.300747584955435</v>
       </c>
       <c r="P131" t="s">
         <v>24</v>
@@ -7445,7 +7457,7 @@
         <v>27</v>
       </c>
       <c r="B132" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C132" t="s">
         <v>46</v>
@@ -7478,13 +7490,13 @@
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>27.6619615739441</v>
+        <v>27.6619611287409</v>
       </c>
       <c r="N132" t="n">
-        <v>-0.798741167412668</v>
+        <v>-0.798741144618895</v>
       </c>
       <c r="O132" t="n">
-        <v>0.00000000000000000216796064709784</v>
+        <v>0.00000000000000000216803263929346</v>
       </c>
       <c r="P132" t="s">
         <v>22</v>
@@ -7498,7 +7510,7 @@
         <v>28</v>
       </c>
       <c r="B133" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C133" t="s">
         <v>54</v>
@@ -7545,7 +7557,7 @@
         <v>28</v>
       </c>
       <c r="B134" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C134" t="s">
         <v>18</v>
@@ -7563,28 +7575,28 @@
         <v>70</v>
       </c>
       <c r="H134" t="n">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="I134" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J134" t="n">
         <v>2000</v>
       </c>
       <c r="K134" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L134" t="b">
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>-5.87122250558736</v>
+        <v>-3.10344816656052</v>
       </c>
       <c r="N134" t="n">
-        <v>1.10079108471336</v>
+        <v>0.943203815583346</v>
       </c>
       <c r="O134" t="n">
-        <v>0.10474902248809</v>
+        <v>0.122110248037415</v>
       </c>
       <c r="P134" t="s">
         <v>24</v>
@@ -7598,7 +7610,7 @@
         <v>28</v>
       </c>
       <c r="B135" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C135" t="s">
         <v>23</v>
@@ -7610,34 +7622,34 @@
         <v>2</v>
       </c>
       <c r="F135" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G135" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H135" t="n">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="I135" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J135" t="n">
         <v>2000</v>
       </c>
       <c r="K135" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L135" t="b">
         <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>19.6311429839964</v>
+        <v>20.4497316684264</v>
       </c>
       <c r="N135" t="n">
-        <v>0.076522796846781</v>
+        <v>0.0238158853394502</v>
       </c>
       <c r="O135" t="n">
-        <v>0.88050571645243</v>
+        <v>0.963570720088847</v>
       </c>
       <c r="P135" t="s">
         <v>24</v>
@@ -7651,10 +7663,10 @@
         <v>28</v>
       </c>
       <c r="B136" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C136" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D136" t="s">
         <v>19</v>
@@ -7698,7 +7710,7 @@
         <v>28</v>
       </c>
       <c r="B137" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C137" t="s">
         <v>25</v>
@@ -7731,13 +7743,13 @@
         <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>2.64228139022739</v>
+        <v>2.64228139349687</v>
       </c>
       <c r="N137" t="n">
-        <v>0.0681648019802267</v>
+        <v>0.0681648018038755</v>
       </c>
       <c r="O137" t="n">
-        <v>0.780887507542741</v>
+        <v>0.780887508079441</v>
       </c>
       <c r="P137" t="s">
         <v>24</v>
@@ -7751,7 +7763,7 @@
         <v>28</v>
       </c>
       <c r="B138" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C138" t="s">
         <v>29</v>
@@ -7769,16 +7781,16 @@
         <v>70</v>
       </c>
       <c r="H138" t="n">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="I138" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J138" t="n">
         <v>2000</v>
       </c>
       <c r="K138" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L138" t="b">
         <v>1</v>
@@ -7798,7 +7810,7 @@
         <v>28</v>
       </c>
       <c r="B139" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C139" t="s">
         <v>31</v>
@@ -7845,7 +7857,7 @@
         <v>28</v>
       </c>
       <c r="B140" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C140" t="s">
         <v>33</v>
@@ -7857,34 +7869,34 @@
         <v>2</v>
       </c>
       <c r="F140" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G140" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H140" t="n">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="I140" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J140" t="n">
         <v>2000</v>
       </c>
       <c r="K140" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L140" t="b">
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>26.6035655592142</v>
+        <v>28.6644715691588</v>
       </c>
       <c r="N140" t="n">
-        <v>-0.476510204712189</v>
+        <v>-0.615903711369213</v>
       </c>
       <c r="O140" t="n">
-        <v>0.158331973904867</v>
+        <v>0.0524185789008096</v>
       </c>
       <c r="P140" t="s">
         <v>24</v>
@@ -7898,7 +7910,7 @@
         <v>28</v>
       </c>
       <c r="B141" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C141" t="s">
         <v>61</v>
@@ -7916,34 +7928,34 @@
         <v>70</v>
       </c>
       <c r="H141" t="n">
-        <v>719</v>
+        <v>749</v>
       </c>
       <c r="I141" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J141" t="n">
         <v>2002</v>
       </c>
       <c r="K141" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L141" t="b">
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>33.4466492799094</v>
+        <v>36.1211747705951</v>
       </c>
       <c r="N141" t="n">
-        <v>-0.526271498290106</v>
+        <v>-0.686322311725415</v>
       </c>
       <c r="O141" t="n">
-        <v>0.134250711812299</v>
+        <v>0.0269282164487721</v>
       </c>
       <c r="P141" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q141" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="142">
@@ -7951,7 +7963,7 @@
         <v>28</v>
       </c>
       <c r="B142" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C142" t="s">
         <v>67</v>
@@ -7998,7 +8010,7 @@
         <v>29</v>
       </c>
       <c r="B143" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C143" t="s">
         <v>23</v>
@@ -8031,13 +8043,13 @@
         <v>1</v>
       </c>
       <c r="M143" t="n">
-        <v>3.70618582273872</v>
+        <v>3.70618560997302</v>
       </c>
       <c r="N143" t="n">
-        <v>0.206821431032827</v>
+        <v>0.206821437785687</v>
       </c>
       <c r="O143" t="n">
-        <v>0.238304224446081</v>
+        <v>0.238304298664762</v>
       </c>
       <c r="P143" t="s">
         <v>24</v>
@@ -8051,7 +8063,7 @@
         <v>29</v>
       </c>
       <c r="B144" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C144" t="s">
         <v>45</v>
@@ -8084,13 +8096,13 @@
         <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>-0.053610494193918</v>
+        <v>-0.0536104941871546</v>
       </c>
       <c r="N144" t="n">
-        <v>0.00283405115336671</v>
+        <v>0.00283405115312692</v>
       </c>
       <c r="O144" t="n">
-        <v>0.161567647341493</v>
+        <v>0.161567647324878</v>
       </c>
       <c r="P144" t="s">
         <v>24</v>
@@ -8104,7 +8116,7 @@
         <v>29</v>
       </c>
       <c r="B145" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C145" t="s">
         <v>31</v>
@@ -8151,7 +8163,7 @@
         <v>29</v>
       </c>
       <c r="B146" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C146" t="s">
         <v>32</v>
@@ -8198,7 +8210,7 @@
         <v>29</v>
       </c>
       <c r="B147" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C147" t="s">
         <v>33</v>
@@ -8245,7 +8257,7 @@
         <v>29</v>
       </c>
       <c r="B148" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C148" t="s">
         <v>46</v>
@@ -8278,13 +8290,13 @@
         <v>1</v>
       </c>
       <c r="M148" t="n">
-        <v>3.67438898821875</v>
+        <v>3.67438896491233</v>
       </c>
       <c r="N148" t="n">
-        <v>0.208564609640469</v>
+        <v>0.208564610351661</v>
       </c>
       <c r="O148" t="n">
-        <v>0.236718465491046</v>
+        <v>0.236718478616711</v>
       </c>
       <c r="P148" t="s">
         <v>24</v>
@@ -8298,7 +8310,7 @@
         <v>48</v>
       </c>
       <c r="B149" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C149" t="s">
         <v>18</v>
@@ -8316,7 +8328,7 @@
         <v>52</v>
       </c>
       <c r="H149" t="n">
-        <v>4768</v>
+        <v>4832</v>
       </c>
       <c r="I149" t="n">
         <v>29</v>
@@ -8331,13 +8343,13 @@
         <v>1</v>
       </c>
       <c r="M149" t="n">
-        <v>18.460796557458</v>
+        <v>18.7222744307186</v>
       </c>
       <c r="N149" t="n">
-        <v>-0.319419682122757</v>
+        <v>-0.321183647156355</v>
       </c>
       <c r="O149" t="n">
-        <v>0.431503009244388</v>
+        <v>0.424402916556277</v>
       </c>
       <c r="P149" t="s">
         <v>24</v>
@@ -8351,7 +8363,7 @@
         <v>48</v>
       </c>
       <c r="B150" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C150" t="s">
         <v>23</v>
@@ -8369,7 +8381,7 @@
         <v>52</v>
       </c>
       <c r="H150" t="n">
-        <v>2561</v>
+        <v>2577</v>
       </c>
       <c r="I150" t="n">
         <v>29</v>
@@ -8384,13 +8396,13 @@
         <v>1</v>
       </c>
       <c r="M150" t="n">
-        <v>14.4442975501166</v>
+        <v>14.751218601691</v>
       </c>
       <c r="N150" t="n">
-        <v>-0.166055290313739</v>
+        <v>-0.177629486598725</v>
       </c>
       <c r="O150" t="n">
-        <v>0.038264187108685</v>
+        <v>0.0209171014472496</v>
       </c>
       <c r="P150" t="s">
         <v>22</v>
@@ -8404,7 +8416,7 @@
         <v>48</v>
       </c>
       <c r="B151" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C151" t="s">
         <v>25</v>
@@ -8437,13 +8449,13 @@
         <v>1</v>
       </c>
       <c r="M151" t="n">
-        <v>8.7879312105827</v>
+        <v>8.78793120652235</v>
       </c>
       <c r="N151" t="n">
-        <v>0.0927755833398184</v>
+        <v>0.0927755835500384</v>
       </c>
       <c r="O151" t="n">
-        <v>0.38946976613155</v>
+        <v>0.389469765864726</v>
       </c>
       <c r="P151" t="s">
         <v>24</v>
@@ -8457,7 +8469,7 @@
         <v>48</v>
       </c>
       <c r="B152" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C152" t="s">
         <v>29</v>
@@ -8504,7 +8516,7 @@
         <v>48</v>
       </c>
       <c r="B153" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C153" t="s">
         <v>31</v>
@@ -8537,13 +8549,13 @@
         <v>1</v>
       </c>
       <c r="M153" t="n">
-        <v>8.39152299448192</v>
+        <v>8.39169481803175</v>
       </c>
       <c r="N153" t="n">
-        <v>0.0442851066408185</v>
+        <v>0.0442811327199265</v>
       </c>
       <c r="O153" t="n">
-        <v>0.969004325922695</v>
+        <v>0.969012704332876</v>
       </c>
       <c r="P153" t="s">
         <v>24</v>
@@ -8557,7 +8569,7 @@
         <v>48</v>
       </c>
       <c r="B154" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C154" t="s">
         <v>32</v>
@@ -8575,7 +8587,7 @@
         <v>52</v>
       </c>
       <c r="H154" t="n">
-        <v>2664</v>
+        <v>2718</v>
       </c>
       <c r="I154" t="n">
         <v>29</v>
@@ -8590,13 +8602,13 @@
         <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>57.5162188256729</v>
+        <v>57.6265740174364</v>
       </c>
       <c r="N154" t="n">
-        <v>-1.51153810685005</v>
+        <v>-1.51714275021571</v>
       </c>
       <c r="O154" t="n">
-        <v>0.00489236123899467</v>
+        <v>0.00474904941918257</v>
       </c>
       <c r="P154" t="s">
         <v>22</v>
@@ -8610,7 +8622,7 @@
         <v>48</v>
       </c>
       <c r="B155" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C155" t="s">
         <v>33</v>
@@ -8628,7 +8640,7 @@
         <v>52</v>
       </c>
       <c r="H155" t="n">
-        <v>9473</v>
+        <v>9681</v>
       </c>
       <c r="I155" t="n">
         <v>29</v>
@@ -8643,13 +8655,13 @@
         <v>1</v>
       </c>
       <c r="M155" t="n">
-        <v>113.703116368091</v>
+        <v>113.58094918986</v>
       </c>
       <c r="N155" t="n">
-        <v>-2.76905746455337</v>
+        <v>-2.76449946591652</v>
       </c>
       <c r="O155" t="n">
-        <v>0.00000000000000480637576416575</v>
+        <v>0.0000000000000049161779112866</v>
       </c>
       <c r="P155" t="s">
         <v>22</v>
@@ -8663,7 +8675,7 @@
         <v>34</v>
       </c>
       <c r="B156" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C156" t="s">
         <v>54</v>
@@ -8681,28 +8693,28 @@
         <v>70</v>
       </c>
       <c r="H156" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I156" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J156" t="n">
         <v>2002</v>
       </c>
       <c r="K156" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="L156" t="b">
         <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>18.4858461593842</v>
+        <v>18.158004633929</v>
       </c>
       <c r="N156" t="n">
-        <v>-0.57107692311824</v>
+        <v>-0.552076811539717</v>
       </c>
       <c r="O156" t="n">
-        <v>0.0671357480917357</v>
+        <v>0.0545747793828319</v>
       </c>
       <c r="P156" t="s">
         <v>24</v>
@@ -8716,7 +8728,7 @@
         <v>34</v>
       </c>
       <c r="B157" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C157" t="s">
         <v>18</v>
@@ -8734,28 +8746,28 @@
         <v>70</v>
       </c>
       <c r="H157" t="n">
-        <v>289</v>
+        <v>317</v>
       </c>
       <c r="I157" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J157" t="n">
         <v>2000</v>
       </c>
       <c r="K157" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L157" t="b">
         <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>12.1257564173751</v>
+        <v>10.2690958630758</v>
       </c>
       <c r="N157" t="n">
-        <v>-0.0149842466671144</v>
+        <v>0.0950389616721726</v>
       </c>
       <c r="O157" t="n">
-        <v>0.931856627659933</v>
+        <v>0.554513575878076</v>
       </c>
       <c r="P157" t="s">
         <v>24</v>
@@ -8769,7 +8781,7 @@
         <v>34</v>
       </c>
       <c r="B158" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C158" t="s">
         <v>23</v>
@@ -8781,34 +8793,34 @@
         <v>2</v>
       </c>
       <c r="F158" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G158" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H158" t="n">
-        <v>698</v>
+        <v>734</v>
       </c>
       <c r="I158" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J158" t="n">
         <v>2000</v>
       </c>
       <c r="K158" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L158" t="b">
         <v>1</v>
       </c>
       <c r="M158" t="n">
-        <v>15.443260712513</v>
+        <v>16.1276980435642</v>
       </c>
       <c r="N158" t="n">
-        <v>0.430165149041334</v>
+        <v>0.389301817469332</v>
       </c>
       <c r="O158" t="n">
-        <v>0.219275347947406</v>
+        <v>0.254274631439356</v>
       </c>
       <c r="P158" t="s">
         <v>24</v>
@@ -8822,10 +8834,10 @@
         <v>34</v>
       </c>
       <c r="B159" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C159" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D159" t="s">
         <v>19</v>
@@ -8869,7 +8881,7 @@
         <v>34</v>
       </c>
       <c r="B160" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C160" t="s">
         <v>25</v>
@@ -8881,10 +8893,10 @@
         <v>2</v>
       </c>
       <c r="F160" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G160" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H160" t="n">
         <v>3</v>
@@ -8916,7 +8928,7 @@
         <v>34</v>
       </c>
       <c r="B161" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C161" t="s">
         <v>29</v>
@@ -8934,16 +8946,16 @@
         <v>70</v>
       </c>
       <c r="H161" t="n">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="I161" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J161" t="n">
         <v>2002</v>
       </c>
       <c r="K161" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L161" t="b">
         <v>1</v>
@@ -8963,7 +8975,7 @@
         <v>34</v>
       </c>
       <c r="B162" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C162" t="s">
         <v>32</v>
@@ -8975,34 +8987,34 @@
         <v>2</v>
       </c>
       <c r="F162" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G162" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H162" t="n">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="I162" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J162" t="n">
         <v>2000</v>
       </c>
       <c r="K162" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L162" t="b">
         <v>1</v>
       </c>
       <c r="M162" t="n">
-        <v>20.5885250687694</v>
+        <v>21.2566159348705</v>
       </c>
       <c r="N162" t="n">
-        <v>0.366270859299474</v>
+        <v>0.324283457492171</v>
       </c>
       <c r="O162" t="n">
-        <v>0.283296617342563</v>
+        <v>0.300730077510925</v>
       </c>
       <c r="P162" t="s">
         <v>24</v>
@@ -9016,7 +9028,7 @@
         <v>34</v>
       </c>
       <c r="B163" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C163" t="s">
         <v>33</v>
@@ -9028,34 +9040,34 @@
         <v>2</v>
       </c>
       <c r="F163" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G163" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H163" t="n">
-        <v>746</v>
+        <v>782</v>
       </c>
       <c r="I163" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J163" t="n">
         <v>1998</v>
       </c>
       <c r="K163" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L163" t="b">
         <v>1</v>
       </c>
       <c r="M163" t="n">
-        <v>8.90778952009263</v>
+        <v>8.5974520615054</v>
       </c>
       <c r="N163" t="n">
-        <v>0.10639731584783</v>
+        <v>0.127193644723436</v>
       </c>
       <c r="O163" t="n">
-        <v>0.459517067678269</v>
+        <v>0.381032557735883</v>
       </c>
       <c r="P163" t="s">
         <v>24</v>
@@ -9069,7 +9081,7 @@
         <v>34</v>
       </c>
       <c r="B164" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C164" t="s">
         <v>61</v>
@@ -9087,28 +9099,28 @@
         <v>70</v>
       </c>
       <c r="H164" t="n">
-        <v>1333</v>
+        <v>1405</v>
       </c>
       <c r="I164" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J164" t="n">
         <v>1998</v>
       </c>
       <c r="K164" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L164" t="b">
         <v>1</v>
       </c>
       <c r="M164" t="n">
-        <v>19.2737433657373</v>
+        <v>19.8178717974954</v>
       </c>
       <c r="N164" t="n">
-        <v>0.298326138204902</v>
+        <v>0.268578219381455</v>
       </c>
       <c r="O164" t="n">
-        <v>0.328421016947526</v>
+        <v>0.366252642267873</v>
       </c>
       <c r="P164" t="s">
         <v>24</v>
@@ -9122,7 +9134,7 @@
         <v>35</v>
       </c>
       <c r="B165" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C165" t="s">
         <v>54</v>
@@ -9155,13 +9167,13 @@
         <v>1</v>
       </c>
       <c r="M165" t="n">
-        <v>1.34638775200742</v>
+        <v>1.34684351566151</v>
       </c>
       <c r="N165" t="n">
-        <v>-0.00872276598730886</v>
+        <v>-0.00874472959896072</v>
       </c>
       <c r="O165" t="n">
-        <v>0.956357577347309</v>
+        <v>0.956248348589432</v>
       </c>
       <c r="P165" t="s">
         <v>24</v>
@@ -9175,7 +9187,7 @@
         <v>35</v>
       </c>
       <c r="B166" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C166" t="s">
         <v>18</v>
@@ -9187,13 +9199,13 @@
         <v>3</v>
       </c>
       <c r="F166" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G166" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H166" t="n">
-        <v>1086</v>
+        <v>1095</v>
       </c>
       <c r="I166" t="n">
         <v>14</v>
@@ -9208,13 +9220,13 @@
         <v>1</v>
       </c>
       <c r="M166" t="n">
-        <v>-49.761290412474</v>
+        <v>-48.0345433037049</v>
       </c>
       <c r="N166" t="n">
-        <v>2.67373427225315</v>
+        <v>2.59271239673626</v>
       </c>
       <c r="O166" t="n">
-        <v>0.00000318809996200969</v>
+        <v>0.00000591891048521211</v>
       </c>
       <c r="P166" t="s">
         <v>50</v>
@@ -9228,7 +9240,7 @@
         <v>35</v>
       </c>
       <c r="B167" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C167" t="s">
         <v>23</v>
@@ -9240,13 +9252,13 @@
         <v>3</v>
       </c>
       <c r="F167" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G167" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H167" t="n">
-        <v>7125</v>
+        <v>7286</v>
       </c>
       <c r="I167" t="n">
         <v>28</v>
@@ -9261,13 +9273,13 @@
         <v>1</v>
       </c>
       <c r="M167" t="n">
-        <v>23.582597929326</v>
+        <v>25.0783082515793</v>
       </c>
       <c r="N167" t="n">
-        <v>0.205904459580598</v>
+        <v>0.126466235526937</v>
       </c>
       <c r="O167" t="n">
-        <v>0.145713233948874</v>
+        <v>0.320740596261107</v>
       </c>
       <c r="P167" t="s">
         <v>24</v>
@@ -9281,7 +9293,7 @@
         <v>35</v>
       </c>
       <c r="B168" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C168" t="s">
         <v>25</v>
@@ -9328,7 +9340,7 @@
         <v>35</v>
       </c>
       <c r="B169" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C169" t="s">
         <v>29</v>
@@ -9340,13 +9352,13 @@
         <v>2</v>
       </c>
       <c r="F169" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G169" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H169" t="n">
-        <v>3961</v>
+        <v>4152</v>
       </c>
       <c r="I169" t="n">
         <v>28</v>
@@ -9375,7 +9387,7 @@
         <v>35</v>
       </c>
       <c r="B170" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C170" t="s">
         <v>31</v>
@@ -9393,28 +9405,28 @@
         <v>66</v>
       </c>
       <c r="H170" t="n">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="I170" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J170" t="n">
         <v>1998</v>
       </c>
       <c r="K170" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L170" t="b">
         <v>1</v>
       </c>
       <c r="M170" t="n">
-        <v>-20.7179114764626</v>
+        <v>-20.5057661687606</v>
       </c>
       <c r="N170" t="n">
-        <v>1.16034761795276</v>
+        <v>1.14922027924735</v>
       </c>
       <c r="O170" t="n">
-        <v>0.368359158553326</v>
+        <v>0.372824567030726</v>
       </c>
       <c r="P170" t="s">
         <v>24</v>
@@ -9428,7 +9440,7 @@
         <v>35</v>
       </c>
       <c r="B171" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C171" t="s">
         <v>32</v>
@@ -9440,13 +9452,13 @@
         <v>3</v>
       </c>
       <c r="F171" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G171" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H171" t="n">
-        <v>4621</v>
+        <v>4780</v>
       </c>
       <c r="I171" t="n">
         <v>28</v>
@@ -9461,13 +9473,13 @@
         <v>1</v>
       </c>
       <c r="M171" t="n">
-        <v>19.9314858536334</v>
+        <v>20.6009648090533</v>
       </c>
       <c r="N171" t="n">
-        <v>0.326801795878895</v>
+        <v>0.293631264820659</v>
       </c>
       <c r="O171" t="n">
-        <v>0.114315322088279</v>
+        <v>0.143832073879305</v>
       </c>
       <c r="P171" t="s">
         <v>24</v>
@@ -9481,7 +9493,7 @@
         <v>35</v>
       </c>
       <c r="B172" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C172" t="s">
         <v>33</v>
@@ -9493,13 +9505,13 @@
         <v>3</v>
       </c>
       <c r="F172" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G172" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H172" t="n">
-        <v>4071</v>
+        <v>4196</v>
       </c>
       <c r="I172" t="n">
         <v>28</v>
@@ -9514,13 +9526,13 @@
         <v>1</v>
       </c>
       <c r="M172" t="n">
-        <v>42.2151159553225</v>
+        <v>44.349028393293</v>
       </c>
       <c r="N172" t="n">
-        <v>-0.212197716071814</v>
+        <v>-0.317529219911252</v>
       </c>
       <c r="O172" t="n">
-        <v>0.196587032046407</v>
+        <v>0.0524635307853776</v>
       </c>
       <c r="P172" t="s">
         <v>24</v>
@@ -9534,7 +9546,7 @@
         <v>35</v>
       </c>
       <c r="B173" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C173" t="s">
         <v>46</v>
@@ -9546,10 +9558,10 @@
         <v>1</v>
       </c>
       <c r="F173" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G173" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H173" t="n">
         <v>2602</v>
@@ -9567,13 +9579,13 @@
         <v>1</v>
       </c>
       <c r="M173" t="n">
-        <v>35.6054215170507</v>
+        <v>35.6054215010464</v>
       </c>
       <c r="N173" t="n">
-        <v>0.419915469481326</v>
+        <v>0.419915470287988</v>
       </c>
       <c r="O173" t="n">
-        <v>0.574127834383349</v>
+        <v>0.574127833094096</v>
       </c>
       <c r="P173" t="s">
         <v>24</v>
@@ -9587,7 +9599,7 @@
         <v>35</v>
       </c>
       <c r="B174" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C174" t="s">
         <v>67</v>
@@ -9620,13 +9632,13 @@
         <v>1</v>
       </c>
       <c r="M174" t="n">
-        <v>-1.63664205039697</v>
+        <v>-1.63664197178343</v>
       </c>
       <c r="N174" t="n">
-        <v>0.109312346931521</v>
+        <v>0.109312342785214</v>
       </c>
       <c r="O174" t="n">
-        <v>0.658167263124645</v>
+        <v>0.658167277370485</v>
       </c>
       <c r="P174" t="s">
         <v>24</v>
@@ -9640,7 +9652,7 @@
         <v>38</v>
       </c>
       <c r="B175" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C175" t="s">
         <v>23</v>
@@ -9652,10 +9664,10 @@
         <v>1</v>
       </c>
       <c r="F175" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G175" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H175" t="n">
         <v>222</v>
@@ -9673,13 +9685,13 @@
         <v>1</v>
       </c>
       <c r="M175" t="n">
-        <v>33.6286656016465</v>
+        <v>33.6286978477817</v>
       </c>
       <c r="N175" t="n">
-        <v>-1.70909816755082</v>
+        <v>-1.70910223741556</v>
       </c>
       <c r="O175" t="n">
-        <v>0.254605077074609</v>
+        <v>0.25461746433824</v>
       </c>
       <c r="P175" t="s">
         <v>24</v>
@@ -9693,10 +9705,10 @@
         <v>38</v>
       </c>
       <c r="B176" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C176" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D176" t="s">
         <v>19</v>
@@ -9705,10 +9717,10 @@
         <v>1</v>
       </c>
       <c r="F176" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G176" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H176" t="n">
         <v>113</v>
@@ -9726,13 +9738,13 @@
         <v>1</v>
       </c>
       <c r="M176" t="n">
-        <v>-0.444567344856501</v>
+        <v>-0.444568802297332</v>
       </c>
       <c r="N176" t="n">
-        <v>0.0784251979579704</v>
+        <v>0.0784251523795353</v>
       </c>
       <c r="O176" t="n">
-        <v>0.356262072866792</v>
+        <v>0.356291146707107</v>
       </c>
       <c r="P176" t="s">
         <v>24</v>
@@ -9746,7 +9758,7 @@
         <v>38</v>
       </c>
       <c r="B177" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C177" t="s">
         <v>25</v>
@@ -9758,10 +9770,10 @@
         <v>1</v>
       </c>
       <c r="F177" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G177" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H177" t="n">
         <v>222</v>
@@ -9779,13 +9791,13 @@
         <v>1</v>
       </c>
       <c r="M177" t="n">
-        <v>3.53048514537169</v>
+        <v>3.53047057456659</v>
       </c>
       <c r="N177" t="n">
-        <v>-0.23232673623941</v>
+        <v>-0.232325432260382</v>
       </c>
       <c r="O177" t="n">
-        <v>0.443711658627369</v>
+        <v>0.443706162411161</v>
       </c>
       <c r="P177" t="s">
         <v>24</v>
@@ -9799,7 +9811,7 @@
         <v>38</v>
       </c>
       <c r="B178" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C178" t="s">
         <v>32</v>
@@ -9811,10 +9823,10 @@
         <v>1</v>
       </c>
       <c r="F178" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G178" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H178" t="n">
         <v>221</v>
@@ -9832,13 +9844,13 @@
         <v>1</v>
       </c>
       <c r="M178" t="n">
-        <v>16.1047804901159</v>
+        <v>16.1047730123582</v>
       </c>
       <c r="N178" t="n">
-        <v>-1.13438365908922</v>
+        <v>-1.1343825881062</v>
       </c>
       <c r="O178" t="n">
-        <v>0.400085578534954</v>
+        <v>0.400162315253054</v>
       </c>
       <c r="P178" t="s">
         <v>24</v>
@@ -9852,7 +9864,7 @@
         <v>38</v>
       </c>
       <c r="B179" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C179" t="s">
         <v>33</v>
@@ -9864,10 +9876,10 @@
         <v>1</v>
       </c>
       <c r="F179" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G179" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H179" t="n">
         <v>222</v>
@@ -9885,13 +9897,13 @@
         <v>1</v>
       </c>
       <c r="M179" t="n">
-        <v>36.9900159752838</v>
+        <v>36.989854463834</v>
       </c>
       <c r="N179" t="n">
-        <v>-3.13814594958305</v>
+        <v>-3.13812499506774</v>
       </c>
       <c r="O179" t="n">
-        <v>0.0666593236207905</v>
+        <v>0.0666668737422986</v>
       </c>
       <c r="P179" t="s">
         <v>24</v>
@@ -9905,7 +9917,7 @@
         <v>38</v>
       </c>
       <c r="B180" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C180" t="s">
         <v>61</v>
@@ -9917,10 +9929,10 @@
         <v>1</v>
       </c>
       <c r="F180" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G180" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H180" t="n">
         <v>220</v>
@@ -9938,13 +9950,13 @@
         <v>1</v>
       </c>
       <c r="M180" t="n">
-        <v>68.3692745038019</v>
+        <v>68.3694952058844</v>
       </c>
       <c r="N180" t="n">
-        <v>-4.52094347983225</v>
+        <v>-4.52097159964253</v>
       </c>
       <c r="O180" t="n">
-        <v>0.0166190751416014</v>
+        <v>0.0166182452371247</v>
       </c>
       <c r="P180" t="s">
         <v>22</v>
@@ -9958,7 +9970,7 @@
         <v>39</v>
       </c>
       <c r="B181" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C181" t="s">
         <v>23</v>
@@ -9970,10 +9982,10 @@
         <v>1</v>
       </c>
       <c r="F181" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G181" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H181" t="n">
         <v>222</v>
@@ -9991,13 +10003,13 @@
         <v>1</v>
       </c>
       <c r="M181" t="n">
-        <v>33.6286656016465</v>
+        <v>33.6286978477817</v>
       </c>
       <c r="N181" t="n">
-        <v>-1.70909816755082</v>
+        <v>-1.70910223741556</v>
       </c>
       <c r="O181" t="n">
-        <v>0.254605077074609</v>
+        <v>0.25461746433824</v>
       </c>
       <c r="P181" t="s">
         <v>24</v>
@@ -10011,22 +10023,22 @@
         <v>39</v>
       </c>
       <c r="B182" t="s">
+        <v>119</v>
+      </c>
+      <c r="C182" t="s">
+        <v>77</v>
+      </c>
+      <c r="D182" t="s">
+        <v>19</v>
+      </c>
+      <c r="E182" t="n">
+        <v>1</v>
+      </c>
+      <c r="F182" t="s">
         <v>117</v>
       </c>
-      <c r="C182" t="s">
-        <v>75</v>
-      </c>
-      <c r="D182" t="s">
-        <v>19</v>
-      </c>
-      <c r="E182" t="n">
-        <v>1</v>
-      </c>
-      <c r="F182" t="s">
-        <v>115</v>
-      </c>
       <c r="G182" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H182" t="n">
         <v>113</v>
@@ -10044,13 +10056,13 @@
         <v>1</v>
       </c>
       <c r="M182" t="n">
-        <v>-0.444567344856501</v>
+        <v>-0.444568802297332</v>
       </c>
       <c r="N182" t="n">
-        <v>0.0784251979579704</v>
+        <v>0.0784251523795353</v>
       </c>
       <c r="O182" t="n">
-        <v>0.356262072866792</v>
+        <v>0.356291146707107</v>
       </c>
       <c r="P182" t="s">
         <v>24</v>
@@ -10064,7 +10076,7 @@
         <v>39</v>
       </c>
       <c r="B183" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C183" t="s">
         <v>25</v>
@@ -10076,10 +10088,10 @@
         <v>1</v>
       </c>
       <c r="F183" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G183" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H183" t="n">
         <v>222</v>
@@ -10097,13 +10109,13 @@
         <v>1</v>
       </c>
       <c r="M183" t="n">
-        <v>3.53048514537169</v>
+        <v>3.53047057456659</v>
       </c>
       <c r="N183" t="n">
-        <v>-0.23232673623941</v>
+        <v>-0.232325432260382</v>
       </c>
       <c r="O183" t="n">
-        <v>0.443711658627369</v>
+        <v>0.443706162411161</v>
       </c>
       <c r="P183" t="s">
         <v>24</v>
@@ -10117,7 +10129,7 @@
         <v>39</v>
       </c>
       <c r="B184" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C184" t="s">
         <v>32</v>
@@ -10129,10 +10141,10 @@
         <v>1</v>
       </c>
       <c r="F184" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G184" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H184" t="n">
         <v>221</v>
@@ -10150,13 +10162,13 @@
         <v>1</v>
       </c>
       <c r="M184" t="n">
-        <v>16.1047804901159</v>
+        <v>16.1047730123582</v>
       </c>
       <c r="N184" t="n">
-        <v>-1.13438365908922</v>
+        <v>-1.1343825881062</v>
       </c>
       <c r="O184" t="n">
-        <v>0.400085578534954</v>
+        <v>0.400162315253054</v>
       </c>
       <c r="P184" t="s">
         <v>24</v>
@@ -10170,7 +10182,7 @@
         <v>39</v>
       </c>
       <c r="B185" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C185" t="s">
         <v>33</v>
@@ -10182,10 +10194,10 @@
         <v>1</v>
       </c>
       <c r="F185" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G185" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H185" t="n">
         <v>222</v>
@@ -10203,13 +10215,13 @@
         <v>1</v>
       </c>
       <c r="M185" t="n">
-        <v>36.9900159752838</v>
+        <v>36.989854463834</v>
       </c>
       <c r="N185" t="n">
-        <v>-3.13814594958305</v>
+        <v>-3.13812499506774</v>
       </c>
       <c r="O185" t="n">
-        <v>0.0666593236207905</v>
+        <v>0.0666668737422986</v>
       </c>
       <c r="P185" t="s">
         <v>24</v>
@@ -10223,7 +10235,7 @@
         <v>39</v>
       </c>
       <c r="B186" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C186" t="s">
         <v>61</v>
@@ -10235,10 +10247,10 @@
         <v>1</v>
       </c>
       <c r="F186" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G186" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H186" t="n">
         <v>220</v>
@@ -10256,13 +10268,13 @@
         <v>1</v>
       </c>
       <c r="M186" t="n">
-        <v>68.3692745038019</v>
+        <v>68.3694952058844</v>
       </c>
       <c r="N186" t="n">
-        <v>-4.52094347983225</v>
+        <v>-4.52097159964253</v>
       </c>
       <c r="O186" t="n">
-        <v>0.0166190751416014</v>
+        <v>0.0166182452371247</v>
       </c>
       <c r="P186" t="s">
         <v>22</v>
@@ -10276,7 +10288,7 @@
         <v>40</v>
       </c>
       <c r="B187" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C187" t="s">
         <v>18</v>
@@ -10294,34 +10306,34 @@
         <v>38</v>
       </c>
       <c r="H187" t="n">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="I187" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J187" t="n">
         <v>2016</v>
       </c>
       <c r="K187" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="L187" t="b">
         <v>1</v>
       </c>
       <c r="M187" t="n">
-        <v>84.4240521172969</v>
+        <v>91.0574153945602</v>
       </c>
       <c r="N187" t="n">
-        <v>-2.62425691537163</v>
+        <v>-2.89553179318251</v>
       </c>
       <c r="O187" t="n">
-        <v>0.0740357853759614</v>
+        <v>0.0196482789849659</v>
       </c>
       <c r="P187" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q187" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="188">
@@ -10329,7 +10341,7 @@
         <v>40</v>
       </c>
       <c r="B188" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C188" t="s">
         <v>23</v>
@@ -10341,34 +10353,34 @@
         <v>2</v>
       </c>
       <c r="F188" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G188" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H188" t="n">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="I188" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J188" t="n">
         <v>2000</v>
       </c>
       <c r="K188" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="L188" t="b">
         <v>1</v>
       </c>
       <c r="M188" t="n">
-        <v>11.986980400469</v>
+        <v>9.41132334742634</v>
       </c>
       <c r="N188" t="n">
-        <v>0.27052871960507</v>
+        <v>0.548528097750594</v>
       </c>
       <c r="O188" t="n">
-        <v>0.485492239666146</v>
+        <v>0.131068457269392</v>
       </c>
       <c r="P188" t="s">
         <v>24</v>
@@ -10382,7 +10394,7 @@
         <v>40</v>
       </c>
       <c r="B189" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C189" t="s">
         <v>29</v>
@@ -10400,16 +10412,16 @@
         <v>38</v>
       </c>
       <c r="H189" t="n">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="I189" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J189" t="n">
         <v>2016</v>
       </c>
       <c r="K189" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="L189" t="b">
         <v>1</v>
@@ -10429,7 +10441,7 @@
         <v>40</v>
       </c>
       <c r="B190" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C190" t="s">
         <v>32</v>
@@ -10441,34 +10453,34 @@
         <v>2</v>
       </c>
       <c r="F190" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G190" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H190" t="n">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="I190" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J190" t="n">
         <v>2000</v>
       </c>
       <c r="K190" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="L190" t="b">
         <v>1</v>
       </c>
       <c r="M190" t="n">
-        <v>4.17278654215605</v>
+        <v>4.67257423361345</v>
       </c>
       <c r="N190" t="n">
-        <v>-0.15138953086087</v>
+        <v>-0.187295686076096</v>
       </c>
       <c r="O190" t="n">
-        <v>0.819593916025816</v>
+        <v>0.771868472194213</v>
       </c>
       <c r="P190" t="s">
         <v>24</v>
@@ -10482,7 +10494,7 @@
         <v>40</v>
       </c>
       <c r="B191" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C191" t="s">
         <v>33</v>
@@ -10494,34 +10506,34 @@
         <v>2</v>
       </c>
       <c r="F191" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G191" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H191" t="n">
-        <v>841</v>
+        <v>892</v>
       </c>
       <c r="I191" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J191" t="n">
         <v>2000</v>
       </c>
       <c r="K191" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="L191" t="b">
         <v>1</v>
       </c>
       <c r="M191" t="n">
-        <v>27.0389687993447</v>
+        <v>31.6460088573484</v>
       </c>
       <c r="N191" t="n">
-        <v>1.06249142248844</v>
+        <v>0.883367160311915</v>
       </c>
       <c r="O191" t="n">
-        <v>0.131535964561105</v>
+        <v>0.145936675518958</v>
       </c>
       <c r="P191" t="s">
         <v>24</v>
@@ -10535,7 +10547,7 @@
         <v>40</v>
       </c>
       <c r="B192" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C192" t="s">
         <v>61</v>
@@ -10547,10 +10559,10 @@
         <v>1</v>
       </c>
       <c r="F192" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G192" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H192" t="n">
         <v>413</v>
@@ -10568,13 +10580,13 @@
         <v>1</v>
       </c>
       <c r="M192" t="n">
-        <v>88.1362868491369</v>
+        <v>88.1358483652798</v>
       </c>
       <c r="N192" t="n">
-        <v>-1.52272482880892</v>
+        <v>-1.52267285532729</v>
       </c>
       <c r="O192" t="n">
-        <v>0.150214626938448</v>
+        <v>0.150214851592237</v>
       </c>
       <c r="P192" t="s">
         <v>24</v>
@@ -10588,7 +10600,7 @@
         <v>41</v>
       </c>
       <c r="B193" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C193" t="s">
         <v>18</v>
@@ -10606,28 +10618,28 @@
         <v>38</v>
       </c>
       <c r="H193" t="n">
-        <v>243</v>
+        <v>301</v>
       </c>
       <c r="I193" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J193" t="n">
         <v>2006</v>
       </c>
       <c r="K193" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="L193" t="b">
         <v>1</v>
       </c>
       <c r="M193" t="n">
-        <v>9.61203742621614</v>
+        <v>10.713726378739</v>
       </c>
       <c r="N193" t="n">
-        <v>0.0838012516893737</v>
+        <v>0.0114082971586227</v>
       </c>
       <c r="O193" t="n">
-        <v>0.831389753629501</v>
+        <v>0.97100829128881</v>
       </c>
       <c r="P193" t="s">
         <v>24</v>
@@ -10641,7 +10653,7 @@
         <v>41</v>
       </c>
       <c r="B194" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C194" t="s">
         <v>23</v>
@@ -10659,28 +10671,28 @@
         <v>38</v>
       </c>
       <c r="H194" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="I194" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J194" t="n">
         <v>2005</v>
       </c>
       <c r="K194" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="L194" t="b">
         <v>1</v>
       </c>
       <c r="M194" t="n">
-        <v>48.4483227947062</v>
+        <v>48.8759408090689</v>
       </c>
       <c r="N194" t="n">
-        <v>-0.491452101326007</v>
+        <v>-0.414586101455546</v>
       </c>
       <c r="O194" t="n">
-        <v>0.503221347188028</v>
+        <v>0.576779327137375</v>
       </c>
       <c r="P194" t="s">
         <v>24</v>
@@ -10694,7 +10706,7 @@
         <v>41</v>
       </c>
       <c r="B195" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C195" t="s">
         <v>29</v>
@@ -10712,16 +10724,16 @@
         <v>38</v>
       </c>
       <c r="H195" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="I195" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J195" t="n">
         <v>2005</v>
       </c>
       <c r="K195" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="L195" t="b">
         <v>0</v>
@@ -10741,7 +10753,7 @@
         <v>41</v>
       </c>
       <c r="B196" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C196" t="s">
         <v>32</v>
@@ -10759,28 +10771,28 @@
         <v>38</v>
       </c>
       <c r="H196" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="I196" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J196" t="n">
         <v>2005</v>
       </c>
       <c r="K196" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="L196" t="b">
         <v>1</v>
       </c>
       <c r="M196" t="n">
-        <v>54.1971703449698</v>
+        <v>50.6094726174639</v>
       </c>
       <c r="N196" t="n">
-        <v>-0.898587802225779</v>
+        <v>-0.749606334966688</v>
       </c>
       <c r="O196" t="n">
-        <v>0.256698903785388</v>
+        <v>0.279645635169462</v>
       </c>
       <c r="P196" t="s">
         <v>24</v>
@@ -10794,7 +10806,7 @@
         <v>41</v>
       </c>
       <c r="B197" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C197" t="s">
         <v>33</v>
@@ -10812,28 +10824,28 @@
         <v>38</v>
       </c>
       <c r="H197" t="n">
-        <v>865</v>
+        <v>938</v>
       </c>
       <c r="I197" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J197" t="n">
         <v>2005</v>
       </c>
       <c r="K197" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="L197" t="b">
         <v>1</v>
       </c>
       <c r="M197" t="n">
-        <v>62.3803683883504</v>
+        <v>49.4655456784082</v>
       </c>
       <c r="N197" t="n">
-        <v>-0.142093117878052</v>
+        <v>0.517957141870631</v>
       </c>
       <c r="O197" t="n">
-        <v>0.687476157247382</v>
+        <v>0.112296480954023</v>
       </c>
       <c r="P197" t="s">
         <v>24</v>
@@ -10847,7 +10859,7 @@
         <v>43</v>
       </c>
       <c r="B198" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C198" t="s">
         <v>18</v>
@@ -10865,7 +10877,7 @@
         <v>52</v>
       </c>
       <c r="H198" t="n">
-        <v>1328</v>
+        <v>1382</v>
       </c>
       <c r="I198" t="n">
         <v>29</v>
@@ -10880,13 +10892,13 @@
         <v>1</v>
       </c>
       <c r="M198" t="n">
-        <v>18.4230481020772</v>
+        <v>17.6804655370662</v>
       </c>
       <c r="N198" t="n">
-        <v>-0.224003186251882</v>
+        <v>-0.177024782821921</v>
       </c>
       <c r="O198" t="n">
-        <v>0.103428972363119</v>
+        <v>0.189234538688251</v>
       </c>
       <c r="P198" t="s">
         <v>24</v>
@@ -10900,7 +10912,7 @@
         <v>43</v>
       </c>
       <c r="B199" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C199" t="s">
         <v>23</v>
@@ -10918,7 +10930,7 @@
         <v>52</v>
       </c>
       <c r="H199" t="n">
-        <v>1631</v>
+        <v>1672</v>
       </c>
       <c r="I199" t="n">
         <v>29</v>
@@ -10933,13 +10945,13 @@
         <v>1</v>
       </c>
       <c r="M199" t="n">
-        <v>27.1359792559161</v>
+        <v>27.7271498126127</v>
       </c>
       <c r="N199" t="n">
-        <v>-0.261424059195711</v>
+        <v>-0.294852695382445</v>
       </c>
       <c r="O199" t="n">
-        <v>0.1437116811893</v>
+        <v>0.098841231894384</v>
       </c>
       <c r="P199" t="s">
         <v>24</v>
@@ -10953,7 +10965,7 @@
         <v>43</v>
       </c>
       <c r="B200" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C200" t="s">
         <v>25</v>
@@ -10971,7 +10983,7 @@
         <v>52</v>
       </c>
       <c r="H200" t="n">
-        <v>503</v>
+        <v>517</v>
       </c>
       <c r="I200" t="n">
         <v>27</v>
@@ -10986,13 +10998,13 @@
         <v>1</v>
       </c>
       <c r="M200" t="n">
-        <v>75.1431686053921</v>
+        <v>75.9743706418127</v>
       </c>
       <c r="N200" t="n">
-        <v>-2.16214489044141</v>
+        <v>-2.19763944366416</v>
       </c>
       <c r="O200" t="n">
-        <v>0.044702954339368</v>
+        <v>0.0405496334355117</v>
       </c>
       <c r="P200" t="s">
         <v>22</v>
@@ -11006,7 +11018,7 @@
         <v>43</v>
       </c>
       <c r="B201" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C201" t="s">
         <v>29</v>
@@ -11053,7 +11065,7 @@
         <v>43</v>
       </c>
       <c r="B202" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C202" t="s">
         <v>31</v>
@@ -11086,13 +11098,13 @@
         <v>1</v>
       </c>
       <c r="M202" t="n">
-        <v>23.5414554090611</v>
+        <v>23.5415153240853</v>
       </c>
       <c r="N202" t="n">
-        <v>-0.163019815792196</v>
+        <v>-0.163024025941442</v>
       </c>
       <c r="O202" t="n">
-        <v>0.664093711204479</v>
+        <v>0.664088876969403</v>
       </c>
       <c r="P202" t="s">
         <v>24</v>
@@ -11106,7 +11118,7 @@
         <v>43</v>
       </c>
       <c r="B203" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C203" t="s">
         <v>32</v>
@@ -11124,7 +11136,7 @@
         <v>52</v>
       </c>
       <c r="H203" t="n">
-        <v>747</v>
+        <v>767</v>
       </c>
       <c r="I203" t="n">
         <v>29</v>
@@ -11139,13 +11151,13 @@
         <v>1</v>
       </c>
       <c r="M203" t="n">
-        <v>18.494359011557</v>
+        <v>18.9597242583327</v>
       </c>
       <c r="N203" t="n">
-        <v>-0.134124424203036</v>
+        <v>-0.168584802053991</v>
       </c>
       <c r="O203" t="n">
-        <v>0.511251330606643</v>
+        <v>0.39005407000185</v>
       </c>
       <c r="P203" t="s">
         <v>24</v>
@@ -11159,7 +11171,7 @@
         <v>43</v>
       </c>
       <c r="B204" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C204" t="s">
         <v>33</v>
@@ -11177,7 +11189,7 @@
         <v>52</v>
       </c>
       <c r="H204" t="n">
-        <v>3260</v>
+        <v>3500</v>
       </c>
       <c r="I204" t="n">
         <v>29</v>
@@ -11192,13 +11204,13 @@
         <v>1</v>
       </c>
       <c r="M204" t="n">
-        <v>36.1626677265256</v>
+        <v>36.0985627998831</v>
       </c>
       <c r="N204" t="n">
-        <v>-0.183596335695938</v>
+        <v>-0.189727253080178</v>
       </c>
       <c r="O204" t="n">
-        <v>0.249088171024273</v>
+        <v>0.20361053790983</v>
       </c>
       <c r="P204" t="s">
         <v>24</v>
@@ -11212,7 +11224,7 @@
         <v>44</v>
       </c>
       <c r="B205" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C205" t="s">
         <v>18</v>
@@ -11230,28 +11242,34 @@
         <v>64</v>
       </c>
       <c r="H205" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I205" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J205" t="n">
         <v>2018</v>
       </c>
       <c r="K205" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L205" t="b">
-        <v>0</v>
-      </c>
-      <c r="M205"/>
-      <c r="N205"/>
-      <c r="O205"/>
+        <v>1</v>
+      </c>
+      <c r="M205" t="n">
+        <v>131.134112551523</v>
+      </c>
+      <c r="N205" t="n">
+        <v>-4.05614620363876</v>
+      </c>
+      <c r="O205" t="n">
+        <v>0.374745189273084</v>
+      </c>
       <c r="P205" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="Q205" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206">
@@ -11259,7 +11277,7 @@
         <v>44</v>
       </c>
       <c r="B206" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C206" t="s">
         <v>23</v>
@@ -11277,28 +11295,28 @@
         <v>64</v>
       </c>
       <c r="H206" t="n">
-        <v>743</v>
+        <v>760</v>
       </c>
       <c r="I206" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J206" t="n">
         <v>1999</v>
       </c>
       <c r="K206" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L206" t="b">
         <v>1</v>
       </c>
       <c r="M206" t="n">
-        <v>25.7351476699092</v>
+        <v>25.6800674300704</v>
       </c>
       <c r="N206" t="n">
-        <v>0.862848997722573</v>
+        <v>0.86889910949592</v>
       </c>
       <c r="O206" t="n">
-        <v>0.00417574791793629</v>
+        <v>0.00138933333999656</v>
       </c>
       <c r="P206" t="s">
         <v>50</v>
@@ -11312,7 +11330,7 @@
         <v>44</v>
       </c>
       <c r="B207" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C207" t="s">
         <v>29</v>
@@ -11330,16 +11348,16 @@
         <v>64</v>
       </c>
       <c r="H207" t="n">
-        <v>987</v>
+        <v>1003</v>
       </c>
       <c r="I207" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J207" t="n">
         <v>1999</v>
       </c>
       <c r="K207" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L207" t="b">
         <v>1</v>
@@ -11359,7 +11377,7 @@
         <v>44</v>
       </c>
       <c r="B208" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C208" t="s">
         <v>31</v>
@@ -11406,7 +11424,7 @@
         <v>44</v>
       </c>
       <c r="B209" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C209" t="s">
         <v>32</v>
@@ -11424,28 +11442,28 @@
         <v>64</v>
       </c>
       <c r="H209" t="n">
-        <v>559</v>
+        <v>582</v>
       </c>
       <c r="I209" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J209" t="n">
         <v>1999</v>
       </c>
       <c r="K209" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="L209" t="b">
         <v>1</v>
       </c>
       <c r="M209" t="n">
-        <v>36.5374750333897</v>
+        <v>36.7344890625355</v>
       </c>
       <c r="N209" t="n">
-        <v>0.141924957308238</v>
+        <v>0.131532821493016</v>
       </c>
       <c r="O209" t="n">
-        <v>0.708114476390101</v>
+        <v>0.722210605272927</v>
       </c>
       <c r="P209" t="s">
         <v>24</v>
@@ -11459,7 +11477,7 @@
         <v>44</v>
       </c>
       <c r="B210" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C210" t="s">
         <v>33</v>
@@ -11477,28 +11495,28 @@
         <v>64</v>
       </c>
       <c r="H210" t="n">
-        <v>1707</v>
+        <v>1739</v>
       </c>
       <c r="I210" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J210" t="n">
         <v>1999</v>
       </c>
       <c r="K210" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L210" t="b">
         <v>1</v>
       </c>
       <c r="M210" t="n">
-        <v>34.4313177493427</v>
+        <v>33.6813297719142</v>
       </c>
       <c r="N210" t="n">
-        <v>0.229663001402628</v>
+        <v>0.284004599679369</v>
       </c>
       <c r="O210" t="n">
-        <v>0.446908276330308</v>
+        <v>0.317855076251355</v>
       </c>
       <c r="P210" t="s">
         <v>24</v>
@@ -11512,7 +11530,7 @@
         <v>44</v>
       </c>
       <c r="B211" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C211" t="s">
         <v>67</v>
